--- a/portfolio_parameter_sweep Study.xlsx
+++ b/portfolio_parameter_sweep Study.xlsx
@@ -13,13 +13,13 @@
   <calcPr calcId="124519"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId3"/>
-    <pivotCache cacheId="6" r:id="rId4"/>
+    <pivotCache cacheId="11" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
   <si>
     <t>Top_N</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Year</t>
+  </si>
+  <si>
+    <t>(blank)</t>
   </si>
 </sst>
 </file>
@@ -582,7 +585,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -600,6 +603,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -647,7 +656,147 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="71">
+  <dxfs count="62">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" readingOrder="0"/>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -785,264 +934,10 @@
       <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" readingOrder="0"/>
@@ -1054,186 +949,7 @@
       <numFmt numFmtId="164" formatCode="0.0"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
     </dxf>
     <dxf>
       <border>
@@ -1347,7 +1063,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46302.854568981478" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="38">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46309.00774641204" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="53">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J1048576" sheet="BACKTEST NEW "/>
   </cacheSource>
@@ -1372,9 +1088,10 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Years" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="5" count="3">
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="10" count="4">
         <n v="3"/>
         <n v="5"/>
+        <n v="10"/>
         <m/>
       </sharedItems>
     </cacheField>
@@ -1382,22 +1099,22 @@
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1000000" maxValue="1000000"/>
     </cacheField>
     <cacheField name="Final_Portfolio_Value" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1811231.91" maxValue="5145465.99"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1000000" maxValue="5145465.99"/>
     </cacheField>
     <cacheField name="Total_Return_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="90.45" maxValue="485.56"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="90.45" maxValue="1882.77"/>
     </cacheField>
     <cacheField name="CAGR_%" numFmtId="0">
       <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="24.72" maxValue="43.26"/>
     </cacheField>
     <cacheField name="XIRR_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="23.2" maxValue="40.03"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="40.03"/>
     </cacheField>
     <cacheField name="Max_Drawdown_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="18.54" maxValue="23.98"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="18.54" maxValue="33.17"/>
     </cacheField>
     <cacheField name="Periods" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="35" maxValue="59"/>
+      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="35" maxValue="107"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
@@ -1913,7 +1630,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="38">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="53">
   <r>
     <x v="0"/>
     <x v="0"/>
@@ -2347,9 +2064,189 @@
     <n v="59"/>
   </r>
   <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1882.77"/>
+    <n v="39.79"/>
+    <n v="0"/>
+    <n v="32.06"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1808.71"/>
+    <n v="39.200000000000003"/>
+    <n v="0"/>
+    <n v="29.46"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1672.3"/>
+    <n v="38.049999999999997"/>
+    <n v="0"/>
+    <n v="30.23"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1670.6"/>
+    <n v="38.03"/>
+    <n v="0"/>
+    <n v="31.02"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1664.18"/>
+    <n v="37.97"/>
+    <n v="0"/>
+    <n v="31.15"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1640.16"/>
+    <n v="37.76"/>
+    <n v="0"/>
+    <n v="30.18"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1582.69"/>
+    <n v="37.24"/>
+    <n v="0"/>
+    <n v="28.93"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1525.26"/>
+    <n v="36.71"/>
+    <n v="0"/>
+    <n v="29.93"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1518.01"/>
+    <n v="36.64"/>
+    <n v="0"/>
+    <n v="32"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1516.19"/>
+    <n v="36.630000000000003"/>
+    <n v="0"/>
+    <n v="31.9"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1468.85"/>
+    <n v="36.17"/>
+    <n v="0"/>
+    <n v="32.35"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1426.32"/>
+    <n v="35.75"/>
+    <n v="0"/>
+    <n v="33.17"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1358.39"/>
+    <n v="35.06"/>
+    <n v="0"/>
+    <n v="32.82"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1285.33"/>
+    <n v="34.28"/>
+    <n v="0"/>
+    <n v="31.12"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="1240.77"/>
+    <n v="33.79"/>
+    <n v="0"/>
+    <n v="30.87"/>
+    <n v="107"/>
+  </r>
+  <r>
     <x v="6"/>
     <x v="3"/>
-    <x v="2"/>
+    <x v="3"/>
     <m/>
     <m/>
     <m/>
@@ -2361,7 +2258,7 @@
   <r>
     <x v="6"/>
     <x v="3"/>
-    <x v="2"/>
+    <x v="3"/>
     <m/>
     <m/>
     <m/>
@@ -2526,8 +2423,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
-  <location ref="Q3:V17" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
+  <location ref="Q3:W23" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="10">
     <pivotField name="No # stock" axis="axisRow" showAll="0">
       <items count="8">
@@ -2551,10 +2448,11 @@
       </items>
     </pivotField>
     <pivotField axis="axisRow" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="3">
+      <items count="4">
         <item x="0"/>
-        <item h="1" x="2"/>
+        <item x="3"/>
         <item x="1"/>
+        <item x="2"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
@@ -2569,7 +2467,7 @@
     <field x="2"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="13">
+  <rowItems count="19">
     <i>
       <x/>
       <x/>
@@ -2590,10 +2488,30 @@
       <x v="5"/>
     </i>
     <i>
+      <x v="1"/>
+      <x v="6"/>
+    </i>
+    <i>
       <x v="2"/>
       <x/>
     </i>
     <i r="1">
+      <x v="1"/>
+    </i>
+    <i r="1">
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i r="1">
+      <x v="4"/>
+    </i>
+    <i r="1">
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
       <x v="1"/>
     </i>
     <i r="1">
@@ -2615,7 +2533,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="4">
+  <colItems count="5">
     <i>
       <x/>
     </i>
@@ -2625,6 +2543,9 @@
     <i>
       <x v="2"/>
     </i>
+    <i>
+      <x v="3"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2632,22 +2553,22 @@
   <dataFields count="1">
     <dataField name="Year" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
-  <formats count="10">
-    <format dxfId="70">
+  <formats count="16">
+    <format dxfId="61">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="69">
+    <format dxfId="60">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="59">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2701,7 +2622,7 @@
     <format dxfId="56">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="55">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -2711,12 +2632,94 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="48">
+    <format dxfId="54">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
           <reference field="2" count="1" selected="0">
             <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="31">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="29">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="5">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -2741,6 +2744,18 @@
     <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
+          <reference field="0" count="1">
+            <x v="6"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="19">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
           <reference field="0" count="6">
             <x v="0"/>
             <x v="1"/>
@@ -2751,6 +2766,22 @@
           </reference>
           <reference field="2" count="1" selected="0">
             <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="17">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="5">
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
           </reference>
         </references>
       </pivotArea>
@@ -4734,7 +4765,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V37"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
@@ -4748,14 +4779,15 @@
     <col min="9" max="9" width="11" customWidth="1"/>
     <col min="10" max="10" width="10.42578125" customWidth="1"/>
     <col min="12" max="12" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.28515625" customWidth="1"/>
+    <col min="17" max="17" width="11.28515625" customWidth="1"/>
     <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.85546875" customWidth="1"/>
     <col min="20" max="21" width="7" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="55.5" customHeight="1">
+    <row r="1" spans="1:23" ht="55.5" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4787,7 +4819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="1">
         <v>20</v>
       </c>
@@ -4819,7 +4851,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="1">
         <v>20</v>
       </c>
@@ -4857,7 +4889,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4" s="1">
         <v>15</v>
       </c>
@@ -4904,10 +4936,13 @@
         <v>80</v>
       </c>
       <c r="V4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="W4" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="1">
         <v>15</v>
       </c>
@@ -4944,20 +4979,21 @@
       <c r="R5" s="10">
         <v>5</v>
       </c>
-      <c r="S5" s="6">
+      <c r="S5" s="11">
         <v>25.1</v>
       </c>
-      <c r="T5" s="6">
+      <c r="T5" s="11">
         <v>26.71</v>
       </c>
-      <c r="U5" s="6">
+      <c r="U5" s="11">
         <v>27.1</v>
       </c>
-      <c r="V5" s="5">
+      <c r="V5" s="5"/>
+      <c r="W5" s="5">
         <v>78.91</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="1">
         <v>30</v>
       </c>
@@ -4991,20 +5027,21 @@
       <c r="R6" s="10">
         <v>10</v>
       </c>
-      <c r="S6" s="6">
+      <c r="S6" s="11">
         <v>33.61</v>
       </c>
-      <c r="T6" s="6">
+      <c r="T6" s="11">
         <v>26.39</v>
       </c>
-      <c r="U6" s="6">
+      <c r="U6" s="11">
         <v>24.72</v>
       </c>
-      <c r="V6" s="5">
+      <c r="V6" s="5"/>
+      <c r="W6" s="5">
         <v>84.72</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="1">
         <v>15</v>
       </c>
@@ -5038,20 +5075,21 @@
       <c r="R7" s="10">
         <v>15</v>
       </c>
-      <c r="S7" s="6">
+      <c r="S7" s="11">
         <v>37.619999999999997</v>
       </c>
-      <c r="T7" s="6">
+      <c r="T7" s="11">
         <v>37.159999999999997</v>
       </c>
-      <c r="U7" s="6">
+      <c r="U7" s="11">
         <v>36.200000000000003</v>
       </c>
-      <c r="V7" s="5">
+      <c r="V7" s="5"/>
+      <c r="W7" s="5">
         <v>110.98</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="1">
         <v>20</v>
       </c>
@@ -5085,20 +5123,21 @@
       <c r="R8" s="10">
         <v>20</v>
       </c>
-      <c r="S8" s="6">
+      <c r="S8" s="11">
         <v>40.35</v>
       </c>
-      <c r="T8" s="6">
+      <c r="T8" s="11">
         <v>37.93</v>
       </c>
-      <c r="U8" s="6">
+      <c r="U8" s="11">
         <v>36.19</v>
       </c>
-      <c r="V8" s="5">
+      <c r="V8" s="5"/>
+      <c r="W8" s="5">
         <v>114.47</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="1">
         <v>10</v>
       </c>
@@ -5132,20 +5171,21 @@
       <c r="R9" s="10">
         <v>25</v>
       </c>
-      <c r="S9" s="6">
+      <c r="S9" s="11">
         <v>33.46</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="11">
         <v>32.39</v>
       </c>
-      <c r="U9" s="6">
+      <c r="U9" s="11">
         <v>31.32</v>
       </c>
-      <c r="V9" s="5">
+      <c r="V9" s="5"/>
+      <c r="W9" s="5">
         <v>97.169999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="1">
         <v>25</v>
       </c>
@@ -5179,20 +5219,21 @@
       <c r="R10" s="10">
         <v>30</v>
       </c>
-      <c r="S10" s="6">
+      <c r="S10" s="11">
         <v>36.64</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="11">
         <v>31.6</v>
       </c>
-      <c r="U10" s="6">
+      <c r="U10" s="11">
         <v>31.86</v>
       </c>
-      <c r="V10" s="5">
+      <c r="V10" s="5"/>
+      <c r="W10" s="5">
         <v>100.10000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="1">
         <v>25</v>
       </c>
@@ -5226,26 +5267,19 @@
       <c r="P11" t="s">
         <v>17</v>
       </c>
-      <c r="Q11" s="7">
-        <v>5</v>
-      </c>
-      <c r="R11" s="10">
-        <v>5</v>
-      </c>
-      <c r="S11" s="6">
-        <v>37.11</v>
-      </c>
-      <c r="T11" s="6">
-        <v>42.17</v>
-      </c>
-      <c r="U11" s="6">
-        <v>41.05</v>
-      </c>
-      <c r="V11" s="5">
-        <v>120.33</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22">
+      <c r="Q11" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="R11" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="S11" s="12"/>
+      <c r="T11" s="12"/>
+      <c r="U11" s="12"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12" s="1">
         <v>30</v>
       </c>
@@ -5276,24 +5310,27 @@
       <c r="J12" s="1">
         <v>35</v>
       </c>
-      <c r="Q12" s="7"/>
+      <c r="Q12" s="7">
+        <v>5</v>
+      </c>
       <c r="R12" s="10">
-        <v>10</v>
-      </c>
-      <c r="S12" s="6">
-        <v>40.07</v>
-      </c>
-      <c r="T12" s="6">
-        <v>33.97</v>
-      </c>
-      <c r="U12" s="6">
-        <v>36.979999999999997</v>
-      </c>
-      <c r="V12" s="5">
-        <v>111.01999999999998</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22">
+        <v>5</v>
+      </c>
+      <c r="S12" s="11">
+        <v>37.11</v>
+      </c>
+      <c r="T12" s="11">
+        <v>42.17</v>
+      </c>
+      <c r="U12" s="11">
+        <v>41.05</v>
+      </c>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5">
+        <v>120.33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13" s="1">
         <v>30</v>
       </c>
@@ -5326,22 +5363,23 @@
       </c>
       <c r="Q13" s="7"/>
       <c r="R13" s="10">
-        <v>15</v>
-      </c>
-      <c r="S13" s="6">
-        <v>43.25</v>
-      </c>
-      <c r="T13" s="6">
-        <v>43.26</v>
-      </c>
-      <c r="U13" s="6">
-        <v>41.49</v>
-      </c>
-      <c r="V13" s="5">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22">
+        <v>10</v>
+      </c>
+      <c r="S13" s="11">
+        <v>40.07</v>
+      </c>
+      <c r="T13" s="11">
+        <v>33.97</v>
+      </c>
+      <c r="U13" s="11">
+        <v>36.979999999999997</v>
+      </c>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5">
+        <v>111.01999999999998</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14" s="1">
         <v>25</v>
       </c>
@@ -5374,22 +5412,23 @@
       </c>
       <c r="Q14" s="7"/>
       <c r="R14" s="10">
-        <v>20</v>
-      </c>
-      <c r="S14" s="6">
-        <v>43.21</v>
-      </c>
-      <c r="T14" s="6">
-        <v>42.83</v>
-      </c>
-      <c r="U14" s="6">
-        <v>41.16</v>
-      </c>
-      <c r="V14" s="5">
-        <v>127.19999999999999</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22">
+        <v>15</v>
+      </c>
+      <c r="S14" s="11">
+        <v>43.25</v>
+      </c>
+      <c r="T14" s="11">
+        <v>43.26</v>
+      </c>
+      <c r="U14" s="11">
+        <v>41.49</v>
+      </c>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -5422,22 +5461,23 @@
       </c>
       <c r="Q15" s="7"/>
       <c r="R15" s="10">
-        <v>25</v>
-      </c>
-      <c r="S15" s="6">
-        <v>40.51</v>
-      </c>
-      <c r="T15" s="6">
-        <v>40.36</v>
-      </c>
-      <c r="U15" s="6">
-        <v>39.44</v>
-      </c>
-      <c r="V15" s="5">
-        <v>120.31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22">
+        <v>20</v>
+      </c>
+      <c r="S15" s="11">
+        <v>43.21</v>
+      </c>
+      <c r="T15" s="11">
+        <v>42.83</v>
+      </c>
+      <c r="U15" s="11">
+        <v>41.16</v>
+      </c>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5">
+        <v>127.19999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -5470,22 +5510,23 @@
       </c>
       <c r="Q16" s="7"/>
       <c r="R16" s="10">
-        <v>30</v>
-      </c>
-      <c r="S16" s="6">
-        <v>41.28</v>
-      </c>
-      <c r="T16" s="6">
-        <v>37.700000000000003</v>
-      </c>
-      <c r="U16" s="6">
-        <v>38.51</v>
-      </c>
-      <c r="V16" s="5">
-        <v>117.49000000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22">
+        <v>25</v>
+      </c>
+      <c r="S16" s="11">
+        <v>40.51</v>
+      </c>
+      <c r="T16" s="11">
+        <v>40.36</v>
+      </c>
+      <c r="U16" s="11">
+        <v>39.44</v>
+      </c>
+      <c r="V16" s="5"/>
+      <c r="W16" s="5">
+        <v>120.31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -5516,23 +5557,25 @@
       <c r="J17" s="1">
         <v>35</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="S17" s="4">
-        <v>452.21000000000004</v>
-      </c>
-      <c r="T17" s="4">
-        <v>432.46999999999991</v>
-      </c>
-      <c r="U17" s="4">
-        <v>426.02000000000004</v>
-      </c>
-      <c r="V17" s="4">
-        <v>1310.7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22">
+      <c r="Q17" s="7"/>
+      <c r="R17" s="10">
+        <v>30</v>
+      </c>
+      <c r="S17" s="11">
+        <v>41.28</v>
+      </c>
+      <c r="T17" s="11">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="U17" s="11">
+        <v>38.51</v>
+      </c>
+      <c r="V17" s="5"/>
+      <c r="W17" s="5">
+        <v>117.49000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18" s="1">
         <v>5</v>
       </c>
@@ -5563,8 +5606,27 @@
       <c r="J18" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="19" spans="1:22">
+      <c r="Q18" s="3">
+        <v>10</v>
+      </c>
+      <c r="R18" s="10">
+        <v>10</v>
+      </c>
+      <c r="S18" s="12">
+        <v>37.97</v>
+      </c>
+      <c r="T18" s="12">
+        <v>33.79</v>
+      </c>
+      <c r="U18" s="12">
+        <v>35.06</v>
+      </c>
+      <c r="V18" s="5"/>
+      <c r="W18" s="5">
+        <v>106.82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -5595,8 +5657,24 @@
       <c r="J19" s="1">
         <v>35</v>
       </c>
-    </row>
-    <row r="20" spans="1:22">
+      <c r="R19" s="10">
+        <v>15</v>
+      </c>
+      <c r="S19" s="12">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="T19" s="12">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="U19" s="12">
+        <v>36.71</v>
+      </c>
+      <c r="V19" s="5"/>
+      <c r="W19" s="5">
+        <v>113.96000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -5627,8 +5705,24 @@
       <c r="J20" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="R20" s="10">
+        <v>20</v>
+      </c>
+      <c r="S20" s="12">
+        <v>38.03</v>
+      </c>
+      <c r="T20" s="12">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="U20" s="12">
+        <v>34.28</v>
+      </c>
+      <c r="V20" s="5"/>
+      <c r="W20" s="5">
+        <v>108.94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21" s="1">
         <v>15</v>
       </c>
@@ -5659,8 +5753,24 @@
       <c r="J21" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="22" spans="1:22">
+      <c r="R21" s="10">
+        <v>25</v>
+      </c>
+      <c r="S21" s="12">
+        <v>37.76</v>
+      </c>
+      <c r="T21" s="12">
+        <v>35.75</v>
+      </c>
+      <c r="U21" s="12">
+        <v>37.24</v>
+      </c>
+      <c r="V21" s="5"/>
+      <c r="W21" s="5">
+        <v>110.75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5691,8 +5801,24 @@
       <c r="J22" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="23" spans="1:22">
+      <c r="R22" s="10">
+        <v>30</v>
+      </c>
+      <c r="S22" s="12">
+        <v>39.79</v>
+      </c>
+      <c r="T22" s="12">
+        <v>36.64</v>
+      </c>
+      <c r="U22" s="12">
+        <v>36.17</v>
+      </c>
+      <c r="V22" s="5"/>
+      <c r="W22" s="5">
+        <v>112.60000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5723,8 +5849,24 @@
       <c r="J23" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Q23" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S23" s="4">
+        <v>644.96</v>
+      </c>
+      <c r="T23" s="4">
+        <v>613.32999999999993</v>
+      </c>
+      <c r="U23" s="4">
+        <v>605.48</v>
+      </c>
+      <c r="V23" s="4"/>
+      <c r="W23" s="4">
+        <v>1863.77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24" s="1">
         <v>5</v>
       </c>
@@ -5756,7 +5898,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:23">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -5788,7 +5930,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:23">
       <c r="A26" s="1">
         <v>30</v>
       </c>
@@ -5820,7 +5962,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
+    <row r="27" spans="1:23">
       <c r="A27" s="1">
         <v>20</v>
       </c>
@@ -5852,7 +5994,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:23">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -5884,7 +6026,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:23">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -5916,7 +6058,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:23">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -5948,7 +6090,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31" s="1">
         <v>10</v>
       </c>
@@ -5980,7 +6122,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32" s="1">
         <v>25</v>
       </c>
@@ -6172,8 +6314,488 @@
         <v>59</v>
       </c>
     </row>
+    <row r="38" spans="1:10">
+      <c r="A38" s="1">
+        <v>30</v>
+      </c>
+      <c r="B38" s="1">
+        <v>60</v>
+      </c>
+      <c r="C38" s="1">
+        <v>10</v>
+      </c>
+      <c r="D38" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E38" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F38" s="1">
+        <v>1882.77</v>
+      </c>
+      <c r="G38" s="6">
+        <v>39.79</v>
+      </c>
+      <c r="H38" s="6">
+        <v>0</v>
+      </c>
+      <c r="I38" s="6">
+        <v>32.06</v>
+      </c>
+      <c r="J38" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="1">
+        <v>15</v>
+      </c>
+      <c r="B39" s="1">
+        <v>60</v>
+      </c>
+      <c r="C39" s="1">
+        <v>10</v>
+      </c>
+      <c r="D39" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E39" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F39" s="1">
+        <v>1808.71</v>
+      </c>
+      <c r="G39" s="6">
+        <v>39.200000000000003</v>
+      </c>
+      <c r="H39" s="6">
+        <v>0</v>
+      </c>
+      <c r="I39" s="6">
+        <v>29.46</v>
+      </c>
+      <c r="J39" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="1">
+        <v>15</v>
+      </c>
+      <c r="B40" s="1">
+        <v>70</v>
+      </c>
+      <c r="C40" s="1">
+        <v>10</v>
+      </c>
+      <c r="D40" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E40" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F40" s="1">
+        <v>1672.3</v>
+      </c>
+      <c r="G40" s="6">
+        <v>38.049999999999997</v>
+      </c>
+      <c r="H40" s="6">
+        <v>0</v>
+      </c>
+      <c r="I40" s="6">
+        <v>30.23</v>
+      </c>
+      <c r="J40" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="1">
+        <v>20</v>
+      </c>
+      <c r="B41" s="1">
+        <v>60</v>
+      </c>
+      <c r="C41" s="1">
+        <v>10</v>
+      </c>
+      <c r="D41" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E41" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F41" s="1">
+        <v>1670.6</v>
+      </c>
+      <c r="G41" s="6">
+        <v>38.03</v>
+      </c>
+      <c r="H41" s="6">
+        <v>0</v>
+      </c>
+      <c r="I41" s="6">
+        <v>31.02</v>
+      </c>
+      <c r="J41" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="1">
+        <v>10</v>
+      </c>
+      <c r="B42" s="1">
+        <v>60</v>
+      </c>
+      <c r="C42" s="1">
+        <v>10</v>
+      </c>
+      <c r="D42" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E42" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F42" s="1">
+        <v>1664.18</v>
+      </c>
+      <c r="G42" s="6">
+        <v>37.97</v>
+      </c>
+      <c r="H42" s="6">
+        <v>0</v>
+      </c>
+      <c r="I42" s="6">
+        <v>31.15</v>
+      </c>
+      <c r="J42" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="1">
+        <v>25</v>
+      </c>
+      <c r="B43" s="1">
+        <v>60</v>
+      </c>
+      <c r="C43" s="1">
+        <v>10</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E43" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F43" s="1">
+        <v>1640.16</v>
+      </c>
+      <c r="G43" s="6">
+        <v>37.76</v>
+      </c>
+      <c r="H43" s="6">
+        <v>0</v>
+      </c>
+      <c r="I43" s="6">
+        <v>30.18</v>
+      </c>
+      <c r="J43" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="1">
+        <v>25</v>
+      </c>
+      <c r="B44" s="1">
+        <v>80</v>
+      </c>
+      <c r="C44" s="1">
+        <v>10</v>
+      </c>
+      <c r="D44" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E44" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F44" s="1">
+        <v>1582.69</v>
+      </c>
+      <c r="G44" s="6">
+        <v>37.24</v>
+      </c>
+      <c r="H44" s="6">
+        <v>0</v>
+      </c>
+      <c r="I44" s="6">
+        <v>28.93</v>
+      </c>
+      <c r="J44" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="1">
+        <v>15</v>
+      </c>
+      <c r="B45" s="1">
+        <v>80</v>
+      </c>
+      <c r="C45" s="1">
+        <v>10</v>
+      </c>
+      <c r="D45" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E45" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F45" s="1">
+        <v>1525.26</v>
+      </c>
+      <c r="G45" s="6">
+        <v>36.71</v>
+      </c>
+      <c r="H45" s="6">
+        <v>0</v>
+      </c>
+      <c r="I45" s="6">
+        <v>29.93</v>
+      </c>
+      <c r="J45" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="1">
+        <v>30</v>
+      </c>
+      <c r="B46" s="1">
+        <v>70</v>
+      </c>
+      <c r="C46" s="1">
+        <v>10</v>
+      </c>
+      <c r="D46" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E46" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F46" s="1">
+        <v>1518.01</v>
+      </c>
+      <c r="G46" s="6">
+        <v>36.64</v>
+      </c>
+      <c r="H46" s="6">
+        <v>0</v>
+      </c>
+      <c r="I46" s="6">
+        <v>32</v>
+      </c>
+      <c r="J46" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="1">
+        <v>20</v>
+      </c>
+      <c r="B47" s="1">
+        <v>70</v>
+      </c>
+      <c r="C47" s="1">
+        <v>10</v>
+      </c>
+      <c r="D47" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E47" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F47" s="1">
+        <v>1516.19</v>
+      </c>
+      <c r="G47" s="6">
+        <v>36.630000000000003</v>
+      </c>
+      <c r="H47" s="6">
+        <v>0</v>
+      </c>
+      <c r="I47" s="6">
+        <v>31.9</v>
+      </c>
+      <c r="J47" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="1">
+        <v>30</v>
+      </c>
+      <c r="B48" s="1">
+        <v>80</v>
+      </c>
+      <c r="C48" s="1">
+        <v>10</v>
+      </c>
+      <c r="D48" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E48" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F48" s="1">
+        <v>1468.85</v>
+      </c>
+      <c r="G48" s="6">
+        <v>36.17</v>
+      </c>
+      <c r="H48" s="6">
+        <v>0</v>
+      </c>
+      <c r="I48" s="6">
+        <v>32.35</v>
+      </c>
+      <c r="J48" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="1">
+        <v>25</v>
+      </c>
+      <c r="B49" s="1">
+        <v>70</v>
+      </c>
+      <c r="C49" s="1">
+        <v>10</v>
+      </c>
+      <c r="D49" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E49" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F49" s="1">
+        <v>1426.32</v>
+      </c>
+      <c r="G49" s="6">
+        <v>35.75</v>
+      </c>
+      <c r="H49" s="6">
+        <v>0</v>
+      </c>
+      <c r="I49" s="6">
+        <v>33.17</v>
+      </c>
+      <c r="J49" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="1">
+        <v>10</v>
+      </c>
+      <c r="B50" s="1">
+        <v>80</v>
+      </c>
+      <c r="C50" s="1">
+        <v>10</v>
+      </c>
+      <c r="D50" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E50" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F50" s="1">
+        <v>1358.39</v>
+      </c>
+      <c r="G50" s="6">
+        <v>35.06</v>
+      </c>
+      <c r="H50" s="6">
+        <v>0</v>
+      </c>
+      <c r="I50" s="6">
+        <v>32.82</v>
+      </c>
+      <c r="J50" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="1">
+        <v>20</v>
+      </c>
+      <c r="B51" s="1">
+        <v>80</v>
+      </c>
+      <c r="C51" s="1">
+        <v>10</v>
+      </c>
+      <c r="D51" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E51" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F51" s="1">
+        <v>1285.33</v>
+      </c>
+      <c r="G51" s="6">
+        <v>34.28</v>
+      </c>
+      <c r="H51" s="6">
+        <v>0</v>
+      </c>
+      <c r="I51" s="6">
+        <v>31.12</v>
+      </c>
+      <c r="J51" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="1">
+        <v>10</v>
+      </c>
+      <c r="B52" s="1">
+        <v>70</v>
+      </c>
+      <c r="C52" s="1">
+        <v>10</v>
+      </c>
+      <c r="D52" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E52" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F52" s="1">
+        <v>1240.77</v>
+      </c>
+      <c r="G52" s="6">
+        <v>33.79</v>
+      </c>
+      <c r="H52" s="6">
+        <v>0</v>
+      </c>
+      <c r="I52" s="6">
+        <v>30.87</v>
+      </c>
+      <c r="J52" s="1">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting pivot="1" sqref="S5:U16">
+  <conditionalFormatting pivot="1" sqref="S5:U10 S12:U22">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -6185,7 +6807,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I37">
+  <conditionalFormatting sqref="G2:I52">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>

--- a/portfolio_parameter_sweep Study.xlsx
+++ b/portfolio_parameter_sweep Study.xlsx
@@ -4,22 +4,23 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" activeTab="1"/>
+    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="portfolio_parameter_sweep copy" sheetId="1" r:id="rId1"/>
     <sheet name="BACKTEST NEW " sheetId="2" r:id="rId2"/>
+    <sheet name="25 Sep" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
-    <pivotCache cacheId="11" r:id="rId4"/>
+    <pivotCache cacheId="13" r:id="rId4"/>
+    <pivotCache cacheId="18" r:id="rId5"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="105">
   <si>
     <t>Top_N</t>
   </si>
@@ -76,6 +77,264 @@
   </si>
   <si>
     <t>(blank)</t>
+  </si>
+  <si>
+    <t>Rank</t>
+  </si>
+  <si>
+    <t>Symbol</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>Rotation score</t>
+  </si>
+  <si>
+    <t>RRG quadrant</t>
+  </si>
+  <si>
+    <t>RRG direction</t>
+  </si>
+  <si>
+    <t>RS percentile</t>
+  </si>
+  <si>
+    <t>Last price</t>
+  </si>
+  <si>
+    <t>200-DMA</t>
+  </si>
+  <si>
+    <t>% vs 200-DMA</t>
+  </si>
+  <si>
+    <t>Sector breadth above 200-DMA (%)</t>
+  </si>
+  <si>
+    <t>Price date</t>
+  </si>
+  <si>
+    <t>LAURUSLABS</t>
+  </si>
+  <si>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Leading</t>
+  </si>
+  <si>
+    <t>accelerating</t>
+  </si>
+  <si>
+    <t>WOCKPHARMA</t>
+  </si>
+  <si>
+    <t>CAPLIPOINT</t>
+  </si>
+  <si>
+    <t>LALPATHLAB</t>
+  </si>
+  <si>
+    <t>FINCABLES</t>
+  </si>
+  <si>
+    <t>Capital Goods</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>Auto Components</t>
+  </si>
+  <si>
+    <t>MEDANTA</t>
+  </si>
+  <si>
+    <t>AJANTPHARM</t>
+  </si>
+  <si>
+    <t>CARBORUNIV</t>
+  </si>
+  <si>
+    <t>GRAPHITE</t>
+  </si>
+  <si>
+    <t>ZYDUSLIFE</t>
+  </si>
+  <si>
+    <t>WELSPUNLIV</t>
+  </si>
+  <si>
+    <t>Textiles</t>
+  </si>
+  <si>
+    <t>decelerating</t>
+  </si>
+  <si>
+    <t>DIVISLAB</t>
+  </si>
+  <si>
+    <t>GABRIEL</t>
+  </si>
+  <si>
+    <t>NAVINFLUOR</t>
+  </si>
+  <si>
+    <t>Chemicals</t>
+  </si>
+  <si>
+    <t>VIJAYA</t>
+  </si>
+  <si>
+    <t>JUBLPHARMA</t>
+  </si>
+  <si>
+    <t>CARTRADE</t>
+  </si>
+  <si>
+    <t>onsumer Services</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP</t>
+  </si>
+  <si>
+    <t>TEGA</t>
+  </si>
+  <si>
+    <t>LAURUSLABS:1;</t>
+  </si>
+  <si>
+    <t>WOCKPHARMA:2;</t>
+  </si>
+  <si>
+    <t>CAPLIPOINT:3;</t>
+  </si>
+  <si>
+    <t>LALPATHLAB:4;</t>
+  </si>
+  <si>
+    <t>FINCABLES:5;</t>
+  </si>
+  <si>
+    <t>SONACOMS:6;</t>
+  </si>
+  <si>
+    <t>MEDANTA:7;</t>
+  </si>
+  <si>
+    <t>AJANTPHARM:8;</t>
+  </si>
+  <si>
+    <t>CARBORUNIV:9;</t>
+  </si>
+  <si>
+    <t>GRAPHITE:10;</t>
+  </si>
+  <si>
+    <t>ZYDUSLIFE:11;</t>
+  </si>
+  <si>
+    <t>WELSPUNLIV:12;</t>
+  </si>
+  <si>
+    <t>DIVISLAB:13;</t>
+  </si>
+  <si>
+    <t>GABRIEL:14;</t>
+  </si>
+  <si>
+    <t>NAVINFLUOR:15;</t>
+  </si>
+  <si>
+    <t>VIJAYA:16;</t>
+  </si>
+  <si>
+    <t>JUBLPHARMA:17;</t>
+  </si>
+  <si>
+    <t>CARTRADE:18;</t>
+  </si>
+  <si>
+    <t>APOLLOHOSP:19;</t>
+  </si>
+  <si>
+    <t>TEGA:20</t>
+  </si>
+  <si>
+    <t>LAURUSLABS:1; WOCKPHARMA:2; CAPLIPOINT:3; LALPATHLAB:4; FINCABLES:5; SONACOMS:6; MEDANTA:7; AJANTPHARM:8; CARBORUNIV:9; GRAPHITE:10; ZYDUSLIFE:11; WELSPUNLIV:12; DIVISLAB:13; GABRIEL:14; NAVINFLUOR:15; VIJAYA:16; JUBLPHARMA:17; CARTRADE:18; APOLLOHOSP:19; TEGA:20</t>
+  </si>
+  <si>
+    <t>LLOYDSME</t>
+  </si>
+  <si>
+    <t>Metals &amp; Mining</t>
+  </si>
+  <si>
+    <t>Rotation score RRG</t>
+  </si>
+  <si>
+    <t>quadrant</t>
+  </si>
+  <si>
+    <t>GLAND</t>
+  </si>
+  <si>
+    <t>IPCALAB</t>
+  </si>
+  <si>
+    <t>JINDALSAW</t>
+  </si>
+  <si>
+    <t>AEGISLOG</t>
+  </si>
+  <si>
+    <t>Gas &amp; Consumable Fuels</t>
+  </si>
+  <si>
+    <t>REDINGTON</t>
+  </si>
+  <si>
+    <t>Services</t>
+  </si>
+  <si>
+    <t>SHYAMMETL</t>
+  </si>
+  <si>
+    <t>CYIENT</t>
+  </si>
+  <si>
+    <t>Information Technology</t>
+  </si>
+  <si>
+    <t>SAREGAMA</t>
+  </si>
+  <si>
+    <t>rtainment &amp; Publication</t>
+  </si>
+  <si>
+    <t>JSWINFRA</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
+  </si>
+  <si>
+    <t>TATATECH</t>
+  </si>
+  <si>
+    <t>SUNTV</t>
+  </si>
+  <si>
+    <t>OFSS</t>
+  </si>
+  <si>
+    <t>AARTIIND</t>
+  </si>
+  <si>
+    <t>HAL</t>
+  </si>
+  <si>
+    <t>PTCIL</t>
   </si>
 </sst>
 </file>
@@ -85,7 +344,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,6 +483,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -585,7 +852,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -611,6 +878,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -656,7 +945,19 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="62">
+  <dxfs count="33">
+    <dxf>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <border>
         <left style="thin">
@@ -744,49 +1045,7 @@
       <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="general" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" readingOrder="0"/>
@@ -798,134 +1057,10 @@
       <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="center" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" readingOrder="0"/>
@@ -1001,7 +1136,68 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46296.423643055554" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="42">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46309.984964120369" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="69">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:J1048576" sheet="BACKTEST NEW "/>
+  </cacheSource>
+  <cacheFields count="10">
+    <cacheField name="Top_N" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="30" count="8">
+        <n v="20"/>
+        <n v="15"/>
+        <n v="30"/>
+        <n v="10"/>
+        <n v="25"/>
+        <n v="5"/>
+        <m/>
+        <s v="Top_N"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Exit_Rank" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="60" maxValue="80" count="5">
+        <n v="60"/>
+        <n v="70"/>
+        <n v="80"/>
+        <m/>
+        <s v="Exit_Rank"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Years" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="10" count="5">
+        <n v="3"/>
+        <n v="5"/>
+        <n v="10"/>
+        <m/>
+        <s v="Years"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Initial_Capital" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="1000000" maxValue="1000000"/>
+    </cacheField>
+    <cacheField name="Final_Portfolio_Value" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="1000000" maxValue="5145465.99"/>
+    </cacheField>
+    <cacheField name="Total_Return_%" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="90.45" maxValue="1882.77"/>
+    </cacheField>
+    <cacheField name="CAGR_%" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="24.41" maxValue="43.26"/>
+    </cacheField>
+    <cacheField name="XIRR_%" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="0" maxValue="40.03"/>
+    </cacheField>
+    <cacheField name="Max_Drawdown_%" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" minValue="18.54" maxValue="44.17"/>
+    </cacheField>
+    <cacheField name="Periods" numFmtId="0">
+      <sharedItems containsBlank="1" containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="35" maxValue="107"/>
+    </cacheField>
+  </cacheFields>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46309.985704976854" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="42">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J43" sheet="portfolio_parameter_sweep copy"/>
   </cacheSource>
@@ -1040,597 +1236,27 @@
     <cacheField name="Final_Portfolio_Value" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1406798" maxValue="2231527"/>
     </cacheField>
-    <cacheField name="Total_Return_%" numFmtId="0">
+    <cacheField name="Total_Return_%" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="40" maxValue="139"/>
     </cacheField>
-    <cacheField name="CAGR_%" numFmtId="0">
+    <cacheField name="CAGR_%" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="12.1" maxValue="33.6"/>
     </cacheField>
-    <cacheField name="XIRR_%" numFmtId="0">
+    <cacheField name="XIRR_%" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="-86" maxValue="-51"/>
     </cacheField>
-    <cacheField name="Max_Drawdown_%" numFmtId="0">
+    <cacheField name="Max_Drawdown_%" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="20" maxValue="44"/>
     </cacheField>
     <cacheField name="Periods" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="35" maxValue="36" count="2">
-        <n v="36"/>
-        <n v="35"/>
-      </sharedItems>
-    </cacheField>
-  </cacheFields>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46309.00774641204" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="53">
-  <cacheSource type="worksheet">
-    <worksheetSource ref="A1:J1048576" sheet="BACKTEST NEW "/>
-  </cacheSource>
-  <cacheFields count="10">
-    <cacheField name="Top_N" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="5" maxValue="30" count="7">
-        <n v="20"/>
-        <n v="15"/>
-        <n v="30"/>
-        <n v="10"/>
-        <n v="25"/>
-        <n v="5"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Exit_Rank" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="60" maxValue="80" count="4">
-        <n v="60"/>
-        <n v="70"/>
-        <n v="80"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Years" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="3" maxValue="10" count="4">
-        <n v="3"/>
-        <n v="5"/>
-        <n v="10"/>
-        <m/>
-      </sharedItems>
-    </cacheField>
-    <cacheField name="Initial_Capital" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="1000000" maxValue="1000000"/>
-    </cacheField>
-    <cacheField name="Final_Portfolio_Value" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="1000000" maxValue="5145465.99"/>
-    </cacheField>
-    <cacheField name="Total_Return_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="90.45" maxValue="1882.77"/>
-    </cacheField>
-    <cacheField name="CAGR_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="24.72" maxValue="43.26"/>
-    </cacheField>
-    <cacheField name="XIRR_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="0" maxValue="40.03"/>
-    </cacheField>
-    <cacheField name="Max_Drawdown_%" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" minValue="18.54" maxValue="33.17"/>
-    </cacheField>
-    <cacheField name="Periods" numFmtId="0">
-      <sharedItems containsString="0" containsBlank="1" containsNumber="1" containsInteger="1" minValue="35" maxValue="107"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="35" maxValue="36"/>
     </cacheField>
   </cacheFields>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="42">
-  <r>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="2231527"/>
-    <n v="139"/>
-    <n v="33.6"/>
-    <n v="-82"/>
-    <n v="29"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="2022745"/>
-    <n v="125"/>
-    <n v="31"/>
-    <n v="-78"/>
-    <n v="32"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1953974"/>
-    <n v="121"/>
-    <n v="30.3"/>
-    <n v="-80"/>
-    <n v="36"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1950713"/>
-    <n v="121"/>
-    <n v="30.2"/>
-    <n v="-79"/>
-    <n v="35"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1891128"/>
-    <n v="115"/>
-    <n v="29.1"/>
-    <n v="-79"/>
-    <n v="34"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1747782"/>
-    <n v="95"/>
-    <n v="25.8"/>
-    <n v="-83"/>
-    <n v="36"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1790802"/>
-    <n v="97"/>
-    <n v="25.4"/>
-    <n v="-79"/>
-    <n v="37"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1728936"/>
-    <n v="93"/>
-    <n v="25.3"/>
-    <n v="-81"/>
-    <n v="34"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1751720"/>
-    <n v="89"/>
-    <n v="24.4"/>
-    <n v="-85"/>
-    <n v="38"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1689613"/>
-    <n v="83"/>
-    <n v="23.1"/>
-    <n v="-82"/>
-    <n v="38"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1746812"/>
-    <n v="78"/>
-    <n v="21.9"/>
-    <n v="-57"/>
-    <n v="20"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1642932"/>
-    <n v="78"/>
-    <n v="21.8"/>
-    <n v="-86"/>
-    <n v="39"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1668177"/>
-    <n v="76"/>
-    <n v="21.4"/>
-    <n v="-79"/>
-    <n v="35"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1780582"/>
-    <n v="76"/>
-    <n v="21.4"/>
-    <n v="-61"/>
-    <n v="23"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1777905"/>
-    <n v="75"/>
-    <n v="21.2"/>
-    <n v="-76"/>
-    <n v="34"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1662345"/>
-    <n v="75"/>
-    <n v="21.1"/>
-    <n v="-53"/>
-    <n v="20"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1657997"/>
-    <n v="74"/>
-    <n v="20.8"/>
-    <n v="-51"/>
-    <n v="20"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1665750"/>
-    <n v="73"/>
-    <n v="20.6"/>
-    <n v="-58"/>
-    <n v="23"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1828960"/>
-    <n v="75"/>
-    <n v="20.5"/>
-    <n v="-75"/>
-    <n v="41"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1735060"/>
-    <n v="72"/>
-    <n v="20.5"/>
-    <n v="-66"/>
-    <n v="25"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1733686"/>
-    <n v="72"/>
-    <n v="20.5"/>
-    <n v="-59"/>
-    <n v="22"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1775830"/>
-    <n v="75"/>
-    <n v="20.399999999999999"/>
-    <n v="-75"/>
-    <n v="41"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1647041"/>
-    <n v="71"/>
-    <n v="20.3"/>
-    <n v="-55"/>
-    <n v="20"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1887234"/>
-    <n v="70"/>
-    <n v="20.100000000000001"/>
-    <n v="-77"/>
-    <n v="38"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1833383"/>
-    <n v="71"/>
-    <n v="20.100000000000001"/>
-    <n v="-79"/>
-    <n v="40"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1709548"/>
-    <n v="70"/>
-    <n v="19.8"/>
-    <n v="-76"/>
-    <n v="37"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1629875"/>
-    <n v="69"/>
-    <n v="19.8"/>
-    <n v="-60"/>
-    <n v="24"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1645005"/>
-    <n v="69"/>
-    <n v="19.600000000000001"/>
-    <n v="-58"/>
-    <n v="25"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="4"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1649774"/>
-    <n v="68"/>
-    <n v="19.399999999999999"/>
-    <n v="-77"/>
-    <n v="34"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1692009"/>
-    <n v="68"/>
-    <n v="18.8"/>
-    <n v="-79"/>
-    <n v="37"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1628595"/>
-    <n v="67"/>
-    <n v="18.7"/>
-    <n v="-75"/>
-    <n v="37"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1584052"/>
-    <n v="67"/>
-    <n v="18.7"/>
-    <n v="-75"/>
-    <n v="44"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="9"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1578438"/>
-    <n v="66"/>
-    <n v="18.3"/>
-    <n v="-76"/>
-    <n v="37"/>
-    <x v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1620258"/>
-    <n v="62"/>
-    <n v="18"/>
-    <n v="-61"/>
-    <n v="27"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1583611"/>
-    <n v="59"/>
-    <n v="17.100000000000001"/>
-    <n v="-75"/>
-    <n v="32"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="3"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1519693"/>
-    <n v="54"/>
-    <n v="15.9"/>
-    <n v="-70"/>
-    <n v="30"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1537945"/>
-    <n v="52"/>
-    <n v="15.6"/>
-    <n v="-70"/>
-    <n v="34"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1512820"/>
-    <n v="52"/>
-    <n v="15.4"/>
-    <n v="-61"/>
-    <n v="28"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1475238"/>
-    <n v="47"/>
-    <n v="14.1"/>
-    <n v="-65"/>
-    <n v="30"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="8"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1438131"/>
-    <n v="46"/>
-    <n v="13.8"/>
-    <n v="-63"/>
-    <n v="29"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="1"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1448049"/>
-    <n v="44"/>
-    <n v="13.4"/>
-    <n v="-69"/>
-    <n v="36"/>
-    <x v="1"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="0"/>
-    <n v="1000000"/>
-    <n v="1406798"/>
-    <n v="40"/>
-    <n v="12.1"/>
-    <n v="-70"/>
-    <n v="36"/>
-    <x v="1"/>
-  </r>
-</pivotCacheRecords>
-</file>
-
-<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="53">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="69">
   <r>
     <x v="0"/>
     <x v="0"/>
@@ -2256,6 +1882,198 @@
     <m/>
   </r>
   <r>
+    <x v="7"/>
+    <x v="4"/>
+    <x v="4"/>
+    <s v="Initial_Capital"/>
+    <s v="Final_Portfolio_Value"/>
+    <s v="Total_Return_%"/>
+    <s v="CAGR_%"/>
+    <s v="XIRR_%"/>
+    <s v="Max_Drawdown_%"/>
+    <s v="Periods"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="808.46"/>
+    <n v="28.08"/>
+    <n v="0"/>
+    <n v="34.69"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="654.41"/>
+    <n v="25.44"/>
+    <n v="0"/>
+    <n v="44.17"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="601.01"/>
+    <n v="24.41"/>
+    <n v="0"/>
+    <n v="37.92"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="810.11"/>
+    <n v="28.1"/>
+    <n v="0"/>
+    <n v="31.91"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="679.04"/>
+    <n v="25.89"/>
+    <n v="0"/>
+    <n v="37.19"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="677.55"/>
+    <n v="25.86"/>
+    <n v="0"/>
+    <n v="35.76"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="714.82"/>
+    <n v="26.52"/>
+    <n v="0"/>
+    <n v="36.619999999999997"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="680.11"/>
+    <n v="25.91"/>
+    <n v="0"/>
+    <n v="40.03"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="630.73"/>
+    <n v="24.99"/>
+    <n v="0"/>
+    <n v="41.1"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="922.28"/>
+    <n v="29.78"/>
+    <n v="0"/>
+    <n v="34.14"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="781.91"/>
+    <n v="27.65"/>
+    <n v="0"/>
+    <n v="32.729999999999997"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="774.51"/>
+    <n v="27.53"/>
+    <n v="0"/>
+    <n v="32.56"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="761.36"/>
+    <n v="27.32"/>
+    <n v="0"/>
+    <n v="40.119999999999997"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="724.99"/>
+    <n v="26.7"/>
+    <n v="0"/>
+    <n v="38.68"/>
+    <n v="107"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="1000000"/>
+    <n v="1000000"/>
+    <n v="699.26"/>
+    <n v="26.25"/>
+    <n v="0"/>
+    <n v="35.130000000000003"/>
+    <n v="107"/>
+  </r>
+  <r>
     <x v="6"/>
     <x v="3"/>
     <x v="3"/>
@@ -2270,8 +2088,517 @@
 </pivotCacheRecords>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="42">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="2231527"/>
+    <n v="139"/>
+    <n v="33.6"/>
+    <n v="-82"/>
+    <n v="29"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="2022745"/>
+    <n v="125"/>
+    <n v="31"/>
+    <n v="-78"/>
+    <n v="32"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1953974"/>
+    <n v="121"/>
+    <n v="30.3"/>
+    <n v="-80"/>
+    <n v="36"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1950713"/>
+    <n v="121"/>
+    <n v="30.2"/>
+    <n v="-79"/>
+    <n v="35"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1891128"/>
+    <n v="115"/>
+    <n v="29.1"/>
+    <n v="-79"/>
+    <n v="34"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1747782"/>
+    <n v="95"/>
+    <n v="25.8"/>
+    <n v="-83"/>
+    <n v="36"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1790802"/>
+    <n v="97"/>
+    <n v="25.4"/>
+    <n v="-79"/>
+    <n v="37"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1728936"/>
+    <n v="93"/>
+    <n v="25.3"/>
+    <n v="-81"/>
+    <n v="34"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1751720"/>
+    <n v="89"/>
+    <n v="24.4"/>
+    <n v="-85"/>
+    <n v="38"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1689613"/>
+    <n v="83"/>
+    <n v="23.1"/>
+    <n v="-82"/>
+    <n v="38"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1746812"/>
+    <n v="78"/>
+    <n v="21.9"/>
+    <n v="-57"/>
+    <n v="20"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1642932"/>
+    <n v="78"/>
+    <n v="21.8"/>
+    <n v="-86"/>
+    <n v="39"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1668177"/>
+    <n v="76"/>
+    <n v="21.4"/>
+    <n v="-79"/>
+    <n v="35"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1780582"/>
+    <n v="76"/>
+    <n v="21.4"/>
+    <n v="-61"/>
+    <n v="23"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1777905"/>
+    <n v="75"/>
+    <n v="21.2"/>
+    <n v="-76"/>
+    <n v="34"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1662345"/>
+    <n v="75"/>
+    <n v="21.1"/>
+    <n v="-53"/>
+    <n v="20"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1657997"/>
+    <n v="74"/>
+    <n v="20.8"/>
+    <n v="-51"/>
+    <n v="20"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1665750"/>
+    <n v="73"/>
+    <n v="20.6"/>
+    <n v="-58"/>
+    <n v="23"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1828960"/>
+    <n v="75"/>
+    <n v="20.5"/>
+    <n v="-75"/>
+    <n v="41"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1735060"/>
+    <n v="72"/>
+    <n v="20.5"/>
+    <n v="-66"/>
+    <n v="25"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1733686"/>
+    <n v="72"/>
+    <n v="20.5"/>
+    <n v="-59"/>
+    <n v="22"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1775830"/>
+    <n v="75"/>
+    <n v="20.399999999999999"/>
+    <n v="-75"/>
+    <n v="41"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1647041"/>
+    <n v="71"/>
+    <n v="20.3"/>
+    <n v="-55"/>
+    <n v="20"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1887234"/>
+    <n v="70"/>
+    <n v="20.100000000000001"/>
+    <n v="-77"/>
+    <n v="38"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1833383"/>
+    <n v="71"/>
+    <n v="20.100000000000001"/>
+    <n v="-79"/>
+    <n v="40"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1709548"/>
+    <n v="70"/>
+    <n v="19.8"/>
+    <n v="-76"/>
+    <n v="37"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1629875"/>
+    <n v="69"/>
+    <n v="19.8"/>
+    <n v="-60"/>
+    <n v="24"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1645005"/>
+    <n v="69"/>
+    <n v="19.600000000000001"/>
+    <n v="-58"/>
+    <n v="25"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1649774"/>
+    <n v="68"/>
+    <n v="19.399999999999999"/>
+    <n v="-77"/>
+    <n v="34"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1692009"/>
+    <n v="68"/>
+    <n v="18.8"/>
+    <n v="-79"/>
+    <n v="37"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1628595"/>
+    <n v="67"/>
+    <n v="18.7"/>
+    <n v="-75"/>
+    <n v="37"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1584052"/>
+    <n v="67"/>
+    <n v="18.7"/>
+    <n v="-75"/>
+    <n v="44"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1578438"/>
+    <n v="66"/>
+    <n v="18.3"/>
+    <n v="-76"/>
+    <n v="37"/>
+    <n v="36"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1620258"/>
+    <n v="62"/>
+    <n v="18"/>
+    <n v="-61"/>
+    <n v="27"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1583611"/>
+    <n v="59"/>
+    <n v="17.100000000000001"/>
+    <n v="-75"/>
+    <n v="32"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1519693"/>
+    <n v="54"/>
+    <n v="15.9"/>
+    <n v="-70"/>
+    <n v="30"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1537945"/>
+    <n v="52"/>
+    <n v="15.6"/>
+    <n v="-70"/>
+    <n v="34"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1512820"/>
+    <n v="52"/>
+    <n v="15.4"/>
+    <n v="-61"/>
+    <n v="28"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1475238"/>
+    <n v="47"/>
+    <n v="14.1"/>
+    <n v="-65"/>
+    <n v="30"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1438131"/>
+    <n v="46"/>
+    <n v="13.8"/>
+    <n v="-63"/>
+    <n v="29"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1448049"/>
+    <n v="44"/>
+    <n v="13.4"/>
+    <n v="-69"/>
+    <n v="36"/>
+    <n v="35"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="1000000"/>
+    <n v="1406798"/>
+    <n v="40"/>
+    <n v="12.1"/>
+    <n v="-70"/>
+    <n v="36"/>
+    <n v="35"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Q3:W15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0">
@@ -2311,13 +2638,7 @@
     <pivotField dataField="1" showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
@@ -2387,7 +2708,7 @@
     <dataField name="Sum of CAGR_%" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <conditionalFormats count="1">
-    <conditionalFormat priority="1">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -2423,11 +2744,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
-  <location ref="Q3:W23" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
+  <location ref="Q3:X24" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="10">
     <pivotField name="No # stock" axis="axisRow" showAll="0">
-      <items count="8">
+      <items count="9">
         <item x="5"/>
         <item x="3"/>
         <item x="1"/>
@@ -2435,24 +2756,27 @@
         <item x="4"/>
         <item x="2"/>
         <item x="6"/>
+        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisCol" showAll="0">
-      <items count="5">
+      <items count="6">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
         <item x="3"/>
+        <item x="4"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField axis="axisRow" outline="0" showAll="0" defaultSubtotal="0">
-      <items count="4">
+      <items count="5">
         <item x="0"/>
         <item x="3"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="4"/>
       </items>
     </pivotField>
     <pivotField showAll="0"/>
@@ -2467,7 +2791,7 @@
     <field x="2"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="19">
+  <rowItems count="20">
     <i>
       <x/>
       <x/>
@@ -2526,6 +2850,10 @@
     <i r="1">
       <x v="5"/>
     </i>
+    <i>
+      <x v="4"/>
+      <x v="7"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2533,7 +2861,7 @@
   <colFields count="1">
     <field x="1"/>
   </colFields>
-  <colItems count="5">
+  <colItems count="6">
     <i>
       <x/>
     </i>
@@ -2546,6 +2874,9 @@
     <i>
       <x v="3"/>
     </i>
+    <i>
+      <x v="4"/>
+    </i>
     <i t="grand">
       <x/>
     </i>
@@ -2554,95 +2885,21 @@
     <dataField name="Year" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="61">
+    <format dxfId="32">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="60">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="59">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="3">
-          <reference field="0" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-          <reference field="1" count="3" selected="0">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="58">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="3">
-          <reference field="0" count="6">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-            <x v="3"/>
-            <x v="4"/>
-            <x v="5"/>
-          </reference>
-          <reference field="1" count="3" selected="0">
-            <x v="0"/>
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-          <reference field="2" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="57">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="1" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="56">
-      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
-    </format>
-    <format dxfId="55">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="1">
-          <reference field="2" count="2">
-            <x v="1"/>
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="54">
-      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
-        <references count="2">
-          <reference field="0" count="0"/>
-          <reference field="2" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </format>
-    <format dxfId="31">
+    <format dxfId="30">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2667,6 +2924,80 @@
     <format dxfId="29">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
+          <reference field="0" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="1" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="2">
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="2">
+          <reference field="0" count="0"/>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="24">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
+          <reference field="0" count="6">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+            <x v="3"/>
+            <x v="4"/>
+            <x v="5"/>
+          </reference>
+          <reference field="1" count="3" selected="0">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="2"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="23">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="3">
           <reference field="0" count="1">
             <x v="6"/>
           </reference>
@@ -2681,7 +3012,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="22">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2703,7 +3034,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="21">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="5">
@@ -2724,7 +3055,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="6">
@@ -2741,7 +3072,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1">
@@ -2753,7 +3084,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="6">
@@ -2788,7 +3119,7 @@
     </format>
   </formats>
   <conditionalFormats count="1">
-    <conditionalFormat priority="2">
+    <conditionalFormat priority="3">
       <pivotAreas count="1">
         <pivotArea type="data" collapsedLevelsAreSubtotals="1" fieldPosition="0">
           <references count="3">
@@ -3111,15 +3442,17 @@
     <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" customWidth="1"/>
     <col min="8" max="8" width="7.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="15.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="15.28515625" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.28515625" customWidth="1"/>
+    <col min="19" max="19" width="5" customWidth="1"/>
+    <col min="20" max="22" width="6" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -3176,16 +3509,16 @@
       <c r="E2" s="1">
         <v>2231527</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="6">
         <v>139</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="6">
         <v>33.6</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="6">
         <v>-82</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="6">
         <v>29</v>
       </c>
       <c r="J2" s="1">
@@ -3208,16 +3541,16 @@
       <c r="E3" s="1">
         <v>2022745</v>
       </c>
-      <c r="F3" s="1">
+      <c r="F3" s="6">
         <v>125</v>
       </c>
-      <c r="G3" s="1">
+      <c r="G3" s="6">
         <v>31</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="6">
         <v>-78</v>
       </c>
-      <c r="I3" s="1">
+      <c r="I3" s="6">
         <v>32</v>
       </c>
       <c r="J3" s="1">
@@ -3246,16 +3579,16 @@
       <c r="E4" s="1">
         <v>1953974</v>
       </c>
-      <c r="F4" s="1">
+      <c r="F4" s="6">
         <v>121</v>
       </c>
-      <c r="G4" s="1">
+      <c r="G4" s="6">
         <v>30.3</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="6">
         <v>-80</v>
       </c>
-      <c r="I4" s="1">
+      <c r="I4" s="6">
         <v>36</v>
       </c>
       <c r="J4" s="1">
@@ -3299,16 +3632,16 @@
       <c r="E5" s="1">
         <v>1950713</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="6">
         <v>121</v>
       </c>
-      <c r="G5" s="1">
+      <c r="G5" s="6">
         <v>30.2</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="6">
         <v>-79</v>
       </c>
-      <c r="I5" s="1">
+      <c r="I5" s="6">
         <v>35</v>
       </c>
       <c r="J5" s="1">
@@ -3352,16 +3685,16 @@
       <c r="E6" s="1">
         <v>1891128</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="6">
         <v>115</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="6">
         <v>29.1</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="6">
         <v>-79</v>
       </c>
-      <c r="I6" s="1">
+      <c r="I6" s="6">
         <v>34</v>
       </c>
       <c r="J6" s="1">
@@ -3401,16 +3734,16 @@
       <c r="E7" s="1">
         <v>1747782</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="6">
         <v>95</v>
       </c>
-      <c r="G7" s="1">
+      <c r="G7" s="6">
         <v>25.8</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="6">
         <v>-83</v>
       </c>
-      <c r="I7" s="1">
+      <c r="I7" s="6">
         <v>36</v>
       </c>
       <c r="J7" s="1">
@@ -3450,16 +3783,16 @@
       <c r="E8" s="1">
         <v>1790802</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="6">
         <v>97</v>
       </c>
-      <c r="G8" s="1">
+      <c r="G8" s="6">
         <v>25.4</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="6">
         <v>-79</v>
       </c>
-      <c r="I8" s="1">
+      <c r="I8" s="6">
         <v>37</v>
       </c>
       <c r="J8" s="1">
@@ -3499,16 +3832,16 @@
       <c r="E9" s="1">
         <v>1728936</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="6">
         <v>93</v>
       </c>
-      <c r="G9" s="1">
+      <c r="G9" s="6">
         <v>25.3</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="6">
         <v>-81</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="6">
         <v>34</v>
       </c>
       <c r="J9" s="1">
@@ -3548,16 +3881,16 @@
       <c r="E10" s="1">
         <v>1751720</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="6">
         <v>89</v>
       </c>
-      <c r="G10" s="1">
+      <c r="G10" s="6">
         <v>24.4</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="6">
         <v>-85</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="6">
         <v>38</v>
       </c>
       <c r="J10" s="1">
@@ -3601,16 +3934,16 @@
       <c r="E11" s="1">
         <v>1689613</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="6">
         <v>83</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="6">
         <v>23.1</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="6">
         <v>-82</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="6">
         <v>38</v>
       </c>
       <c r="J11" s="1">
@@ -3654,16 +3987,16 @@
       <c r="E12" s="1">
         <v>1746812</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="6">
         <v>78</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="6">
         <v>21.9</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="6">
         <v>-57</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="6">
         <v>20</v>
       </c>
       <c r="J12" s="1">
@@ -3707,16 +4040,16 @@
       <c r="E13" s="1">
         <v>1642932</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="6">
         <v>78</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="6">
         <v>21.8</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="6">
         <v>-86</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="6">
         <v>39</v>
       </c>
       <c r="J13" s="1">
@@ -3760,16 +4093,16 @@
       <c r="E14" s="1">
         <v>1668177</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="6">
         <v>76</v>
       </c>
-      <c r="G14" s="1">
+      <c r="G14" s="6">
         <v>21.4</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="6">
         <v>-79</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="6">
         <v>35</v>
       </c>
       <c r="J14" s="1">
@@ -3813,16 +4146,16 @@
       <c r="E15" s="1">
         <v>1780582</v>
       </c>
-      <c r="F15" s="1">
+      <c r="F15" s="6">
         <v>76</v>
       </c>
-      <c r="G15" s="1">
+      <c r="G15" s="6">
         <v>21.4</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="6">
         <v>-61</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="6">
         <v>23</v>
       </c>
       <c r="J15" s="1">
@@ -3866,16 +4199,16 @@
       <c r="E16" s="1">
         <v>1777905</v>
       </c>
-      <c r="F16" s="1">
+      <c r="F16" s="6">
         <v>75</v>
       </c>
-      <c r="G16" s="1">
+      <c r="G16" s="6">
         <v>21.2</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="6">
         <v>-76</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="6">
         <v>34</v>
       </c>
       <c r="J16" s="1">
@@ -3898,16 +4231,16 @@
       <c r="E17" s="1">
         <v>1662345</v>
       </c>
-      <c r="F17" s="1">
+      <c r="F17" s="6">
         <v>75</v>
       </c>
-      <c r="G17" s="1">
+      <c r="G17" s="6">
         <v>21.1</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="6">
         <v>-53</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="6">
         <v>20</v>
       </c>
       <c r="J17" s="1">
@@ -3930,16 +4263,16 @@
       <c r="E18" s="1">
         <v>1657997</v>
       </c>
-      <c r="F18" s="1">
+      <c r="F18" s="6">
         <v>74</v>
       </c>
-      <c r="G18" s="1">
+      <c r="G18" s="6">
         <v>20.8</v>
       </c>
-      <c r="H18" s="1">
+      <c r="H18" s="6">
         <v>-51</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="6">
         <v>20</v>
       </c>
       <c r="J18" s="1">
@@ -3962,16 +4295,16 @@
       <c r="E19" s="1">
         <v>1665750</v>
       </c>
-      <c r="F19" s="1">
+      <c r="F19" s="6">
         <v>73</v>
       </c>
-      <c r="G19" s="1">
+      <c r="G19" s="6">
         <v>20.6</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H19" s="6">
         <v>-58</v>
       </c>
-      <c r="I19" s="1">
+      <c r="I19" s="6">
         <v>23</v>
       </c>
       <c r="J19" s="1">
@@ -3994,16 +4327,16 @@
       <c r="E20" s="1">
         <v>1828960</v>
       </c>
-      <c r="F20" s="1">
+      <c r="F20" s="6">
         <v>75</v>
       </c>
-      <c r="G20" s="1">
+      <c r="G20" s="6">
         <v>20.5</v>
       </c>
-      <c r="H20" s="1">
+      <c r="H20" s="6">
         <v>-75</v>
       </c>
-      <c r="I20" s="1">
+      <c r="I20" s="6">
         <v>41</v>
       </c>
       <c r="J20" s="1">
@@ -4026,16 +4359,16 @@
       <c r="E21" s="1">
         <v>1735060</v>
       </c>
-      <c r="F21" s="1">
+      <c r="F21" s="6">
         <v>72</v>
       </c>
-      <c r="G21" s="1">
+      <c r="G21" s="6">
         <v>20.5</v>
       </c>
-      <c r="H21" s="1">
+      <c r="H21" s="6">
         <v>-66</v>
       </c>
-      <c r="I21" s="1">
+      <c r="I21" s="6">
         <v>25</v>
       </c>
       <c r="J21" s="1">
@@ -4058,16 +4391,16 @@
       <c r="E22" s="1">
         <v>1733686</v>
       </c>
-      <c r="F22" s="1">
+      <c r="F22" s="6">
         <v>72</v>
       </c>
-      <c r="G22" s="1">
+      <c r="G22" s="6">
         <v>20.5</v>
       </c>
-      <c r="H22" s="1">
+      <c r="H22" s="6">
         <v>-59</v>
       </c>
-      <c r="I22" s="1">
+      <c r="I22" s="6">
         <v>22</v>
       </c>
       <c r="J22" s="1">
@@ -4090,16 +4423,16 @@
       <c r="E23" s="1">
         <v>1775830</v>
       </c>
-      <c r="F23" s="1">
+      <c r="F23" s="6">
         <v>75</v>
       </c>
-      <c r="G23" s="1">
+      <c r="G23" s="6">
         <v>20.399999999999999</v>
       </c>
-      <c r="H23" s="1">
+      <c r="H23" s="6">
         <v>-75</v>
       </c>
-      <c r="I23" s="1">
+      <c r="I23" s="6">
         <v>41</v>
       </c>
       <c r="J23" s="1">
@@ -4122,16 +4455,16 @@
       <c r="E24" s="1">
         <v>1647041</v>
       </c>
-      <c r="F24" s="1">
+      <c r="F24" s="6">
         <v>71</v>
       </c>
-      <c r="G24" s="1">
+      <c r="G24" s="6">
         <v>20.3</v>
       </c>
-      <c r="H24" s="1">
+      <c r="H24" s="6">
         <v>-55</v>
       </c>
-      <c r="I24" s="1">
+      <c r="I24" s="6">
         <v>20</v>
       </c>
       <c r="J24" s="1">
@@ -4154,16 +4487,16 @@
       <c r="E25" s="1">
         <v>1887234</v>
       </c>
-      <c r="F25" s="1">
+      <c r="F25" s="6">
         <v>70</v>
       </c>
-      <c r="G25" s="1">
+      <c r="G25" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="H25" s="1">
+      <c r="H25" s="6">
         <v>-77</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="6">
         <v>38</v>
       </c>
       <c r="J25" s="1">
@@ -4186,16 +4519,16 @@
       <c r="E26" s="1">
         <v>1833383</v>
       </c>
-      <c r="F26" s="1">
+      <c r="F26" s="6">
         <v>71</v>
       </c>
-      <c r="G26" s="1">
+      <c r="G26" s="6">
         <v>20.100000000000001</v>
       </c>
-      <c r="H26" s="1">
+      <c r="H26" s="6">
         <v>-79</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="6">
         <v>40</v>
       </c>
       <c r="J26" s="1">
@@ -4218,16 +4551,16 @@
       <c r="E27" s="1">
         <v>1709548</v>
       </c>
-      <c r="F27" s="1">
+      <c r="F27" s="6">
         <v>70</v>
       </c>
-      <c r="G27" s="1">
+      <c r="G27" s="6">
         <v>19.8</v>
       </c>
-      <c r="H27" s="1">
+      <c r="H27" s="6">
         <v>-76</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="6">
         <v>37</v>
       </c>
       <c r="J27" s="1">
@@ -4250,16 +4583,16 @@
       <c r="E28" s="1">
         <v>1629875</v>
       </c>
-      <c r="F28" s="1">
+      <c r="F28" s="6">
         <v>69</v>
       </c>
-      <c r="G28" s="1">
+      <c r="G28" s="6">
         <v>19.8</v>
       </c>
-      <c r="H28" s="1">
+      <c r="H28" s="6">
         <v>-60</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="6">
         <v>24</v>
       </c>
       <c r="J28" s="1">
@@ -4282,16 +4615,16 @@
       <c r="E29" s="1">
         <v>1645005</v>
       </c>
-      <c r="F29" s="1">
+      <c r="F29" s="6">
         <v>69</v>
       </c>
-      <c r="G29" s="1">
+      <c r="G29" s="6">
         <v>19.600000000000001</v>
       </c>
-      <c r="H29" s="1">
+      <c r="H29" s="6">
         <v>-58</v>
       </c>
-      <c r="I29" s="1">
+      <c r="I29" s="6">
         <v>25</v>
       </c>
       <c r="J29" s="1">
@@ -4314,16 +4647,16 @@
       <c r="E30" s="1">
         <v>1649774</v>
       </c>
-      <c r="F30" s="1">
+      <c r="F30" s="6">
         <v>68</v>
       </c>
-      <c r="G30" s="1">
+      <c r="G30" s="6">
         <v>19.399999999999999</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30" s="6">
         <v>-77</v>
       </c>
-      <c r="I30" s="1">
+      <c r="I30" s="6">
         <v>34</v>
       </c>
       <c r="J30" s="1">
@@ -4346,16 +4679,16 @@
       <c r="E31" s="1">
         <v>1692009</v>
       </c>
-      <c r="F31" s="1">
+      <c r="F31" s="6">
         <v>68</v>
       </c>
-      <c r="G31" s="1">
+      <c r="G31" s="6">
         <v>18.8</v>
       </c>
-      <c r="H31" s="1">
+      <c r="H31" s="6">
         <v>-79</v>
       </c>
-      <c r="I31" s="1">
+      <c r="I31" s="6">
         <v>37</v>
       </c>
       <c r="J31" s="1">
@@ -4378,16 +4711,16 @@
       <c r="E32" s="1">
         <v>1628595</v>
       </c>
-      <c r="F32" s="1">
+      <c r="F32" s="6">
         <v>67</v>
       </c>
-      <c r="G32" s="1">
+      <c r="G32" s="6">
         <v>18.7</v>
       </c>
-      <c r="H32" s="1">
+      <c r="H32" s="6">
         <v>-75</v>
       </c>
-      <c r="I32" s="1">
+      <c r="I32" s="6">
         <v>37</v>
       </c>
       <c r="J32" s="1">
@@ -4410,16 +4743,16 @@
       <c r="E33" s="1">
         <v>1584052</v>
       </c>
-      <c r="F33" s="1">
+      <c r="F33" s="6">
         <v>67</v>
       </c>
-      <c r="G33" s="1">
+      <c r="G33" s="6">
         <v>18.7</v>
       </c>
-      <c r="H33" s="1">
+      <c r="H33" s="6">
         <v>-75</v>
       </c>
-      <c r="I33" s="1">
+      <c r="I33" s="6">
         <v>44</v>
       </c>
       <c r="J33" s="1">
@@ -4442,16 +4775,16 @@
       <c r="E34" s="1">
         <v>1578438</v>
       </c>
-      <c r="F34" s="1">
+      <c r="F34" s="6">
         <v>66</v>
       </c>
-      <c r="G34" s="1">
+      <c r="G34" s="6">
         <v>18.3</v>
       </c>
-      <c r="H34" s="1">
+      <c r="H34" s="6">
         <v>-76</v>
       </c>
-      <c r="I34" s="1">
+      <c r="I34" s="6">
         <v>37</v>
       </c>
       <c r="J34" s="1">
@@ -4474,16 +4807,16 @@
       <c r="E35" s="1">
         <v>1620258</v>
       </c>
-      <c r="F35" s="1">
+      <c r="F35" s="6">
         <v>62</v>
       </c>
-      <c r="G35" s="1">
+      <c r="G35" s="6">
         <v>18</v>
       </c>
-      <c r="H35" s="1">
+      <c r="H35" s="6">
         <v>-61</v>
       </c>
-      <c r="I35" s="1">
+      <c r="I35" s="6">
         <v>27</v>
       </c>
       <c r="J35" s="1">
@@ -4506,16 +4839,16 @@
       <c r="E36" s="1">
         <v>1583611</v>
       </c>
-      <c r="F36" s="1">
+      <c r="F36" s="6">
         <v>59</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G36" s="6">
         <v>17.100000000000001</v>
       </c>
-      <c r="H36" s="1">
+      <c r="H36" s="6">
         <v>-75</v>
       </c>
-      <c r="I36" s="1">
+      <c r="I36" s="6">
         <v>32</v>
       </c>
       <c r="J36" s="1">
@@ -4538,16 +4871,16 @@
       <c r="E37" s="1">
         <v>1519693</v>
       </c>
-      <c r="F37" s="1">
+      <c r="F37" s="6">
         <v>54</v>
       </c>
-      <c r="G37" s="1">
+      <c r="G37" s="6">
         <v>15.9</v>
       </c>
-      <c r="H37" s="1">
+      <c r="H37" s="6">
         <v>-70</v>
       </c>
-      <c r="I37" s="1">
+      <c r="I37" s="6">
         <v>30</v>
       </c>
       <c r="J37" s="1">
@@ -4570,16 +4903,16 @@
       <c r="E38" s="1">
         <v>1537945</v>
       </c>
-      <c r="F38" s="1">
+      <c r="F38" s="6">
         <v>52</v>
       </c>
-      <c r="G38" s="1">
+      <c r="G38" s="6">
         <v>15.6</v>
       </c>
-      <c r="H38" s="1">
+      <c r="H38" s="6">
         <v>-70</v>
       </c>
-      <c r="I38" s="1">
+      <c r="I38" s="6">
         <v>34</v>
       </c>
       <c r="J38" s="1">
@@ -4602,16 +4935,16 @@
       <c r="E39" s="1">
         <v>1512820</v>
       </c>
-      <c r="F39" s="1">
+      <c r="F39" s="6">
         <v>52</v>
       </c>
-      <c r="G39" s="1">
+      <c r="G39" s="6">
         <v>15.4</v>
       </c>
-      <c r="H39" s="1">
+      <c r="H39" s="6">
         <v>-61</v>
       </c>
-      <c r="I39" s="1">
+      <c r="I39" s="6">
         <v>28</v>
       </c>
       <c r="J39" s="1">
@@ -4634,16 +4967,16 @@
       <c r="E40" s="1">
         <v>1475238</v>
       </c>
-      <c r="F40" s="1">
+      <c r="F40" s="6">
         <v>47</v>
       </c>
-      <c r="G40" s="1">
+      <c r="G40" s="6">
         <v>14.1</v>
       </c>
-      <c r="H40" s="1">
+      <c r="H40" s="6">
         <v>-65</v>
       </c>
-      <c r="I40" s="1">
+      <c r="I40" s="6">
         <v>30</v>
       </c>
       <c r="J40" s="1">
@@ -4666,16 +4999,16 @@
       <c r="E41" s="1">
         <v>1438131</v>
       </c>
-      <c r="F41" s="1">
+      <c r="F41" s="6">
         <v>46</v>
       </c>
-      <c r="G41" s="1">
+      <c r="G41" s="6">
         <v>13.8</v>
       </c>
-      <c r="H41" s="1">
+      <c r="H41" s="6">
         <v>-63</v>
       </c>
-      <c r="I41" s="1">
+      <c r="I41" s="6">
         <v>29</v>
       </c>
       <c r="J41" s="1">
@@ -4698,16 +5031,16 @@
       <c r="E42" s="1">
         <v>1448049</v>
       </c>
-      <c r="F42" s="1">
+      <c r="F42" s="6">
         <v>44</v>
       </c>
-      <c r="G42" s="1">
+      <c r="G42" s="6">
         <v>13.4</v>
       </c>
-      <c r="H42" s="1">
+      <c r="H42" s="6">
         <v>-69</v>
       </c>
-      <c r="I42" s="1">
+      <c r="I42" s="6">
         <v>36</v>
       </c>
       <c r="J42" s="1">
@@ -4730,16 +5063,16 @@
       <c r="E43" s="1">
         <v>1406798</v>
       </c>
-      <c r="F43" s="1">
+      <c r="F43" s="6">
         <v>40</v>
       </c>
-      <c r="G43" s="1">
+      <c r="G43" s="6">
         <v>12.1</v>
       </c>
-      <c r="H43" s="1">
+      <c r="H43" s="6">
         <v>-70</v>
       </c>
-      <c r="I43" s="1">
+      <c r="I43" s="6">
         <v>36</v>
       </c>
       <c r="J43" s="1">
@@ -4748,6 +5081,30 @@
     </row>
   </sheetData>
   <conditionalFormatting pivot="1" sqref="R5:V14">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:I2">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:I43">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -4765,13 +5122,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:X69"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.5703125" customWidth="1"/>
     <col min="3" max="3" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.28515625" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.85546875" customWidth="1"/>
     <col min="7" max="7" width="8.42578125" bestFit="1" customWidth="1"/>
@@ -4782,12 +5139,13 @@
     <col min="17" max="17" width="11.28515625" customWidth="1"/>
     <col min="18" max="18" width="12.28515625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="11.85546875" customWidth="1"/>
-    <col min="20" max="21" width="7" customWidth="1"/>
+    <col min="20" max="21" width="7.85546875" customWidth="1"/>
     <col min="22" max="22" width="7.28515625" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.7109375" customWidth="1"/>
+    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="55.5" customHeight="1">
+    <row r="1" spans="1:24" ht="30">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4819,7 +5177,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="1">
         <v>20</v>
       </c>
@@ -4851,7 +5209,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="1">
         <v>20</v>
       </c>
@@ -4889,7 +5247,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="1">
         <v>15</v>
       </c>
@@ -4939,10 +5297,13 @@
         <v>18</v>
       </c>
       <c r="W4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="1">
         <v>15</v>
       </c>
@@ -4989,11 +5350,12 @@
         <v>27.1</v>
       </c>
       <c r="V5" s="5"/>
-      <c r="W5" s="5">
+      <c r="W5" s="5"/>
+      <c r="X5" s="5">
         <v>78.91</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="1">
         <v>30</v>
       </c>
@@ -5037,11 +5399,12 @@
         <v>24.72</v>
       </c>
       <c r="V6" s="5"/>
-      <c r="W6" s="5">
+      <c r="W6" s="5"/>
+      <c r="X6" s="5">
         <v>84.72</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="1">
         <v>15</v>
       </c>
@@ -5085,11 +5448,12 @@
         <v>36.200000000000003</v>
       </c>
       <c r="V7" s="5"/>
-      <c r="W7" s="5">
+      <c r="W7" s="5"/>
+      <c r="X7" s="5">
         <v>110.98</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="1">
         <v>20</v>
       </c>
@@ -5133,11 +5497,12 @@
         <v>36.19</v>
       </c>
       <c r="V8" s="5"/>
-      <c r="W8" s="5">
+      <c r="W8" s="5"/>
+      <c r="X8" s="5">
         <v>114.47</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="1">
         <v>10</v>
       </c>
@@ -5181,11 +5546,12 @@
         <v>31.32</v>
       </c>
       <c r="V9" s="5"/>
-      <c r="W9" s="5">
+      <c r="W9" s="5"/>
+      <c r="X9" s="5">
         <v>97.169999999999987</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="1">
         <v>25</v>
       </c>
@@ -5229,11 +5595,12 @@
         <v>31.86</v>
       </c>
       <c r="V10" s="5"/>
-      <c r="W10" s="5">
+      <c r="W10" s="5"/>
+      <c r="X10" s="5">
         <v>100.10000000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="1">
         <v>25</v>
       </c>
@@ -5278,8 +5645,9 @@
       <c r="U11" s="12"/>
       <c r="V11" s="5"/>
       <c r="W11" s="5"/>
-    </row>
-    <row r="12" spans="1:23">
+      <c r="X11" s="5"/>
+    </row>
+    <row r="12" spans="1:24">
       <c r="A12" s="1">
         <v>30</v>
       </c>
@@ -5326,11 +5694,12 @@
         <v>41.05</v>
       </c>
       <c r="V12" s="5"/>
-      <c r="W12" s="5">
+      <c r="W12" s="5"/>
+      <c r="X12" s="5">
         <v>120.33</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="1">
         <v>30</v>
       </c>
@@ -5375,11 +5744,12 @@
         <v>36.979999999999997</v>
       </c>
       <c r="V13" s="5"/>
-      <c r="W13" s="5">
+      <c r="W13" s="5"/>
+      <c r="X13" s="5">
         <v>111.01999999999998</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="1">
         <v>25</v>
       </c>
@@ -5424,11 +5794,12 @@
         <v>41.49</v>
       </c>
       <c r="V14" s="5"/>
-      <c r="W14" s="5">
+      <c r="W14" s="5"/>
+      <c r="X14" s="5">
         <v>128</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="1">
         <v>5</v>
       </c>
@@ -5473,11 +5844,12 @@
         <v>41.16</v>
       </c>
       <c r="V15" s="5"/>
-      <c r="W15" s="5">
+      <c r="W15" s="5"/>
+      <c r="X15" s="5">
         <v>127.19999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -5522,11 +5894,12 @@
         <v>39.44</v>
       </c>
       <c r="V16" s="5"/>
-      <c r="W16" s="5">
+      <c r="W16" s="5"/>
+      <c r="X16" s="5">
         <v>120.31</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="1">
         <v>10</v>
       </c>
@@ -5571,11 +5944,12 @@
         <v>38.51</v>
       </c>
       <c r="V17" s="5"/>
-      <c r="W17" s="5">
+      <c r="W17" s="5"/>
+      <c r="X17" s="5">
         <v>117.49000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="1">
         <v>5</v>
       </c>
@@ -5613,20 +5987,21 @@
         <v>10</v>
       </c>
       <c r="S18" s="12">
-        <v>37.97</v>
+        <v>66.05</v>
       </c>
       <c r="T18" s="12">
-        <v>33.79</v>
+        <v>59.230000000000004</v>
       </c>
       <c r="U18" s="12">
-        <v>35.06</v>
+        <v>59.47</v>
       </c>
       <c r="V18" s="5"/>
-      <c r="W18" s="5">
-        <v>106.82</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="W18" s="5"/>
+      <c r="X18" s="5">
+        <v>184.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24">
       <c r="A19" s="1">
         <v>10</v>
       </c>
@@ -5661,20 +6036,21 @@
         <v>15</v>
       </c>
       <c r="S19" s="12">
-        <v>39.200000000000003</v>
+        <v>67.300000000000011</v>
       </c>
       <c r="T19" s="12">
-        <v>38.049999999999997</v>
+        <v>63.94</v>
       </c>
       <c r="U19" s="12">
-        <v>36.71</v>
+        <v>62.57</v>
       </c>
       <c r="V19" s="5"/>
-      <c r="W19" s="5">
-        <v>113.96000000000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="W19" s="5"/>
+      <c r="X19" s="5">
+        <v>193.81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24">
       <c r="A20" s="1">
         <v>15</v>
       </c>
@@ -5709,20 +6085,21 @@
         <v>20</v>
       </c>
       <c r="S20" s="12">
-        <v>38.03</v>
+        <v>63.94</v>
       </c>
       <c r="T20" s="12">
-        <v>36.630000000000003</v>
+        <v>63.150000000000006</v>
       </c>
       <c r="U20" s="12">
-        <v>34.28</v>
+        <v>59.269999999999996</v>
       </c>
       <c r="V20" s="5"/>
-      <c r="W20" s="5">
-        <v>108.94</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="W20" s="5"/>
+      <c r="X20" s="5">
+        <v>186.36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24">
       <c r="A21" s="1">
         <v>15</v>
       </c>
@@ -5757,20 +6134,21 @@
         <v>25</v>
       </c>
       <c r="S21" s="12">
-        <v>37.76</v>
+        <v>67.539999999999992</v>
       </c>
       <c r="T21" s="12">
-        <v>35.75</v>
+        <v>63.28</v>
       </c>
       <c r="U21" s="12">
-        <v>37.24</v>
+        <v>64.89</v>
       </c>
       <c r="V21" s="5"/>
-      <c r="W21" s="5">
-        <v>110.75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="W21" s="5"/>
+      <c r="X21" s="5">
+        <v>195.70999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -5805,20 +6183,21 @@
         <v>30</v>
       </c>
       <c r="S22" s="12">
-        <v>39.79</v>
+        <v>67.11</v>
       </c>
       <c r="T22" s="12">
-        <v>36.64</v>
+        <v>63.34</v>
       </c>
       <c r="U22" s="12">
-        <v>36.17</v>
+        <v>62.42</v>
       </c>
       <c r="V22" s="5"/>
-      <c r="W22" s="5">
-        <v>112.60000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="W22" s="5"/>
+      <c r="X22" s="5">
+        <v>192.87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24">
       <c r="A23" s="1">
         <v>20</v>
       </c>
@@ -5850,23 +6229,23 @@
         <v>59</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="S23" s="4">
-        <v>644.96</v>
-      </c>
-      <c r="T23" s="4">
-        <v>613.32999999999993</v>
-      </c>
-      <c r="U23" s="4">
-        <v>605.48</v>
-      </c>
-      <c r="V23" s="4"/>
-      <c r="W23" s="4">
-        <v>1863.77</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+        <v>2</v>
+      </c>
+      <c r="R23" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="S23" s="5"/>
+      <c r="T23" s="5"/>
+      <c r="U23" s="5"/>
+      <c r="V23" s="5"/>
+      <c r="W23" s="5">
+        <v>0</v>
+      </c>
+      <c r="X23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24">
       <c r="A24" s="1">
         <v>5</v>
       </c>
@@ -5897,8 +6276,27 @@
       <c r="J24" s="1">
         <v>59</v>
       </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="Q24" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24" s="4">
+        <v>784.15</v>
+      </c>
+      <c r="T24" s="4">
+        <v>745.40999999999985</v>
+      </c>
+      <c r="U24" s="4">
+        <v>734.64</v>
+      </c>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4">
+        <v>0</v>
+      </c>
+      <c r="X24" s="4">
+        <v>2264.1999999999998</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24">
       <c r="A25" s="1">
         <v>15</v>
       </c>
@@ -5930,7 +6328,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="1">
         <v>30</v>
       </c>
@@ -5962,7 +6360,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:24">
       <c r="A27" s="1">
         <v>20</v>
       </c>
@@ -5994,7 +6392,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="1">
         <v>5</v>
       </c>
@@ -6026,7 +6424,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:24">
       <c r="A29" s="1">
         <v>25</v>
       </c>
@@ -6058,7 +6456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:24">
       <c r="A30" s="1">
         <v>25</v>
       </c>
@@ -6090,7 +6488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="1">
         <v>10</v>
       </c>
@@ -6122,7 +6520,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="1">
         <v>25</v>
       </c>
@@ -6794,8 +7192,535 @@
         <v>107</v>
       </c>
     </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J54" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="1">
+        <v>10</v>
+      </c>
+      <c r="B55" s="1">
+        <v>60</v>
+      </c>
+      <c r="C55" s="1">
+        <v>10</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E55" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F55" s="1">
+        <v>808.46</v>
+      </c>
+      <c r="G55" s="6">
+        <v>28.08</v>
+      </c>
+      <c r="H55" s="6">
+        <v>0</v>
+      </c>
+      <c r="I55" s="6">
+        <v>34.69</v>
+      </c>
+      <c r="J55" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="1">
+        <v>10</v>
+      </c>
+      <c r="B56" s="1">
+        <v>70</v>
+      </c>
+      <c r="C56" s="1">
+        <v>10</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E56" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F56" s="1">
+        <v>654.41</v>
+      </c>
+      <c r="G56" s="6">
+        <v>25.44</v>
+      </c>
+      <c r="H56" s="6">
+        <v>0</v>
+      </c>
+      <c r="I56" s="6">
+        <v>44.17</v>
+      </c>
+      <c r="J56" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="1">
+        <v>10</v>
+      </c>
+      <c r="B57" s="1">
+        <v>80</v>
+      </c>
+      <c r="C57" s="1">
+        <v>10</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E57" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F57" s="1">
+        <v>601.01</v>
+      </c>
+      <c r="G57" s="6">
+        <v>24.41</v>
+      </c>
+      <c r="H57" s="6">
+        <v>0</v>
+      </c>
+      <c r="I57" s="6">
+        <v>37.92</v>
+      </c>
+      <c r="J57" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="1">
+        <v>15</v>
+      </c>
+      <c r="B58" s="1">
+        <v>60</v>
+      </c>
+      <c r="C58" s="1">
+        <v>10</v>
+      </c>
+      <c r="D58" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E58" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F58" s="1">
+        <v>810.11</v>
+      </c>
+      <c r="G58" s="6">
+        <v>28.1</v>
+      </c>
+      <c r="H58" s="6">
+        <v>0</v>
+      </c>
+      <c r="I58" s="6">
+        <v>31.91</v>
+      </c>
+      <c r="J58" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="1">
+        <v>15</v>
+      </c>
+      <c r="B59" s="1">
+        <v>70</v>
+      </c>
+      <c r="C59" s="1">
+        <v>10</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E59" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F59" s="1">
+        <v>679.04</v>
+      </c>
+      <c r="G59" s="6">
+        <v>25.89</v>
+      </c>
+      <c r="H59" s="6">
+        <v>0</v>
+      </c>
+      <c r="I59" s="6">
+        <v>37.19</v>
+      </c>
+      <c r="J59" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="1">
+        <v>15</v>
+      </c>
+      <c r="B60" s="1">
+        <v>80</v>
+      </c>
+      <c r="C60" s="1">
+        <v>10</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E60" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F60" s="1">
+        <v>677.55</v>
+      </c>
+      <c r="G60" s="6">
+        <v>25.86</v>
+      </c>
+      <c r="H60" s="6">
+        <v>0</v>
+      </c>
+      <c r="I60" s="6">
+        <v>35.76</v>
+      </c>
+      <c r="J60" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="1">
+        <v>20</v>
+      </c>
+      <c r="B61" s="1">
+        <v>70</v>
+      </c>
+      <c r="C61" s="1">
+        <v>10</v>
+      </c>
+      <c r="D61" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E61" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F61" s="1">
+        <v>714.82</v>
+      </c>
+      <c r="G61" s="6">
+        <v>26.52</v>
+      </c>
+      <c r="H61" s="6">
+        <v>0</v>
+      </c>
+      <c r="I61" s="6">
+        <v>36.619999999999997</v>
+      </c>
+      <c r="J61" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="1">
+        <v>20</v>
+      </c>
+      <c r="B62" s="1">
+        <v>60</v>
+      </c>
+      <c r="C62" s="1">
+        <v>10</v>
+      </c>
+      <c r="D62" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E62" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F62" s="1">
+        <v>680.11</v>
+      </c>
+      <c r="G62" s="6">
+        <v>25.91</v>
+      </c>
+      <c r="H62" s="6">
+        <v>0</v>
+      </c>
+      <c r="I62" s="6">
+        <v>40.03</v>
+      </c>
+      <c r="J62" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="1">
+        <v>20</v>
+      </c>
+      <c r="B63" s="1">
+        <v>80</v>
+      </c>
+      <c r="C63" s="1">
+        <v>10</v>
+      </c>
+      <c r="D63" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E63" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F63" s="1">
+        <v>630.73</v>
+      </c>
+      <c r="G63" s="6">
+        <v>24.99</v>
+      </c>
+      <c r="H63" s="6">
+        <v>0</v>
+      </c>
+      <c r="I63" s="6">
+        <v>41.1</v>
+      </c>
+      <c r="J63" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="1">
+        <v>25</v>
+      </c>
+      <c r="B64" s="1">
+        <v>60</v>
+      </c>
+      <c r="C64" s="1">
+        <v>10</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E64" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F64" s="1">
+        <v>922.28</v>
+      </c>
+      <c r="G64" s="6">
+        <v>29.78</v>
+      </c>
+      <c r="H64" s="6">
+        <v>0</v>
+      </c>
+      <c r="I64" s="6">
+        <v>34.14</v>
+      </c>
+      <c r="J64" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10">
+      <c r="A65" s="1">
+        <v>25</v>
+      </c>
+      <c r="B65" s="1">
+        <v>80</v>
+      </c>
+      <c r="C65" s="1">
+        <v>10</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E65" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F65" s="1">
+        <v>781.91</v>
+      </c>
+      <c r="G65" s="6">
+        <v>27.65</v>
+      </c>
+      <c r="H65" s="6">
+        <v>0</v>
+      </c>
+      <c r="I65" s="6">
+        <v>32.729999999999997</v>
+      </c>
+      <c r="J65" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10">
+      <c r="A66" s="1">
+        <v>25</v>
+      </c>
+      <c r="B66" s="1">
+        <v>70</v>
+      </c>
+      <c r="C66" s="1">
+        <v>10</v>
+      </c>
+      <c r="D66" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E66" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F66" s="1">
+        <v>774.51</v>
+      </c>
+      <c r="G66" s="6">
+        <v>27.53</v>
+      </c>
+      <c r="H66" s="6">
+        <v>0</v>
+      </c>
+      <c r="I66" s="6">
+        <v>32.56</v>
+      </c>
+      <c r="J66" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:10">
+      <c r="A67" s="1">
+        <v>30</v>
+      </c>
+      <c r="B67" s="1">
+        <v>60</v>
+      </c>
+      <c r="C67" s="1">
+        <v>10</v>
+      </c>
+      <c r="D67" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E67" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F67" s="1">
+        <v>761.36</v>
+      </c>
+      <c r="G67" s="6">
+        <v>27.32</v>
+      </c>
+      <c r="H67" s="6">
+        <v>0</v>
+      </c>
+      <c r="I67" s="6">
+        <v>40.119999999999997</v>
+      </c>
+      <c r="J67" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10">
+      <c r="A68" s="1">
+        <v>30</v>
+      </c>
+      <c r="B68" s="1">
+        <v>70</v>
+      </c>
+      <c r="C68" s="1">
+        <v>10</v>
+      </c>
+      <c r="D68" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E68" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F68" s="1">
+        <v>724.99</v>
+      </c>
+      <c r="G68" s="6">
+        <v>26.7</v>
+      </c>
+      <c r="H68" s="6">
+        <v>0</v>
+      </c>
+      <c r="I68" s="6">
+        <v>38.68</v>
+      </c>
+      <c r="J68" s="1">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10">
+      <c r="A69" s="1">
+        <v>30</v>
+      </c>
+      <c r="B69" s="1">
+        <v>80</v>
+      </c>
+      <c r="C69" s="1">
+        <v>10</v>
+      </c>
+      <c r="D69" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="E69" s="1">
+        <v>1000000</v>
+      </c>
+      <c r="F69" s="1">
+        <v>699.26</v>
+      </c>
+      <c r="G69" s="6">
+        <v>26.25</v>
+      </c>
+      <c r="H69" s="6">
+        <v>0</v>
+      </c>
+      <c r="I69" s="6">
+        <v>35.130000000000003</v>
+      </c>
+      <c r="J69" s="1">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState ref="A55:J69">
+    <sortCondition ref="A55"/>
+  </sortState>
   <conditionalFormatting pivot="1" sqref="S5:U10 S12:U22">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G2:I52">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -6807,7 +7732,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:I52">
+  <conditionalFormatting sqref="G55:I69">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min" val="0"/>
@@ -6822,4 +7747,2648 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P99"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="7" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" style="7" customWidth="1"/>
+    <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="45">
+      <c r="A1" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="G1" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J1" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K1" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="10">
+        <v>95.6</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="H2" s="10">
+        <v>2007</v>
+      </c>
+      <c r="I2" s="10">
+        <v>1333.97</v>
+      </c>
+      <c r="J2" s="10">
+        <v>50.45</v>
+      </c>
+      <c r="K2" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L2" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N2" t="s">
+        <v>60</v>
+      </c>
+      <c r="P2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="10">
+        <v>94.4</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="10">
+        <v>96</v>
+      </c>
+      <c r="H3" s="10">
+        <v>2265.6</v>
+      </c>
+      <c r="I3" s="10">
+        <v>1635.97</v>
+      </c>
+      <c r="J3" s="10">
+        <v>38.49</v>
+      </c>
+      <c r="K3" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L3" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="10">
+        <v>94.2</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="10">
+        <v>95.2</v>
+      </c>
+      <c r="H4" s="10">
+        <v>2835.1</v>
+      </c>
+      <c r="I4" s="10">
+        <v>2095.15</v>
+      </c>
+      <c r="J4" s="10">
+        <v>35.32</v>
+      </c>
+      <c r="K4" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L4" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="10">
+        <v>91.4</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10">
+        <v>87.2</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1952.3</v>
+      </c>
+      <c r="I5" s="10">
+        <v>1577.25</v>
+      </c>
+      <c r="J5" s="10">
+        <v>23.78</v>
+      </c>
+      <c r="K5" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L5" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="10">
+        <v>97.7</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1460.9</v>
+      </c>
+      <c r="I6" s="10">
+        <v>977.88</v>
+      </c>
+      <c r="J6" s="10">
+        <v>49.4</v>
+      </c>
+      <c r="K6" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="L6" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>824.5</v>
+      </c>
+      <c r="I7" s="10">
+        <v>604.44000000000005</v>
+      </c>
+      <c r="J7" s="10">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="K7" s="10">
+        <v>56.8</v>
+      </c>
+      <c r="L7" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="10">
+        <v>90.5</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="10">
+        <v>84.8</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1495.4</v>
+      </c>
+      <c r="I8" s="10">
+        <v>1230.3800000000001</v>
+      </c>
+      <c r="J8" s="10">
+        <v>21.54</v>
+      </c>
+      <c r="K8" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L8" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="10">
+        <v>90.4</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="10">
+        <v>84.4</v>
+      </c>
+      <c r="H9" s="10">
+        <v>3547.8</v>
+      </c>
+      <c r="I9" s="10">
+        <v>3060.4</v>
+      </c>
+      <c r="J9" s="10">
+        <v>15.93</v>
+      </c>
+      <c r="K9" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L9" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="10">
+        <v>88.9</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="10">
+        <v>92.6</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1278.5</v>
+      </c>
+      <c r="I10" s="10">
+        <v>966</v>
+      </c>
+      <c r="J10" s="10">
+        <v>32.35</v>
+      </c>
+      <c r="K10" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="L10" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N10" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="10">
+        <v>88.8</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="10">
+        <v>92.4</v>
+      </c>
+      <c r="H11" s="10">
+        <v>820.7</v>
+      </c>
+      <c r="I11" s="10">
+        <v>670.49</v>
+      </c>
+      <c r="J11" s="10">
+        <v>22.4</v>
+      </c>
+      <c r="K11" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="L11" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N11" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="10">
+        <v>88.7</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="10">
+        <v>79.599999999999994</v>
+      </c>
+      <c r="H12" s="10">
+        <v>1203.9000000000001</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1005.37</v>
+      </c>
+      <c r="J12" s="10">
+        <v>19.75</v>
+      </c>
+      <c r="K12" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L12" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N12" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="10">
+        <v>88.1</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="10">
+        <v>98.9</v>
+      </c>
+      <c r="H13" s="10">
+        <v>224.68</v>
+      </c>
+      <c r="I13" s="10">
+        <v>147.49</v>
+      </c>
+      <c r="J13" s="10">
+        <v>52.34</v>
+      </c>
+      <c r="K13" s="10">
+        <v>80</v>
+      </c>
+      <c r="L13" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D14" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="10">
+        <v>96.4</v>
+      </c>
+      <c r="H14" s="10">
+        <v>9619.5</v>
+      </c>
+      <c r="I14" s="10">
+        <v>6957.95</v>
+      </c>
+      <c r="J14" s="10">
+        <v>38.25</v>
+      </c>
+      <c r="K14" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L14" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D15" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G15" s="10">
+        <v>87.8</v>
+      </c>
+      <c r="H15" s="10">
+        <v>1386.7</v>
+      </c>
+      <c r="I15" s="10">
+        <v>1115.5999999999999</v>
+      </c>
+      <c r="J15" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="K15" s="10">
+        <v>56.8</v>
+      </c>
+      <c r="L15" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" s="10">
+        <v>93.9</v>
+      </c>
+      <c r="H16" s="10">
+        <v>8584.5</v>
+      </c>
+      <c r="I16" s="10">
+        <v>6950.34</v>
+      </c>
+      <c r="J16" s="10">
+        <v>23.51</v>
+      </c>
+      <c r="K16" s="10">
+        <v>42.3</v>
+      </c>
+      <c r="L16" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N16" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="10">
+        <v>94.1</v>
+      </c>
+      <c r="H17" s="10">
+        <v>1513.6</v>
+      </c>
+      <c r="I17" s="10">
+        <v>1185.1199999999999</v>
+      </c>
+      <c r="J17" s="10">
+        <v>27.72</v>
+      </c>
+      <c r="K17" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L17" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="10">
+        <v>86.2</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="10">
+        <v>72.400000000000006</v>
+      </c>
+      <c r="H18" s="10">
+        <v>1071.95</v>
+      </c>
+      <c r="I18" s="10">
+        <v>957.54</v>
+      </c>
+      <c r="J18" s="10">
+        <v>11.95</v>
+      </c>
+      <c r="K18" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L18" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="10">
+        <v>85.7</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="10">
+        <v>91.2</v>
+      </c>
+      <c r="H19" s="10">
+        <v>3002.6</v>
+      </c>
+      <c r="I19" s="10">
+        <v>2389.2399999999998</v>
+      </c>
+      <c r="J19" s="10">
+        <v>25.67</v>
+      </c>
+      <c r="K19" s="10">
+        <v>44</v>
+      </c>
+      <c r="L19" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N19" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="10">
+        <v>85.1</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G20" s="10">
+        <v>69.3</v>
+      </c>
+      <c r="H20" s="10">
+        <v>8889</v>
+      </c>
+      <c r="I20" s="10">
+        <v>7983.94</v>
+      </c>
+      <c r="J20" s="10">
+        <v>11.34</v>
+      </c>
+      <c r="K20" s="10">
+        <v>79.2</v>
+      </c>
+      <c r="L20" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="10">
+        <v>84.7</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="10">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="H21" s="10">
+        <v>2091.6</v>
+      </c>
+      <c r="I21" s="10">
+        <v>1730.71</v>
+      </c>
+      <c r="J21" s="10">
+        <v>20.85</v>
+      </c>
+      <c r="K21" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="L21" s="14">
+        <v>46290</v>
+      </c>
+      <c r="N21" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" ht="45">
+      <c r="A27" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G27" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="H27" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="I27" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="J27" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="K27" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="L27" s="18" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
+      <c r="A28" s="1">
+        <v>1</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D28" s="10">
+        <v>95.6</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="H28" s="10">
+        <v>2007</v>
+      </c>
+      <c r="I28" s="10">
+        <v>1333.45</v>
+      </c>
+      <c r="J28" s="10">
+        <v>50.51</v>
+      </c>
+      <c r="K28" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L28" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
+      <c r="A29" s="1">
+        <v>2</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="10">
+        <v>94.4</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="10">
+        <v>96</v>
+      </c>
+      <c r="H29" s="10">
+        <v>2265.6</v>
+      </c>
+      <c r="I29" s="10">
+        <v>1635.97</v>
+      </c>
+      <c r="J29" s="10">
+        <v>38.49</v>
+      </c>
+      <c r="K29" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L29" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
+      <c r="A30" s="1">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="10">
+        <v>94.2</v>
+      </c>
+      <c r="E30" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="10">
+        <v>95.2</v>
+      </c>
+      <c r="H30" s="10">
+        <v>2835.1</v>
+      </c>
+      <c r="I30" s="10">
+        <v>2095.15</v>
+      </c>
+      <c r="J30" s="10">
+        <v>35.32</v>
+      </c>
+      <c r="K30" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L30" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
+      <c r="A31" s="1">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="10">
+        <v>91.4</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="10">
+        <v>87.2</v>
+      </c>
+      <c r="H31" s="10">
+        <v>1952.3</v>
+      </c>
+      <c r="I31" s="10">
+        <v>1577.25</v>
+      </c>
+      <c r="J31" s="10">
+        <v>23.78</v>
+      </c>
+      <c r="K31" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L31" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
+      <c r="A32" s="1">
+        <v>5</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D32" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E32" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="10">
+        <v>97.7</v>
+      </c>
+      <c r="H32" s="10">
+        <v>1460.9</v>
+      </c>
+      <c r="I32" s="10">
+        <v>977.88</v>
+      </c>
+      <c r="J32" s="10">
+        <v>49.4</v>
+      </c>
+      <c r="K32" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L32" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="1">
+        <v>6</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E33" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H33" s="10">
+        <v>824.5</v>
+      </c>
+      <c r="I33" s="10">
+        <v>604.44000000000005</v>
+      </c>
+      <c r="J33" s="10">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="K33" s="1">
+        <v>56.8</v>
+      </c>
+      <c r="L33" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="1">
+        <v>7</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="10">
+        <v>90.5</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="10">
+        <v>84.6</v>
+      </c>
+      <c r="H34" s="10">
+        <v>1495.4</v>
+      </c>
+      <c r="I34" s="10">
+        <v>1230.3800000000001</v>
+      </c>
+      <c r="J34" s="10">
+        <v>21.54</v>
+      </c>
+      <c r="K34" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L34" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="1">
+        <v>8</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="10">
+        <v>90.3</v>
+      </c>
+      <c r="E35" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="10">
+        <v>84.2</v>
+      </c>
+      <c r="H35" s="10">
+        <v>3547.8</v>
+      </c>
+      <c r="I35" s="10">
+        <v>3061.42</v>
+      </c>
+      <c r="J35" s="10">
+        <v>15.89</v>
+      </c>
+      <c r="K35" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L35" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="1">
+        <v>9</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="10">
+        <v>89</v>
+      </c>
+      <c r="E36" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G36" s="10">
+        <v>92.8</v>
+      </c>
+      <c r="H36" s="10">
+        <v>820.7</v>
+      </c>
+      <c r="I36" s="10">
+        <v>665.21</v>
+      </c>
+      <c r="J36" s="10">
+        <v>23.37</v>
+      </c>
+      <c r="K36" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L36" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="1">
+        <v>10</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="10">
+        <v>88.8</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="10">
+        <v>92.4</v>
+      </c>
+      <c r="H37" s="10">
+        <v>1278.5</v>
+      </c>
+      <c r="I37" s="10">
+        <v>966</v>
+      </c>
+      <c r="J37" s="10">
+        <v>32.35</v>
+      </c>
+      <c r="K37" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L37" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="1">
+        <v>11</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D38" s="10">
+        <v>88.8</v>
+      </c>
+      <c r="E38" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G38" s="10">
+        <v>79.8</v>
+      </c>
+      <c r="H38" s="10">
+        <v>1203.9000000000001</v>
+      </c>
+      <c r="I38" s="10">
+        <v>1005.37</v>
+      </c>
+      <c r="J38" s="10">
+        <v>19.75</v>
+      </c>
+      <c r="K38" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L38" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="1">
+        <v>12</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="10">
+        <v>88.1</v>
+      </c>
+      <c r="E39" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="10">
+        <v>98.9</v>
+      </c>
+      <c r="H39" s="10">
+        <v>224.68</v>
+      </c>
+      <c r="I39" s="10">
+        <v>147.49</v>
+      </c>
+      <c r="J39" s="10">
+        <v>52.34</v>
+      </c>
+      <c r="K39" s="1">
+        <v>80</v>
+      </c>
+      <c r="L39" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="1">
+        <v>13</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D40" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E40" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G40" s="10">
+        <v>96.4</v>
+      </c>
+      <c r="H40" s="10">
+        <v>9619.5</v>
+      </c>
+      <c r="I40" s="10">
+        <v>6976.27</v>
+      </c>
+      <c r="J40" s="10">
+        <v>37.89</v>
+      </c>
+      <c r="K40" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L40" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="1">
+        <v>14</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D41" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E41" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G41" s="10">
+        <v>87.8</v>
+      </c>
+      <c r="H41" s="10">
+        <v>1386.7</v>
+      </c>
+      <c r="I41" s="10">
+        <v>1115.5999999999999</v>
+      </c>
+      <c r="J41" s="10">
+        <v>24.3</v>
+      </c>
+      <c r="K41" s="1">
+        <v>56.8</v>
+      </c>
+      <c r="L41" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="1">
+        <v>15</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="10">
+        <v>72.8</v>
+      </c>
+      <c r="H42" s="10">
+        <v>1071.95</v>
+      </c>
+      <c r="I42" s="10">
+        <v>953.76</v>
+      </c>
+      <c r="J42" s="10">
+        <v>12.39</v>
+      </c>
+      <c r="K42" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L42" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="1">
+        <v>16</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E43" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="10">
+        <v>93.7</v>
+      </c>
+      <c r="H43" s="10">
+        <v>8584.5</v>
+      </c>
+      <c r="I43" s="10">
+        <v>6950.34</v>
+      </c>
+      <c r="J43" s="10">
+        <v>23.51</v>
+      </c>
+      <c r="K43" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="L43" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="1">
+        <v>17</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E44" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="10">
+        <v>94.1</v>
+      </c>
+      <c r="H44" s="10">
+        <v>1513.6</v>
+      </c>
+      <c r="I44" s="10">
+        <v>1185.1199999999999</v>
+      </c>
+      <c r="J44" s="10">
+        <v>27.72</v>
+      </c>
+      <c r="K44" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L44" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="1">
+        <v>18</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D45" s="10">
+        <v>85.7</v>
+      </c>
+      <c r="E45" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G45" s="10">
+        <v>91.2</v>
+      </c>
+      <c r="H45" s="10">
+        <v>3002.6</v>
+      </c>
+      <c r="I45" s="10">
+        <v>2389.2399999999998</v>
+      </c>
+      <c r="J45" s="10">
+        <v>25.67</v>
+      </c>
+      <c r="K45" s="1">
+        <v>44</v>
+      </c>
+      <c r="L45" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="1">
+        <v>19</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" s="10">
+        <v>85.4</v>
+      </c>
+      <c r="E46" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G46" s="10">
+        <v>88.6</v>
+      </c>
+      <c r="H46" s="10">
+        <v>1838</v>
+      </c>
+      <c r="I46" s="10">
+        <v>1573</v>
+      </c>
+      <c r="J46" s="10">
+        <v>16.850000000000001</v>
+      </c>
+      <c r="K46" s="1">
+        <v>47.1</v>
+      </c>
+      <c r="L46" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="1">
+        <v>20</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" s="10">
+        <v>85.2</v>
+      </c>
+      <c r="E47" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G47" s="10">
+        <v>69.7</v>
+      </c>
+      <c r="H47" s="10">
+        <v>8889</v>
+      </c>
+      <c r="I47" s="10">
+        <v>7982.82</v>
+      </c>
+      <c r="J47" s="10">
+        <v>11.35</v>
+      </c>
+      <c r="K47" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L47" s="14">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14">
+      <c r="A50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B50" t="s">
+        <v>20</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H50" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K50" t="s">
+        <v>29</v>
+      </c>
+      <c r="L50" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14">
+      <c r="A51">
+        <v>1</v>
+      </c>
+      <c r="B51" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="7">
+        <v>91</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="7">
+        <v>98.1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3091.1</v>
+      </c>
+      <c r="I51" s="7">
+        <v>2184.92</v>
+      </c>
+      <c r="J51" s="7">
+        <v>41.47</v>
+      </c>
+      <c r="K51">
+        <v>58.3</v>
+      </c>
+      <c r="L51" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D52" s="7">
+        <v>90</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="7">
+        <v>98.5</v>
+      </c>
+      <c r="H52" s="7">
+        <v>1474.5</v>
+      </c>
+      <c r="I52" s="7">
+        <v>1016.25</v>
+      </c>
+      <c r="J52" s="7">
+        <v>45.09</v>
+      </c>
+      <c r="K52">
+        <v>52.5</v>
+      </c>
+      <c r="L52" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>35</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="7">
+        <v>89.6</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="7">
+        <v>94.2</v>
+      </c>
+      <c r="H53" s="7">
+        <v>1983.1</v>
+      </c>
+      <c r="I53" s="7">
+        <v>1676.41</v>
+      </c>
+      <c r="J53" s="7">
+        <v>18.29</v>
+      </c>
+      <c r="K53">
+        <v>58.3</v>
+      </c>
+      <c r="L53" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="54" spans="1:14">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>86</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="7">
+        <v>89.5</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="7">
+        <v>93.7</v>
+      </c>
+      <c r="H54" s="7">
+        <v>1919.2</v>
+      </c>
+      <c r="I54" s="7">
+        <v>1642.3</v>
+      </c>
+      <c r="J54" s="7">
+        <v>16.86</v>
+      </c>
+      <c r="K54">
+        <v>58.3</v>
+      </c>
+      <c r="L54" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14">
+      <c r="A55">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>87</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="7">
+        <v>88.7</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="7">
+        <v>94.8</v>
+      </c>
+      <c r="H55" s="7">
+        <v>283.05</v>
+      </c>
+      <c r="I55" s="7">
+        <v>230.88</v>
+      </c>
+      <c r="J55" s="7">
+        <v>22.6</v>
+      </c>
+      <c r="K55">
+        <v>52.5</v>
+      </c>
+      <c r="L55" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14">
+      <c r="A56">
+        <v>6</v>
+      </c>
+      <c r="B56" t="s">
+        <v>54</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" s="7">
+        <v>88.6</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="7">
+        <v>91.2</v>
+      </c>
+      <c r="H56" s="7">
+        <v>1406.5</v>
+      </c>
+      <c r="I56" s="7">
+        <v>1209.3499999999999</v>
+      </c>
+      <c r="J56" s="7">
+        <v>16.3</v>
+      </c>
+      <c r="K56">
+        <v>58.3</v>
+      </c>
+      <c r="L56" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14">
+      <c r="A57">
+        <v>7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>88</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="7">
+        <v>88.1</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G57" s="7">
+        <v>99.6</v>
+      </c>
+      <c r="H57" s="7">
+        <v>1489.1</v>
+      </c>
+      <c r="I57" s="7">
+        <v>948.97</v>
+      </c>
+      <c r="J57" s="7">
+        <v>56.92</v>
+      </c>
+      <c r="K57">
+        <v>41.2</v>
+      </c>
+      <c r="L57" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14">
+      <c r="A58">
+        <v>8</v>
+      </c>
+      <c r="B58" t="s">
+        <v>90</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D58" s="7">
+        <v>87.8</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G58" s="7">
+        <v>97.9</v>
+      </c>
+      <c r="H58" s="7">
+        <v>391.95</v>
+      </c>
+      <c r="I58" s="7">
+        <v>277.29000000000002</v>
+      </c>
+      <c r="J58" s="7">
+        <v>41.35</v>
+      </c>
+      <c r="K58">
+        <v>42.9</v>
+      </c>
+      <c r="L58" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14">
+      <c r="A59">
+        <v>9</v>
+      </c>
+      <c r="B59" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D59" s="7">
+        <v>86.3</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="7">
+        <v>87.9</v>
+      </c>
+      <c r="H59" s="7">
+        <v>1097.5999999999999</v>
+      </c>
+      <c r="I59" s="7">
+        <v>924.32</v>
+      </c>
+      <c r="J59" s="7">
+        <v>18.75</v>
+      </c>
+      <c r="K59">
+        <v>52.5</v>
+      </c>
+      <c r="L59" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14">
+      <c r="A60">
+        <v>10</v>
+      </c>
+      <c r="B60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D60" s="7">
+        <v>86.2</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="7">
+        <v>92.3</v>
+      </c>
+      <c r="H60" s="7">
+        <v>1195.4000000000001</v>
+      </c>
+      <c r="I60" s="7">
+        <v>963.91</v>
+      </c>
+      <c r="J60" s="7">
+        <v>24.02</v>
+      </c>
+      <c r="K60">
+        <v>44.4</v>
+      </c>
+      <c r="L60" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:14">
+      <c r="A61">
+        <v>11</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="7">
+        <v>85.7</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="7">
+        <v>82.9</v>
+      </c>
+      <c r="H61" s="7">
+        <v>1132.5</v>
+      </c>
+      <c r="I61" s="7">
+        <v>1018.08</v>
+      </c>
+      <c r="J61" s="7">
+        <v>11.24</v>
+      </c>
+      <c r="K61">
+        <v>58.3</v>
+      </c>
+      <c r="L61" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14">
+      <c r="A62">
+        <v>12</v>
+      </c>
+      <c r="B62" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D62" s="7">
+        <v>83.8</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G62" s="7">
+        <v>86.6</v>
+      </c>
+      <c r="H62" s="7">
+        <v>501.15</v>
+      </c>
+      <c r="I62" s="7">
+        <v>416</v>
+      </c>
+      <c r="J62" s="7">
+        <v>20.47</v>
+      </c>
+      <c r="K62">
+        <v>80</v>
+      </c>
+      <c r="L62" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="63" spans="1:14">
+      <c r="A63">
+        <v>13</v>
+      </c>
+      <c r="B63" t="s">
+        <v>97</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D63" s="7">
+        <v>83.7</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G63" s="7">
+        <v>86</v>
+      </c>
+      <c r="H63" s="7">
+        <v>343.3</v>
+      </c>
+      <c r="I63" s="7">
+        <v>294.55</v>
+      </c>
+      <c r="J63" s="7">
+        <v>16.55</v>
+      </c>
+      <c r="K63">
+        <v>42.9</v>
+      </c>
+      <c r="L63" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="64" spans="1:14">
+      <c r="A64">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s">
+        <v>98</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D64" s="7">
+        <v>82.9</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G64" s="7">
+        <v>99.8</v>
+      </c>
+      <c r="H64" s="7">
+        <v>2730</v>
+      </c>
+      <c r="I64" s="7">
+        <v>1423.33</v>
+      </c>
+      <c r="J64" s="7">
+        <v>91.8</v>
+      </c>
+      <c r="K64">
+        <v>52.5</v>
+      </c>
+      <c r="L64" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>99</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D65" s="7">
+        <v>82.8</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="7">
+        <v>82.7</v>
+      </c>
+      <c r="H65" s="7">
+        <v>743.7</v>
+      </c>
+      <c r="I65" s="7">
+        <v>673.48</v>
+      </c>
+      <c r="J65" s="7">
+        <v>10.43</v>
+      </c>
+      <c r="K65">
+        <v>44.4</v>
+      </c>
+      <c r="L65" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66">
+        <v>16</v>
+      </c>
+      <c r="B66" t="s">
+        <v>100</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="7">
+        <v>82.7</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G66" s="7">
+        <v>83.5</v>
+      </c>
+      <c r="H66" s="7">
+        <v>636.04999999999995</v>
+      </c>
+      <c r="I66" s="7">
+        <v>537.41</v>
+      </c>
+      <c r="J66" s="7">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="K66">
+        <v>80</v>
+      </c>
+      <c r="L66" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="A67">
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>101</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D67" s="7">
+        <v>82.6</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G67" s="7">
+        <v>82</v>
+      </c>
+      <c r="H67" s="7">
+        <v>10640</v>
+      </c>
+      <c r="I67" s="7">
+        <v>9226.5499999999993</v>
+      </c>
+      <c r="J67" s="7">
+        <v>15.32</v>
+      </c>
+      <c r="K67">
+        <v>44.4</v>
+      </c>
+      <c r="L67" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="A68">
+        <v>18</v>
+      </c>
+      <c r="B68" t="s">
+        <v>102</v>
+      </c>
+      <c r="C68" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D68" s="7">
+        <v>82.3</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G68" s="7">
+        <v>80.2</v>
+      </c>
+      <c r="H68" s="7">
+        <v>497.9</v>
+      </c>
+      <c r="I68" s="7">
+        <v>455.9</v>
+      </c>
+      <c r="J68" s="7">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="K68">
+        <v>46.2</v>
+      </c>
+      <c r="L68" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15">
+      <c r="A69">
+        <v>19</v>
+      </c>
+      <c r="B69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="7">
+        <v>82.2</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G69" s="7">
+        <v>76.2</v>
+      </c>
+      <c r="H69" s="7">
+        <v>4869</v>
+      </c>
+      <c r="I69" s="7">
+        <v>4410.57</v>
+      </c>
+      <c r="J69" s="7">
+        <v>10.39</v>
+      </c>
+      <c r="K69">
+        <v>52.5</v>
+      </c>
+      <c r="L69" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15">
+      <c r="A70">
+        <v>20</v>
+      </c>
+      <c r="B70" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="7">
+        <v>82.1</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G70" s="7">
+        <v>97.5</v>
+      </c>
+      <c r="H70" s="7">
+        <v>25500</v>
+      </c>
+      <c r="I70" s="7">
+        <v>18462.580000000002</v>
+      </c>
+      <c r="J70" s="7">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="K70">
+        <v>52.5</v>
+      </c>
+      <c r="L70" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="J77" s="20"/>
+      <c r="M77" s="21"/>
+      <c r="O77" s="22"/>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="J78" s="20"/>
+      <c r="M78" s="21"/>
+      <c r="O78" s="22"/>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="J79" s="20"/>
+      <c r="M79" s="21"/>
+      <c r="O79" s="22"/>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="J80" s="20"/>
+      <c r="M80" s="21"/>
+      <c r="O80" s="22"/>
+    </row>
+    <row r="81" spans="10:15">
+      <c r="J81" s="20"/>
+      <c r="M81" s="21"/>
+      <c r="O81" s="22"/>
+    </row>
+    <row r="82" spans="10:15">
+      <c r="J82" s="20"/>
+      <c r="M82" s="21"/>
+      <c r="O82" s="22"/>
+    </row>
+    <row r="83" spans="10:15">
+      <c r="J83" s="20"/>
+      <c r="M83" s="21"/>
+      <c r="O83" s="22"/>
+    </row>
+    <row r="85" spans="10:15">
+      <c r="J85" s="20"/>
+      <c r="M85" s="21"/>
+      <c r="O85" s="22"/>
+    </row>
+    <row r="86" spans="10:15">
+      <c r="J86" s="20"/>
+      <c r="M86" s="21"/>
+      <c r="O86" s="22"/>
+    </row>
+    <row r="87" spans="10:15">
+      <c r="J87" s="20"/>
+      <c r="M87" s="21"/>
+      <c r="O87" s="22"/>
+    </row>
+    <row r="88" spans="10:15">
+      <c r="J88" s="20"/>
+      <c r="M88" s="21"/>
+      <c r="O88" s="22"/>
+    </row>
+    <row r="89" spans="10:15">
+      <c r="J89" s="20"/>
+      <c r="M89" s="21"/>
+      <c r="O89" s="22"/>
+    </row>
+    <row r="91" spans="10:15">
+      <c r="J91" s="20"/>
+      <c r="M91" s="21"/>
+      <c r="O91" s="22"/>
+    </row>
+    <row r="92" spans="10:15">
+      <c r="J92" s="20"/>
+      <c r="M92" s="21"/>
+      <c r="O92" s="22"/>
+    </row>
+    <row r="93" spans="10:15">
+      <c r="J93" s="20"/>
+      <c r="M93" s="21"/>
+      <c r="O93" s="22"/>
+    </row>
+    <row r="94" spans="10:15">
+      <c r="J94" s="20"/>
+      <c r="M94" s="21"/>
+      <c r="O94" s="22"/>
+    </row>
+    <row r="96" spans="10:15">
+      <c r="J96" s="20"/>
+      <c r="M96" s="21"/>
+      <c r="O96" s="22"/>
+    </row>
+    <row r="97" spans="10:15">
+      <c r="J97" s="20"/>
+      <c r="M97" s="21"/>
+      <c r="O97" s="22"/>
+    </row>
+    <row r="98" spans="10:15">
+      <c r="J98" s="20"/>
+      <c r="M98" s="21"/>
+      <c r="O98" s="22"/>
+    </row>
+    <row r="99" spans="10:15">
+      <c r="J99" s="20"/>
+      <c r="M99" s="21"/>
+      <c r="O99" s="22"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/portfolio_parameter_sweep Study.xlsx
+++ b/portfolio_parameter_sweep Study.xlsx
@@ -4,23 +4,24 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" activeTab="2"/>
+    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="portfolio_parameter_sweep copy" sheetId="1" r:id="rId1"/>
     <sheet name="BACKTEST NEW " sheetId="2" r:id="rId2"/>
     <sheet name="25 Sep" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
   <pivotCaches>
-    <pivotCache cacheId="13" r:id="rId4"/>
-    <pivotCache cacheId="18" r:id="rId5"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="184">
   <si>
     <t>Top_N</t>
   </si>
@@ -202,69 +203,6 @@
     <t>TEGA</t>
   </si>
   <si>
-    <t>LAURUSLABS:1;</t>
-  </si>
-  <si>
-    <t>WOCKPHARMA:2;</t>
-  </si>
-  <si>
-    <t>CAPLIPOINT:3;</t>
-  </si>
-  <si>
-    <t>LALPATHLAB:4;</t>
-  </si>
-  <si>
-    <t>FINCABLES:5;</t>
-  </si>
-  <si>
-    <t>SONACOMS:6;</t>
-  </si>
-  <si>
-    <t>MEDANTA:7;</t>
-  </si>
-  <si>
-    <t>AJANTPHARM:8;</t>
-  </si>
-  <si>
-    <t>CARBORUNIV:9;</t>
-  </si>
-  <si>
-    <t>GRAPHITE:10;</t>
-  </si>
-  <si>
-    <t>ZYDUSLIFE:11;</t>
-  </si>
-  <si>
-    <t>WELSPUNLIV:12;</t>
-  </si>
-  <si>
-    <t>DIVISLAB:13;</t>
-  </si>
-  <si>
-    <t>GABRIEL:14;</t>
-  </si>
-  <si>
-    <t>NAVINFLUOR:15;</t>
-  </si>
-  <si>
-    <t>VIJAYA:16;</t>
-  </si>
-  <si>
-    <t>JUBLPHARMA:17;</t>
-  </si>
-  <si>
-    <t>CARTRADE:18;</t>
-  </si>
-  <si>
-    <t>APOLLOHOSP:19;</t>
-  </si>
-  <si>
-    <t>TEGA:20</t>
-  </si>
-  <si>
-    <t>LAURUSLABS:1; WOCKPHARMA:2; CAPLIPOINT:3; LALPATHLAB:4; FINCABLES:5; SONACOMS:6; MEDANTA:7; AJANTPHARM:8; CARBORUNIV:9; GRAPHITE:10; ZYDUSLIFE:11; WELSPUNLIV:12; DIVISLAB:13; GABRIEL:14; NAVINFLUOR:15; VIJAYA:16; JUBLPHARMA:17; CARTRADE:18; APOLLOHOSP:19; TEGA:20</t>
-  </si>
-  <si>
     <t>LLOYDSME</t>
   </si>
   <si>
@@ -335,16 +273,323 @@
   </si>
   <si>
     <t>PTCIL</t>
+  </si>
+  <si>
+    <t>ACUTAAS</t>
+  </si>
+  <si>
+    <t>as on 18 oct</t>
+  </si>
+  <si>
+    <t>WELCORP:1; HFCL:2; CPPLUS:3; ATHERENERG:4; LAURUSLABS:5; RRKABEL:6; ANANDRATHI:7; GRANULES:8; ACUTAAS:9; BHEL:10; SONACOMS:11; RADICO:12; SYRMA:13; HONASA:14; ADANIENSOL:15; NEULANDLAB:16; FEDERALBNK:17; APARINDS:18; AEGISLOG:19; CHENNPETRO:20</t>
+  </si>
+  <si>
+    <t>2026-09-25</t>
+  </si>
+  <si>
+    <t>HFCL</t>
+  </si>
+  <si>
+    <t>CPPLUS</t>
+  </si>
+  <si>
+    <t>ATHERENERG</t>
+  </si>
+  <si>
+    <t>RRKABEL</t>
+  </si>
+  <si>
+    <t>ANANDRATHI</t>
+  </si>
+  <si>
+    <t>GRANULES</t>
+  </si>
+  <si>
+    <t>BHEL</t>
+  </si>
+  <si>
+    <t>RADICO</t>
+  </si>
+  <si>
+    <t>SYRMA</t>
+  </si>
+  <si>
+    <t>HONASA</t>
+  </si>
+  <si>
+    <t>ADANIENSOL</t>
+  </si>
+  <si>
+    <t>NEULANDLAB</t>
+  </si>
+  <si>
+    <t>FEDERALBNK</t>
+  </si>
+  <si>
+    <t>APARINDS</t>
+  </si>
+  <si>
+    <t>CHENNPETRO</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN:1; NATIONALUM:2; ASHOKLEY:3; LTF:4; HINDCOPPER:5; VEDL:6; ABCAPITAL:7; SBIN:8; MCX:9; MUTHOOTFIN:10; HINDALCO:11; FORCEMOT:12; EICHERMOT:13; CANBK:14; TVSMOTOR:15; INDIANB:16; BANKINDIA:17; FEDERALBNK:18; HINDZINC:19; AUBANK:20</t>
+  </si>
+  <si>
+    <t>2026-01-26</t>
+  </si>
+  <si>
+    <t>LTF:1; LAURUSLABS:2; MUTHOOTFIN:3; MARUTI:4; EICHERMOT:5; FORCEMOT:6; RBLBANK:7; ASHOKLEY:8; SHRIRAMFIN:9; CUB:10; ABCAPITAL:11; ANURAS:12; AUBANK:13; CANBK:14; M&amp;MFIN:15; TVSMOTOR:16; NATIONALUM:17; NAVINFLUOR:18; PFOCUS:19; CUMMINSIND:20</t>
+  </si>
+  <si>
+    <t>TATASTEEL</t>
+  </si>
+  <si>
+    <t>JINDALSTEL</t>
+  </si>
+  <si>
+    <t>JKTYRE</t>
+  </si>
+  <si>
+    <t>tomobile and Auto Components</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>CRAFTSMAN</t>
+  </si>
+  <si>
+    <t>UNIONBANK</t>
+  </si>
+  <si>
+    <t>HINDCOPPER</t>
+  </si>
+  <si>
+    <t>NATIONALUM</t>
+  </si>
+  <si>
+    <t>HINDZINC</t>
+  </si>
+  <si>
+    <t>VEDL</t>
+  </si>
+  <si>
+    <t>BANKBARODA</t>
+  </si>
+  <si>
+    <t>HINDALCO</t>
+  </si>
+  <si>
+    <t>MAHABANK</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>INDIACEM</t>
+  </si>
+  <si>
+    <t>Construction Materials</t>
+  </si>
+  <si>
+    <t>MRPL</t>
+  </si>
+  <si>
+    <t>Oil Gas &amp; Consumable Fuels</t>
+  </si>
+  <si>
+    <t>SAIL</t>
+  </si>
+  <si>
+    <t>PFOCUS</t>
+  </si>
+  <si>
+    <t>Entertainment &amp; Publication</t>
+  </si>
+  <si>
+    <t>TECHM</t>
+  </si>
+  <si>
+    <t>TATASTEEL:1; JINDALSTEL:2; JKTYRE:3; MCX:4; CRAFTSMAN:5; UNIONBANK:6; FEDERALBNK:7; BANKBARODA:8; HINDCOPPER:9; NATIONALUM:10; ANANDRATHI:11; HINDZINC:12; MAHABANK:13; VEDL:14; HINDALCO:15; AXISBANK:16; IIFL:17; INDIACEM:18; SAIL:19; NAM-INDIA:20</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>2026-10-14</t>
+  </si>
+  <si>
+    <t>LTF:1;</t>
+  </si>
+  <si>
+    <t>LAURUSLABS:2;</t>
+  </si>
+  <si>
+    <t>MUTHOOTFIN:3;</t>
+  </si>
+  <si>
+    <t>MARUTI:4;</t>
+  </si>
+  <si>
+    <t>EICHERMOT:5;</t>
+  </si>
+  <si>
+    <t>FORCEMOT:6;</t>
+  </si>
+  <si>
+    <t>RBLBANK:7;</t>
+  </si>
+  <si>
+    <t>ASHOKLEY:8;</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN:9;</t>
+  </si>
+  <si>
+    <t>CUB:10;</t>
+  </si>
+  <si>
+    <t>ABCAPITAL:11;</t>
+  </si>
+  <si>
+    <t>ANURAS:12;</t>
+  </si>
+  <si>
+    <t>AUBANK:13;</t>
+  </si>
+  <si>
+    <t>CANBK:14;</t>
+  </si>
+  <si>
+    <t>M&amp;MFIN:15;</t>
+  </si>
+  <si>
+    <t>TVSMOTOR:16;</t>
+  </si>
+  <si>
+    <t>NATIONALUM:17;</t>
+  </si>
+  <si>
+    <t>NAVINFLUOR:18;</t>
+  </si>
+  <si>
+    <t>PFOCUS:19;</t>
+  </si>
+  <si>
+    <t>CUMMINSIND:20</t>
+  </si>
+  <si>
+    <t>TATASTEEL:1;</t>
+  </si>
+  <si>
+    <t>JINDALSTEL:2;</t>
+  </si>
+  <si>
+    <t>JKTYRE:3;</t>
+  </si>
+  <si>
+    <t>MCX:4;</t>
+  </si>
+  <si>
+    <t>CRAFTSMAN:5;</t>
+  </si>
+  <si>
+    <t>UNIONBANK:6;</t>
+  </si>
+  <si>
+    <t>FEDERALBNK:7;</t>
+  </si>
+  <si>
+    <t>BANKBARODA:8;</t>
+  </si>
+  <si>
+    <t>HINDCOPPER:9;</t>
+  </si>
+  <si>
+    <t>NATIONALUM:10;</t>
+  </si>
+  <si>
+    <t>ANANDRATHI:11;</t>
+  </si>
+  <si>
+    <t>HINDZINC:12;</t>
+  </si>
+  <si>
+    <t>MAHABANK:13;</t>
+  </si>
+  <si>
+    <t>VEDL:14;</t>
+  </si>
+  <si>
+    <t>HINDALCO:15;</t>
+  </si>
+  <si>
+    <t>AXISBANK:16;</t>
+  </si>
+  <si>
+    <t>IIFL:17;</t>
+  </si>
+  <si>
+    <t>INDIACEM:18;</t>
+  </si>
+  <si>
+    <t>SAIL:19;</t>
+  </si>
+  <si>
+    <t>NAM-INDIA:20</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN:1; NATIONALUM:2; ASHOKLEY:3; LTF:4; HINDCOPPER:5; VEDL:6; ABCAPITAL:7; SBIN:8; MCX:9; MUTHOOTFIN:10; HINDALCO:11; FORCEMOT:12; INDIANB:13; EICHERMOT:14; CANBK:15; TVSMOTOR:16; BANKINDIA:17; HINDZINC:18; FEDERALBNK:19; AUBANK:20</t>
+  </si>
+  <si>
+    <t>2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> python current_stock_picks.py --as-of 2026-09-25 --include-below-200dma
+CURRENT STOCK CANDIDATES (research backtest scoring rules)
+Data as of benchmark date: 2026-09-25
+Indicator timeframe: monthly
+Above 200-DMA filter: off
+Candidates only; this report does not place orders or make a personalized recommendation.
+</t>
+  </si>
+  <si>
+    <t>ZENTEC</t>
+  </si>
+  <si>
+    <t>CEMPRO</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>ETERNAL</t>
+  </si>
+  <si>
+    <t>Consumer Services</t>
+  </si>
+  <si>
+    <t>│ 1 │ GLAND │ Healthcare │ Leading │ 98% │ ✓ +37.3% │ 54% │ 90 │</t>
+  </si>
+  <si>
+    <t>┃ # ┃ Stock ┃ Sector ┃ Quadrant ┃ RS Rank ┃ 200-DMA ┃ Breadth ┃ Score ┃</t>
+  </si>
+  <si>
+    <t>2026-10-16  3096.9  3096.9  3004.3  3043.4  165156  GLAND  2216.7725           True</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,6 +736,33 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -677,7 +949,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -807,6 +1079,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -852,7 +1137,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -878,7 +1163,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -900,6 +1184,64 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="7"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="7" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="10" xfId="7" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -945,7 +1287,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="18">
     <dxf>
       <font>
         <condense val="0"/>
@@ -959,90 +1301,16 @@
       </fill>
     </dxf>
     <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" indent="0" relativeIndent="255" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" readingOrder="0"/>
+      <font>
+        <condense val="0"/>
+        <extend val="0"/>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <alignment horizontal="center" readingOrder="0"/>
@@ -2598,7 +2866,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="18" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Q3:W15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0">
@@ -2744,7 +3012,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="13" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Year" colHeaderCaption="Exit Score">
   <location ref="Q3:X24" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="10">
     <pivotField name="No # stock" axis="axisRow" showAll="0">
@@ -2885,21 +3153,21 @@
     <dataField name="Year" fld="6" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="16">
-    <format dxfId="32">
+    <format dxfId="17">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="30">
+    <format dxfId="15">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2921,7 +3189,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="29">
+    <format dxfId="14">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2943,17 +3211,17 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="28">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="0"/>
         </references>
       </pivotArea>
     </format>
-    <format dxfId="27">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandCol="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="2">
@@ -2963,7 +3231,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -2973,7 +3241,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="24">
+    <format dxfId="9">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -2995,7 +3263,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="23">
+    <format dxfId="8">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="1">
@@ -3012,7 +3280,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="22">
+    <format dxfId="7">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="6">
@@ -3034,7 +3302,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="6">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="3">
           <reference field="0" count="5">
@@ -3055,7 +3323,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="6">
@@ -3072,7 +3340,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="1">
@@ -3084,7 +3352,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="6">
@@ -3101,7 +3369,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="2">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="2">
           <reference field="0" count="5">
@@ -6231,7 +6499,7 @@
       <c r="Q23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="R23" s="15" t="s">
+      <c r="R23" s="14" t="s">
         <v>0</v>
       </c>
       <c r="S23" s="5"/>
@@ -7751,73 +8019,80 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P99"/>
+  <dimension ref="A1:Z124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" style="7" customWidth="1"/>
     <col min="5" max="6" width="13.140625" style="7" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="7" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10" style="7" customWidth="1"/>
-    <col min="11" max="11" width="16.7109375" style="7" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="7" customWidth="1"/>
     <col min="12" max="13" width="10.42578125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="23" customWidth="1"/>
+    <col min="17" max="17" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="45">
-      <c r="A1" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C1" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>24</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="H1" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="J1" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
+    <row r="1" spans="1:18">
+      <c r="A1" s="1">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G1" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H1" s="10">
+        <v>824.5</v>
+      </c>
+      <c r="I1" s="10">
+        <v>604.44000000000005</v>
+      </c>
+      <c r="J1" s="10">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="K1" s="10">
+        <v>56.8</v>
+      </c>
+      <c r="L1" s="13">
+        <v>46290</v>
+      </c>
+      <c r="P1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="10">
-        <v>95.6</v>
+        <v>90.5</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>33</v>
@@ -7826,42 +8101,36 @@
         <v>34</v>
       </c>
       <c r="G2" s="10">
-        <v>99.2</v>
+        <v>84.8</v>
       </c>
       <c r="H2" s="10">
-        <v>2007</v>
+        <v>1495.4</v>
       </c>
       <c r="I2" s="10">
-        <v>1333.97</v>
+        <v>1230.3800000000001</v>
       </c>
       <c r="J2" s="10">
-        <v>50.45</v>
+        <v>21.54</v>
       </c>
       <c r="K2" s="10">
         <v>79.2</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
         <v>46290</v>
       </c>
-      <c r="N2" t="s">
-        <v>60</v>
-      </c>
-      <c r="P2" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+    </row>
+    <row r="3" spans="1:18">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D3" s="10">
-        <v>94.4</v>
+        <v>90.4</v>
       </c>
       <c r="E3" s="10" t="s">
         <v>33</v>
@@ -7870,39 +8139,42 @@
         <v>34</v>
       </c>
       <c r="G3" s="10">
-        <v>96</v>
+        <v>84.4</v>
       </c>
       <c r="H3" s="10">
-        <v>2265.6</v>
+        <v>3547.8</v>
       </c>
       <c r="I3" s="10">
-        <v>1635.97</v>
+        <v>3060.4</v>
       </c>
       <c r="J3" s="10">
-        <v>38.49</v>
+        <v>15.93</v>
       </c>
       <c r="K3" s="10">
         <v>79.2</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
         <v>46290</v>
       </c>
-      <c r="N3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+      <c r="O3" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="P3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D4" s="10">
-        <v>94.2</v>
+        <v>88.9</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>33</v>
@@ -7911,39 +8183,36 @@
         <v>34</v>
       </c>
       <c r="G4" s="10">
-        <v>95.2</v>
+        <v>92.6</v>
       </c>
       <c r="H4" s="10">
-        <v>2835.1</v>
+        <v>1278.5</v>
       </c>
       <c r="I4" s="10">
-        <v>2095.15</v>
+        <v>966</v>
       </c>
       <c r="J4" s="10">
-        <v>35.32</v>
+        <v>32.35</v>
       </c>
       <c r="K4" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L4" s="14">
+        <v>57.4</v>
+      </c>
+      <c r="L4" s="13">
         <v>46290</v>
       </c>
-      <c r="N4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+    </row>
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D5" s="10">
-        <v>91.4</v>
+        <v>88.8</v>
       </c>
       <c r="E5" s="10" t="s">
         <v>33</v>
@@ -7952,39 +8221,45 @@
         <v>34</v>
       </c>
       <c r="G5" s="10">
-        <v>87.2</v>
+        <v>92.4</v>
       </c>
       <c r="H5" s="10">
-        <v>1952.3</v>
+        <v>820.7</v>
       </c>
       <c r="I5" s="10">
-        <v>1577.25</v>
+        <v>670.49</v>
       </c>
       <c r="J5" s="10">
-        <v>23.78</v>
+        <v>22.4</v>
       </c>
       <c r="K5" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L5" s="14">
+        <v>57.4</v>
+      </c>
+      <c r="L5" s="13">
         <v>46290</v>
       </c>
-      <c r="N5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="O5" s="1">
+        <v>1</v>
+      </c>
+      <c r="P5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D6" s="10">
-        <v>90.7</v>
+        <v>88.7</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>33</v>
@@ -7993,121 +8268,139 @@
         <v>34</v>
       </c>
       <c r="G6" s="10">
-        <v>97.7</v>
+        <v>79.599999999999994</v>
       </c>
       <c r="H6" s="10">
-        <v>1460.9</v>
+        <v>1203.9000000000001</v>
       </c>
       <c r="I6" s="10">
-        <v>977.88</v>
+        <v>1005.37</v>
       </c>
       <c r="J6" s="10">
-        <v>49.4</v>
+        <v>19.75</v>
       </c>
       <c r="K6" s="10">
-        <v>57.4</v>
-      </c>
-      <c r="L6" s="14">
+        <v>79.2</v>
+      </c>
+      <c r="L6" s="13">
         <v>46290</v>
       </c>
-      <c r="N6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="O6" s="1">
+        <v>2</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D7" s="10">
-        <v>90.7</v>
+        <v>88.1</v>
       </c>
       <c r="E7" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G7" s="10">
-        <v>98.1</v>
+        <v>98.9</v>
       </c>
       <c r="H7" s="10">
-        <v>824.5</v>
+        <v>224.68</v>
       </c>
       <c r="I7" s="10">
-        <v>604.44000000000005</v>
+        <v>147.49</v>
       </c>
       <c r="J7" s="10">
-        <v>36.409999999999997</v>
+        <v>52.34</v>
       </c>
       <c r="K7" s="10">
-        <v>56.8</v>
-      </c>
-      <c r="L7" s="14">
+        <v>80</v>
+      </c>
+      <c r="L7" s="13">
         <v>46290</v>
       </c>
-      <c r="N7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="O7" s="1">
+        <v>3</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D8" s="10">
-        <v>90.5</v>
+        <v>87.1</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G8" s="10">
-        <v>84.8</v>
+        <v>96.4</v>
       </c>
       <c r="H8" s="10">
-        <v>1495.4</v>
+        <v>9619.5</v>
       </c>
       <c r="I8" s="10">
-        <v>1230.3800000000001</v>
+        <v>6957.95</v>
       </c>
       <c r="J8" s="10">
-        <v>21.54</v>
+        <v>38.25</v>
       </c>
       <c r="K8" s="10">
         <v>79.2</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>46290</v>
       </c>
-      <c r="N8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="O8" s="1">
+        <v>4</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D9" s="10">
-        <v>90.4</v>
+        <v>87.1</v>
       </c>
       <c r="E9" s="10" t="s">
         <v>33</v>
@@ -8116,39 +8409,45 @@
         <v>34</v>
       </c>
       <c r="G9" s="10">
-        <v>84.4</v>
+        <v>87.8</v>
       </c>
       <c r="H9" s="10">
-        <v>3547.8</v>
+        <v>1386.7</v>
       </c>
       <c r="I9" s="10">
-        <v>3060.4</v>
+        <v>1115.5999999999999</v>
       </c>
       <c r="J9" s="10">
-        <v>15.93</v>
+        <v>24.3</v>
       </c>
       <c r="K9" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L9" s="14">
+        <v>56.8</v>
+      </c>
+      <c r="L9" s="13">
         <v>46290</v>
       </c>
-      <c r="N9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="O9" s="1">
+        <v>5</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D10" s="10">
-        <v>88.9</v>
+        <v>86.3</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>33</v>
@@ -8157,80 +8456,92 @@
         <v>34</v>
       </c>
       <c r="G10" s="10">
-        <v>92.6</v>
+        <v>93.9</v>
       </c>
       <c r="H10" s="10">
-        <v>1278.5</v>
+        <v>8584.5</v>
       </c>
       <c r="I10" s="10">
-        <v>966</v>
+        <v>6950.34</v>
       </c>
       <c r="J10" s="10">
-        <v>32.35</v>
+        <v>23.51</v>
       </c>
       <c r="K10" s="10">
-        <v>57.4</v>
-      </c>
-      <c r="L10" s="14">
+        <v>42.3</v>
+      </c>
+      <c r="L10" s="13">
         <v>46290</v>
       </c>
-      <c r="N10" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="O10" s="1">
+        <v>6</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D11" s="10">
-        <v>88.8</v>
+        <v>86.3</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G11" s="10">
-        <v>92.4</v>
+        <v>94.1</v>
       </c>
       <c r="H11" s="10">
-        <v>820.7</v>
+        <v>1513.6</v>
       </c>
       <c r="I11" s="10">
-        <v>670.49</v>
+        <v>1185.1199999999999</v>
       </c>
       <c r="J11" s="10">
-        <v>22.4</v>
+        <v>27.72</v>
       </c>
       <c r="K11" s="10">
-        <v>57.4</v>
-      </c>
-      <c r="L11" s="14">
+        <v>79.2</v>
+      </c>
+      <c r="L11" s="13">
         <v>46290</v>
       </c>
-      <c r="N11" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="O11" s="1">
+        <v>7</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D12" s="10">
-        <v>88.7</v>
+        <v>86.2</v>
       </c>
       <c r="E12" s="10" t="s">
         <v>33</v>
@@ -8239,121 +8550,139 @@
         <v>34</v>
       </c>
       <c r="G12" s="10">
-        <v>79.599999999999994</v>
+        <v>72.400000000000006</v>
       </c>
       <c r="H12" s="10">
-        <v>1203.9000000000001</v>
+        <v>1071.95</v>
       </c>
       <c r="I12" s="10">
-        <v>1005.37</v>
+        <v>957.54</v>
       </c>
       <c r="J12" s="10">
-        <v>19.75</v>
+        <v>11.95</v>
       </c>
       <c r="K12" s="10">
         <v>79.2</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="13">
         <v>46290</v>
       </c>
-      <c r="N12" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="O12" s="1">
+        <v>8</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D13" s="10">
-        <v>88.1</v>
+        <v>85.7</v>
       </c>
       <c r="E13" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G13" s="10">
-        <v>98.9</v>
+        <v>91.2</v>
       </c>
       <c r="H13" s="10">
-        <v>224.68</v>
+        <v>3002.6</v>
       </c>
       <c r="I13" s="10">
-        <v>147.49</v>
+        <v>2389.2399999999998</v>
       </c>
       <c r="J13" s="10">
-        <v>52.34</v>
+        <v>25.67</v>
       </c>
       <c r="K13" s="10">
-        <v>80</v>
-      </c>
-      <c r="L13" s="14">
+        <v>44</v>
+      </c>
+      <c r="L13" s="13">
         <v>46290</v>
       </c>
-      <c r="N13" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="O13" s="1">
+        <v>9</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>32</v>
       </c>
       <c r="D14" s="10">
-        <v>87.1</v>
+        <v>85.1</v>
       </c>
       <c r="E14" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G14" s="10">
-        <v>96.4</v>
+        <v>69.3</v>
       </c>
       <c r="H14" s="10">
-        <v>9619.5</v>
+        <v>8889</v>
       </c>
       <c r="I14" s="10">
-        <v>6957.95</v>
+        <v>7983.94</v>
       </c>
       <c r="J14" s="10">
-        <v>38.25</v>
+        <v>11.34</v>
       </c>
       <c r="K14" s="10">
         <v>79.2</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="13">
         <v>46290</v>
       </c>
-      <c r="N14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="O14" s="1">
+        <v>10</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D15" s="10">
-        <v>87.1</v>
+        <v>84.7</v>
       </c>
       <c r="E15" s="10" t="s">
         <v>33</v>
@@ -8362,323 +8691,402 @@
         <v>34</v>
       </c>
       <c r="G15" s="10">
-        <v>87.8</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="H15" s="10">
-        <v>1386.7</v>
+        <v>2091.6</v>
       </c>
       <c r="I15" s="10">
-        <v>1115.5999999999999</v>
+        <v>1730.71</v>
       </c>
       <c r="J15" s="10">
-        <v>24.3</v>
+        <v>20.85</v>
       </c>
       <c r="K15" s="10">
+        <v>57.4</v>
+      </c>
+      <c r="L15" s="13">
+        <v>46290</v>
+      </c>
+      <c r="O15" s="1">
+        <v>11</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="O16" s="1">
+        <v>12</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26">
+      <c r="O17" s="1">
+        <v>13</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26">
+      <c r="O18" s="1">
+        <v>14</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26">
+      <c r="O19" s="1">
+        <v>15</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26">
+      <c r="O20" s="1">
+        <v>16</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="45">
+      <c r="A21" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="I21" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="J21" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="K21" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="L21" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="O21" s="1">
+        <v>17</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" s="1">
+        <v>1</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D22" s="10">
+        <v>95.6</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="10">
+        <v>99.2</v>
+      </c>
+      <c r="H22" s="10">
+        <v>2007</v>
+      </c>
+      <c r="I22" s="10">
+        <v>1333.45</v>
+      </c>
+      <c r="J22" s="10">
+        <v>50.51</v>
+      </c>
+      <c r="K22" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L22" s="13">
+        <v>46290</v>
+      </c>
+      <c r="O22" s="1">
+        <v>18</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" s="1">
+        <v>2</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="10">
+        <v>94.4</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="10">
+        <v>96</v>
+      </c>
+      <c r="H23" s="10">
+        <v>2265.6</v>
+      </c>
+      <c r="I23" s="10">
+        <v>1635.97</v>
+      </c>
+      <c r="J23" s="10">
+        <v>38.49</v>
+      </c>
+      <c r="K23" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L23" s="13">
+        <v>46290</v>
+      </c>
+      <c r="O23" s="1">
+        <v>19</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" s="1">
+        <v>3</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D24" s="10">
+        <v>94.2</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="10">
+        <v>95.2</v>
+      </c>
+      <c r="H24" s="10">
+        <v>2835.1</v>
+      </c>
+      <c r="I24" s="10">
+        <v>2095.15</v>
+      </c>
+      <c r="J24" s="10">
+        <v>35.32</v>
+      </c>
+      <c r="K24" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L24" s="13">
+        <v>46290</v>
+      </c>
+      <c r="O24" s="1">
+        <v>20</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" s="1">
+        <v>4</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="10">
+        <v>91.4</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="10">
+        <v>87.2</v>
+      </c>
+      <c r="H25" s="10">
+        <v>1952.3</v>
+      </c>
+      <c r="I25" s="10">
+        <v>1577.25</v>
+      </c>
+      <c r="J25" s="10">
+        <v>23.78</v>
+      </c>
+      <c r="K25" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L25" s="13">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26">
+      <c r="A26" s="1">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D26" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="10">
+        <v>97.7</v>
+      </c>
+      <c r="H26" s="10">
+        <v>1460.9</v>
+      </c>
+      <c r="I26" s="10">
+        <v>977.88</v>
+      </c>
+      <c r="J26" s="10">
+        <v>49.4</v>
+      </c>
+      <c r="K26" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L26" s="13">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
+      <c r="A27" s="1">
+        <v>6</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D27" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H27" s="10">
+        <v>824.5</v>
+      </c>
+      <c r="I27" s="10">
+        <v>604.44000000000005</v>
+      </c>
+      <c r="J27" s="10">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="K27" s="1">
         <v>56.8</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L27" s="13">
         <v>46290</v>
       </c>
-      <c r="N15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" s="10">
-        <v>86.3</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G16" s="10">
-        <v>93.9</v>
-      </c>
-      <c r="H16" s="10">
-        <v>8584.5</v>
-      </c>
-      <c r="I16" s="10">
-        <v>6950.34</v>
-      </c>
-      <c r="J16" s="10">
-        <v>23.51</v>
-      </c>
-      <c r="K16" s="10">
-        <v>42.3</v>
-      </c>
-      <c r="L16" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N16" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="10">
-        <v>86.3</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G17" s="10">
-        <v>94.1</v>
-      </c>
-      <c r="H17" s="10">
-        <v>1513.6</v>
-      </c>
-      <c r="I17" s="10">
-        <v>1185.1199999999999</v>
-      </c>
-      <c r="J17" s="10">
-        <v>27.72</v>
-      </c>
-      <c r="K17" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L17" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N17" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D18" s="10">
-        <v>86.2</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G18" s="10">
-        <v>72.400000000000006</v>
-      </c>
-      <c r="H18" s="10">
-        <v>1071.95</v>
-      </c>
-      <c r="I18" s="10">
-        <v>957.54</v>
-      </c>
-      <c r="J18" s="10">
-        <v>11.95</v>
-      </c>
-      <c r="K18" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L18" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N18" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D19" s="10">
-        <v>85.7</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G19" s="10">
-        <v>91.2</v>
-      </c>
-      <c r="H19" s="10">
-        <v>3002.6</v>
-      </c>
-      <c r="I19" s="10">
-        <v>2389.2399999999998</v>
-      </c>
-      <c r="J19" s="10">
-        <v>25.67</v>
-      </c>
-      <c r="K19" s="10">
-        <v>44</v>
-      </c>
-      <c r="L19" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D20" s="10">
-        <v>85.1</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G20" s="10">
-        <v>69.3</v>
-      </c>
-      <c r="H20" s="10">
-        <v>8889</v>
-      </c>
-      <c r="I20" s="10">
-        <v>7983.94</v>
-      </c>
-      <c r="J20" s="10">
-        <v>11.34</v>
-      </c>
-      <c r="K20" s="10">
-        <v>79.2</v>
-      </c>
-      <c r="L20" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N20" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="10">
-        <v>84.7</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="10">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="H21" s="10">
-        <v>2091.6</v>
-      </c>
-      <c r="I21" s="10">
-        <v>1730.71</v>
-      </c>
-      <c r="J21" s="10">
-        <v>20.85</v>
-      </c>
-      <c r="K21" s="10">
-        <v>57.4</v>
-      </c>
-      <c r="L21" s="14">
-        <v>46290</v>
-      </c>
-      <c r="N21" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" ht="45">
-      <c r="A27" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="B27" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="I27" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="K27" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="L27" s="18" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28" s="1">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D28" s="10">
-        <v>95.6</v>
+        <v>90.5</v>
       </c>
       <c r="E28" s="10" t="s">
         <v>33</v>
@@ -8687,36 +9095,36 @@
         <v>34</v>
       </c>
       <c r="G28" s="10">
-        <v>99.2</v>
+        <v>84.6</v>
       </c>
       <c r="H28" s="10">
-        <v>2007</v>
+        <v>1495.4</v>
       </c>
       <c r="I28" s="10">
-        <v>1333.45</v>
+        <v>1230.3800000000001</v>
       </c>
       <c r="J28" s="10">
-        <v>50.51</v>
+        <v>21.54</v>
       </c>
       <c r="K28" s="1">
         <v>79.2</v>
       </c>
-      <c r="L28" s="14">
+      <c r="L28" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:26">
       <c r="A29" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D29" s="10">
-        <v>94.4</v>
+        <v>90.3</v>
       </c>
       <c r="E29" s="10" t="s">
         <v>33</v>
@@ -8725,36 +9133,36 @@
         <v>34</v>
       </c>
       <c r="G29" s="10">
-        <v>96</v>
+        <v>84.2</v>
       </c>
       <c r="H29" s="10">
-        <v>2265.6</v>
+        <v>3547.8</v>
       </c>
       <c r="I29" s="10">
-        <v>1635.97</v>
+        <v>3061.42</v>
       </c>
       <c r="J29" s="10">
-        <v>38.49</v>
+        <v>15.89</v>
       </c>
       <c r="K29" s="1">
         <v>79.2</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:26">
       <c r="A30" s="1">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D30" s="10">
-        <v>94.2</v>
+        <v>89</v>
       </c>
       <c r="E30" s="10" t="s">
         <v>33</v>
@@ -8763,36 +9171,42 @@
         <v>34</v>
       </c>
       <c r="G30" s="10">
-        <v>95.2</v>
+        <v>92.8</v>
       </c>
       <c r="H30" s="10">
-        <v>2835.1</v>
+        <v>820.7</v>
       </c>
       <c r="I30" s="10">
-        <v>2095.15</v>
+        <v>665.21</v>
       </c>
       <c r="J30" s="10">
-        <v>35.32</v>
+        <v>23.37</v>
       </c>
       <c r="K30" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L30" s="14">
+        <v>57.4</v>
+      </c>
+      <c r="L30" s="13">
         <v>46290</v>
       </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="26"/>
+      <c r="Z30" s="27"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D31" s="10">
-        <v>91.4</v>
+        <v>88.8</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>33</v>
@@ -8801,36 +9215,36 @@
         <v>34</v>
       </c>
       <c r="G31" s="10">
-        <v>87.2</v>
+        <v>92.4</v>
       </c>
       <c r="H31" s="10">
-        <v>1952.3</v>
+        <v>1278.5</v>
       </c>
       <c r="I31" s="10">
-        <v>1577.25</v>
+        <v>966</v>
       </c>
       <c r="J31" s="10">
-        <v>23.78</v>
+        <v>32.35</v>
       </c>
       <c r="K31" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L31" s="14">
+        <v>57.4</v>
+      </c>
+      <c r="L31" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:26">
       <c r="A32" s="1">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D32" s="10">
-        <v>90.7</v>
+        <v>88.8</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>33</v>
@@ -8839,112 +9253,112 @@
         <v>34</v>
       </c>
       <c r="G32" s="10">
-        <v>97.7</v>
+        <v>79.8</v>
       </c>
       <c r="H32" s="10">
-        <v>1460.9</v>
+        <v>1203.9000000000001</v>
       </c>
       <c r="I32" s="10">
-        <v>977.88</v>
+        <v>1005.37</v>
       </c>
       <c r="J32" s="10">
-        <v>49.4</v>
+        <v>19.75</v>
       </c>
       <c r="K32" s="1">
-        <v>57.4</v>
-      </c>
-      <c r="L32" s="14">
+        <v>79.2</v>
+      </c>
+      <c r="L32" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="33" spans="1:12">
+    <row r="33" spans="1:15">
       <c r="A33" s="1">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D33" s="10">
-        <v>90.7</v>
+        <v>88.1</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F33" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G33" s="10">
-        <v>98.1</v>
+        <v>98.9</v>
       </c>
       <c r="H33" s="10">
-        <v>824.5</v>
+        <v>224.68</v>
       </c>
       <c r="I33" s="10">
-        <v>604.44000000000005</v>
+        <v>147.49</v>
       </c>
       <c r="J33" s="10">
-        <v>36.409999999999997</v>
+        <v>52.34</v>
       </c>
       <c r="K33" s="1">
-        <v>56.8</v>
-      </c>
-      <c r="L33" s="14">
+        <v>80</v>
+      </c>
+      <c r="L33" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="34" spans="1:12">
+    <row r="34" spans="1:15">
       <c r="A34" s="1">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D34" s="10">
-        <v>90.5</v>
+        <v>87.1</v>
       </c>
       <c r="E34" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F34" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G34" s="10">
-        <v>84.6</v>
+        <v>96.4</v>
       </c>
       <c r="H34" s="10">
-        <v>1495.4</v>
+        <v>9619.5</v>
       </c>
       <c r="I34" s="10">
-        <v>1230.3800000000001</v>
+        <v>6976.27</v>
       </c>
       <c r="J34" s="10">
-        <v>21.54</v>
+        <v>37.89</v>
       </c>
       <c r="K34" s="1">
         <v>79.2</v>
       </c>
-      <c r="L34" s="14">
+      <c r="L34" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="35" spans="1:12">
+    <row r="35" spans="1:15">
       <c r="A35" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="D35" s="10">
-        <v>90.3</v>
+        <v>87.1</v>
       </c>
       <c r="E35" s="10" t="s">
         <v>33</v>
@@ -8953,36 +9367,36 @@
         <v>34</v>
       </c>
       <c r="G35" s="10">
-        <v>84.2</v>
+        <v>87.8</v>
       </c>
       <c r="H35" s="10">
-        <v>3547.8</v>
+        <v>1386.7</v>
       </c>
       <c r="I35" s="10">
-        <v>3061.42</v>
+        <v>1115.5999999999999</v>
       </c>
       <c r="J35" s="10">
-        <v>15.89</v>
+        <v>24.3</v>
       </c>
       <c r="K35" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L35" s="14">
+        <v>56.8</v>
+      </c>
+      <c r="L35" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="36" spans="1:12">
+    <row r="36" spans="1:15">
       <c r="A36" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="D36" s="10">
-        <v>89</v>
+        <v>86.3</v>
       </c>
       <c r="E36" s="10" t="s">
         <v>33</v>
@@ -8991,36 +9405,36 @@
         <v>34</v>
       </c>
       <c r="G36" s="10">
-        <v>92.8</v>
+        <v>72.8</v>
       </c>
       <c r="H36" s="10">
-        <v>820.7</v>
+        <v>1071.95</v>
       </c>
       <c r="I36" s="10">
-        <v>665.21</v>
+        <v>953.76</v>
       </c>
       <c r="J36" s="10">
-        <v>23.37</v>
+        <v>12.39</v>
       </c>
       <c r="K36" s="1">
-        <v>57.4</v>
-      </c>
-      <c r="L36" s="14">
+        <v>79.2</v>
+      </c>
+      <c r="L36" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="37" spans="1:12">
+    <row r="37" spans="1:15">
       <c r="A37" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D37" s="10">
-        <v>88.8</v>
+        <v>86.3</v>
       </c>
       <c r="E37" s="10" t="s">
         <v>33</v>
@@ -9029,150 +9443,150 @@
         <v>34</v>
       </c>
       <c r="G37" s="10">
-        <v>92.4</v>
+        <v>93.7</v>
       </c>
       <c r="H37" s="10">
-        <v>1278.5</v>
+        <v>8584.5</v>
       </c>
       <c r="I37" s="10">
-        <v>966</v>
+        <v>6950.34</v>
       </c>
       <c r="J37" s="10">
-        <v>32.35</v>
+        <v>23.51</v>
       </c>
       <c r="K37" s="1">
-        <v>57.4</v>
-      </c>
-      <c r="L37" s="14">
+        <v>42.3</v>
+      </c>
+      <c r="L37" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" spans="1:15">
       <c r="A38" s="1">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D38" s="10">
-        <v>88.8</v>
+        <v>86.3</v>
       </c>
       <c r="E38" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G38" s="10">
-        <v>79.8</v>
+        <v>94.1</v>
       </c>
       <c r="H38" s="10">
-        <v>1203.9000000000001</v>
+        <v>1513.6</v>
       </c>
       <c r="I38" s="10">
-        <v>1005.37</v>
+        <v>1185.1199999999999</v>
       </c>
       <c r="J38" s="10">
-        <v>19.75</v>
+        <v>27.72</v>
       </c>
       <c r="K38" s="1">
         <v>79.2</v>
       </c>
-      <c r="L38" s="14">
+      <c r="L38" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:15">
       <c r="A39" s="1">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="D39" s="10">
-        <v>88.1</v>
+        <v>85.7</v>
       </c>
       <c r="E39" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G39" s="10">
-        <v>98.9</v>
+        <v>91.2</v>
       </c>
       <c r="H39" s="10">
-        <v>224.68</v>
+        <v>3002.6</v>
       </c>
       <c r="I39" s="10">
-        <v>147.49</v>
+        <v>2389.2399999999998</v>
       </c>
       <c r="J39" s="10">
-        <v>52.34</v>
+        <v>25.67</v>
       </c>
       <c r="K39" s="1">
-        <v>80</v>
-      </c>
-      <c r="L39" s="14">
+        <v>44</v>
+      </c>
+      <c r="L39" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="40" spans="1:12">
+    <row r="40" spans="1:15">
       <c r="A40" s="1">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D40" s="10">
-        <v>87.1</v>
+        <v>85.4</v>
       </c>
       <c r="E40" s="10" t="s">
         <v>33</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="G40" s="10">
-        <v>96.4</v>
+        <v>88.6</v>
       </c>
       <c r="H40" s="10">
-        <v>9619.5</v>
+        <v>1838</v>
       </c>
       <c r="I40" s="10">
-        <v>6976.27</v>
+        <v>1573</v>
       </c>
       <c r="J40" s="10">
-        <v>37.89</v>
+        <v>16.850000000000001</v>
       </c>
       <c r="K40" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L40" s="14">
+        <v>47.1</v>
+      </c>
+      <c r="L40" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:15">
       <c r="A41" s="1">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D41" s="10">
-        <v>87.1</v>
+        <v>85.2</v>
       </c>
       <c r="E41" s="10" t="s">
         <v>33</v>
@@ -9181,226 +9595,81 @@
         <v>34</v>
       </c>
       <c r="G41" s="10">
-        <v>87.8</v>
+        <v>69.7</v>
       </c>
       <c r="H41" s="10">
-        <v>1386.7</v>
+        <v>8889</v>
       </c>
       <c r="I41" s="10">
-        <v>1115.5999999999999</v>
+        <v>7982.82</v>
       </c>
       <c r="J41" s="10">
-        <v>24.3</v>
+        <v>11.35</v>
       </c>
       <c r="K41" s="1">
-        <v>56.8</v>
-      </c>
-      <c r="L41" s="14">
+        <v>79.2</v>
+      </c>
+      <c r="L41" s="13">
         <v>46290</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
-      <c r="A42" s="1">
-        <v>15</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D42" s="10">
-        <v>86.3</v>
-      </c>
-      <c r="E42" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F42" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G42" s="10">
-        <v>72.8</v>
-      </c>
-      <c r="H42" s="10">
-        <v>1071.95</v>
-      </c>
-      <c r="I42" s="10">
-        <v>953.76</v>
-      </c>
-      <c r="J42" s="10">
-        <v>12.39</v>
-      </c>
-      <c r="K42" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L42" s="14">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12">
-      <c r="A43" s="1">
-        <v>16</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>53</v>
-      </c>
-      <c r="D43" s="10">
-        <v>86.3</v>
-      </c>
-      <c r="E43" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F43" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="10">
-        <v>93.7</v>
-      </c>
-      <c r="H43" s="10">
-        <v>8584.5</v>
-      </c>
-      <c r="I43" s="10">
-        <v>6950.34</v>
-      </c>
-      <c r="J43" s="10">
-        <v>23.51</v>
-      </c>
-      <c r="K43" s="1">
-        <v>42.3</v>
-      </c>
-      <c r="L43" s="14">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12">
-      <c r="A44" s="1">
-        <v>17</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D44" s="10">
-        <v>86.3</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="10">
-        <v>94.1</v>
-      </c>
-      <c r="H44" s="10">
-        <v>1513.6</v>
-      </c>
-      <c r="I44" s="10">
-        <v>1185.1199999999999</v>
-      </c>
-      <c r="J44" s="10">
-        <v>27.72</v>
-      </c>
-      <c r="K44" s="1">
-        <v>79.2</v>
-      </c>
-      <c r="L44" s="14">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12">
-      <c r="A45" s="1">
-        <v>18</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D45" s="10">
-        <v>85.7</v>
-      </c>
-      <c r="E45" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G45" s="10">
-        <v>91.2</v>
-      </c>
-      <c r="H45" s="10">
-        <v>3002.6</v>
-      </c>
-      <c r="I45" s="10">
-        <v>2389.2399999999998</v>
-      </c>
-      <c r="J45" s="10">
-        <v>25.67</v>
-      </c>
-      <c r="K45" s="1">
-        <v>44</v>
-      </c>
-      <c r="L45" s="14">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12">
-      <c r="A46" s="1">
+    <row r="45" spans="1:15">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>81</v>
+        <v>20</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D46" s="10">
-        <v>85.4</v>
+        <v>21</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>22</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="G46" s="10">
-        <v>88.6</v>
-      </c>
-      <c r="H46" s="10">
-        <v>1838</v>
-      </c>
-      <c r="I46" s="10">
-        <v>1573</v>
-      </c>
-      <c r="J46" s="10">
-        <v>16.850000000000001</v>
-      </c>
-      <c r="K46" s="1">
-        <v>47.1</v>
-      </c>
-      <c r="L46" s="14">
-        <v>46290</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12">
+        <v>24</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="I46" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L46" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="N46" s="24"/>
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="A47" s="1">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C47" s="10" t="s">
         <v>32</v>
       </c>
       <c r="D47" s="10">
-        <v>85.2</v>
+        <v>95.6</v>
       </c>
       <c r="E47" s="10" t="s">
         <v>33</v>
@@ -9409,986 +9678,4390 @@
         <v>34</v>
       </c>
       <c r="G47" s="10">
-        <v>69.7</v>
+        <v>99.2</v>
       </c>
       <c r="H47" s="10">
-        <v>8889</v>
-      </c>
-      <c r="I47" s="10">
-        <v>7982.82</v>
+        <v>2007</v>
+      </c>
+      <c r="I47" s="22">
+        <v>1333.97</v>
       </c>
       <c r="J47" s="10">
-        <v>11.35</v>
+        <v>50.45</v>
       </c>
       <c r="K47" s="1">
         <v>79.2</v>
       </c>
-      <c r="L47" s="14">
+      <c r="L47" s="13">
         <v>46290</v>
       </c>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" t="s">
+      <c r="N47" s="24"/>
+      <c r="O47" s="21"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="1">
+        <v>2</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D48" s="10">
+        <v>94.5</v>
+      </c>
+      <c r="E48" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G48" s="10">
+        <v>96.2</v>
+      </c>
+      <c r="H48" s="10">
+        <v>2265.6</v>
+      </c>
+      <c r="I48" s="22">
+        <v>1635.94</v>
+      </c>
+      <c r="J48" s="10">
+        <v>38.49</v>
+      </c>
+      <c r="K48" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L48" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N48" s="24"/>
+      <c r="O48" s="21"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="1">
+        <v>3</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" s="10">
+        <v>94.3</v>
+      </c>
+      <c r="E49" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G49" s="10">
+        <v>95.6</v>
+      </c>
+      <c r="H49" s="10">
+        <v>2835.1</v>
+      </c>
+      <c r="I49" s="22">
+        <v>2099.5</v>
+      </c>
+      <c r="J49" s="10">
+        <v>35.04</v>
+      </c>
+      <c r="K49" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L49" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N49" s="24"/>
+      <c r="O49" s="21"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="1">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D50" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E50" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="10">
+        <v>97.9</v>
+      </c>
+      <c r="H50" s="10">
+        <v>1460.9</v>
+      </c>
+      <c r="I50" s="22">
+        <v>984</v>
+      </c>
+      <c r="J50" s="10">
+        <v>48.47</v>
+      </c>
+      <c r="K50" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L50" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N50" s="24"/>
+      <c r="O50" s="21"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="1">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D51" s="10">
+        <v>90.7</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="10">
+        <v>85.3</v>
+      </c>
+      <c r="H51" s="10">
+        <v>1495.4</v>
+      </c>
+      <c r="I51" s="22">
+        <v>1230.52</v>
+      </c>
+      <c r="J51" s="10">
+        <v>21.53</v>
+      </c>
+      <c r="K51" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L51" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N51" s="24"/>
+      <c r="O51" s="21"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="1">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D52" s="10">
+        <v>90.2</v>
+      </c>
+      <c r="E52" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G52" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H52" s="10">
+        <v>824.5</v>
+      </c>
+      <c r="I52" s="22">
+        <v>605.74</v>
+      </c>
+      <c r="J52" s="10">
+        <v>36.11</v>
+      </c>
+      <c r="K52" s="1">
+        <v>54.1</v>
+      </c>
+      <c r="L52" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N52" s="24"/>
+      <c r="O52" s="21"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="1">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D53" s="10">
+        <v>90</v>
+      </c>
+      <c r="E53" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G53" s="10">
+        <v>83.4</v>
+      </c>
+      <c r="H53" s="10">
+        <v>3547.8</v>
+      </c>
+      <c r="I53" s="10">
+        <v>3083.31</v>
+      </c>
+      <c r="J53" s="10">
+        <v>15.06</v>
+      </c>
+      <c r="K53" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L53" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N53" s="24"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="1">
+        <v>8</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D54" s="10">
+        <v>89.3</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="10">
+        <v>81.3</v>
+      </c>
+      <c r="H54" s="10">
+        <v>1203.9000000000001</v>
+      </c>
+      <c r="I54" s="22">
+        <v>1005.77</v>
+      </c>
+      <c r="J54" s="10">
+        <v>19.7</v>
+      </c>
+      <c r="K54" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L54" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N54" s="24"/>
+      <c r="O54" s="21"/>
+    </row>
+    <row r="55" spans="1:15">
+      <c r="A55" s="1">
+        <v>9</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D55" s="10">
+        <v>89</v>
+      </c>
+      <c r="E55" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G55" s="10">
+        <v>92.9</v>
+      </c>
+      <c r="H55" s="10">
+        <v>1278.5</v>
+      </c>
+      <c r="I55" s="22">
+        <v>967.61</v>
+      </c>
+      <c r="J55" s="10">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="K55" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L55" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N55" s="24"/>
+      <c r="O55" s="21"/>
+    </row>
+    <row r="56" spans="1:15">
+      <c r="A56" s="1">
+        <v>10</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D56" s="10">
+        <v>88.9</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="10">
+        <v>92.6</v>
+      </c>
+      <c r="H56" s="10">
+        <v>820.7</v>
+      </c>
+      <c r="I56" s="22">
+        <v>670.49</v>
+      </c>
+      <c r="J56" s="10">
+        <v>22.4</v>
+      </c>
+      <c r="K56" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L56" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N56" s="24"/>
+      <c r="O56" s="21"/>
+    </row>
+    <row r="57" spans="1:15">
+      <c r="A57" s="1">
+        <v>11</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D57" s="10">
+        <v>88.1</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G57" s="10">
+        <v>98.9</v>
+      </c>
+      <c r="H57" s="10">
+        <v>224.68</v>
+      </c>
+      <c r="I57" s="22">
+        <v>147.49</v>
+      </c>
+      <c r="J57" s="10">
+        <v>52.34</v>
+      </c>
+      <c r="K57" s="1">
+        <v>80</v>
+      </c>
+      <c r="L57" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N57" s="24"/>
+      <c r="O57" s="21"/>
+    </row>
+    <row r="58" spans="1:15">
+      <c r="A58" s="1">
+        <v>12</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="10">
+        <v>87.2</v>
+      </c>
+      <c r="E58" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G58" s="10">
+        <v>96.8</v>
+      </c>
+      <c r="H58" s="10">
+        <v>3272.5</v>
+      </c>
+      <c r="I58" s="22">
+        <v>2632.42</v>
+      </c>
+      <c r="J58" s="10">
+        <v>24.32</v>
+      </c>
+      <c r="K58" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L58" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N58" s="24"/>
+      <c r="O58" s="21"/>
+    </row>
+    <row r="59" spans="1:15">
+      <c r="A59" s="1">
+        <v>13</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D59" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E59" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G59" s="10">
+        <v>96.4</v>
+      </c>
+      <c r="H59" s="10">
+        <v>9619.5</v>
+      </c>
+      <c r="I59" s="10">
+        <v>6976.27</v>
+      </c>
+      <c r="J59" s="10">
+        <v>37.89</v>
+      </c>
+      <c r="K59" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L59" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N59" s="24"/>
+    </row>
+    <row r="60" spans="1:15">
+      <c r="A60" s="1">
+        <v>14</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D60" s="10">
+        <v>87</v>
+      </c>
+      <c r="E60" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G60" s="10">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="H60" s="10">
+        <v>1071.95</v>
+      </c>
+      <c r="I60" s="22">
+        <v>957.54</v>
+      </c>
+      <c r="J60" s="10">
+        <v>11.95</v>
+      </c>
+      <c r="K60" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L60" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N60" s="24"/>
+      <c r="O60" s="21"/>
+    </row>
+    <row r="61" spans="1:15">
+      <c r="A61" s="1">
+        <v>15</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="D61" s="10">
+        <v>86.7</v>
+      </c>
+      <c r="E61" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G61" s="10">
+        <v>88.2</v>
+      </c>
+      <c r="H61" s="10">
+        <v>1386.7</v>
+      </c>
+      <c r="I61" s="22">
+        <v>1117.24</v>
+      </c>
+      <c r="J61" s="10">
+        <v>24.12</v>
+      </c>
+      <c r="K61" s="1">
+        <v>54.1</v>
+      </c>
+      <c r="L61" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N61" s="24"/>
+      <c r="O61" s="21"/>
+    </row>
+    <row r="62" spans="1:15">
+      <c r="A62" s="1">
+        <v>16</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D62" s="10">
+        <v>86.4</v>
+      </c>
+      <c r="E62" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G62" s="10">
+        <v>94.1</v>
+      </c>
+      <c r="H62" s="10">
+        <v>8584.5</v>
+      </c>
+      <c r="I62" s="22">
+        <v>6956.07</v>
+      </c>
+      <c r="J62" s="10">
+        <v>23.41</v>
+      </c>
+      <c r="K62" s="1">
+        <v>42.3</v>
+      </c>
+      <c r="L62" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N62" s="24"/>
+      <c r="O62" s="21"/>
+    </row>
+    <row r="63" spans="1:15">
+      <c r="A63" s="1">
+        <v>17</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D63" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E63" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G63" s="10">
+        <v>94.3</v>
+      </c>
+      <c r="H63" s="10">
+        <v>1513.6</v>
+      </c>
+      <c r="I63" s="22">
+        <v>1186.18</v>
+      </c>
+      <c r="J63" s="10">
+        <v>27.6</v>
+      </c>
+      <c r="K63" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L63" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N63" s="24"/>
+      <c r="O63" s="21"/>
+    </row>
+    <row r="64" spans="1:15">
+      <c r="A64" s="1">
+        <v>18</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D64" s="10">
+        <v>85.8</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G64" s="10">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="H64" s="10">
+        <v>8889</v>
+      </c>
+      <c r="I64" s="10">
+        <v>7992.71</v>
+      </c>
+      <c r="J64" s="10">
+        <v>11.21</v>
+      </c>
+      <c r="K64" s="1">
+        <v>79.2</v>
+      </c>
+      <c r="L64" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N64" s="24"/>
+    </row>
+    <row r="65" spans="1:15">
+      <c r="A65" s="1">
         <v>19</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B65" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="D65" s="10">
+        <v>85.8</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G65" s="10">
+        <v>91.4</v>
+      </c>
+      <c r="H65" s="10">
+        <v>3002.6</v>
+      </c>
+      <c r="I65" s="22">
+        <v>2387.33</v>
+      </c>
+      <c r="J65" s="10">
+        <v>25.77</v>
+      </c>
+      <c r="K65" s="1">
+        <v>44</v>
+      </c>
+      <c r="L65" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N65" s="24"/>
+      <c r="O65" s="21"/>
+    </row>
+    <row r="66" spans="1:15">
+      <c r="A66" s="1">
         <v>20</v>
       </c>
-      <c r="C50" s="7" t="s">
+      <c r="B66" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D66" s="10">
+        <v>85.2</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="10">
+        <v>82.1</v>
+      </c>
+      <c r="H66" s="10">
+        <v>2091.6</v>
+      </c>
+      <c r="I66" s="22">
+        <v>1731.48</v>
+      </c>
+      <c r="J66" s="10">
+        <v>20.8</v>
+      </c>
+      <c r="K66" s="1">
+        <v>57.4</v>
+      </c>
+      <c r="L66" s="13">
+        <v>46290</v>
+      </c>
+      <c r="N66" s="24"/>
+      <c r="O66" s="21"/>
+    </row>
+    <row r="67" spans="1:15">
+      <c r="J67" s="19"/>
+      <c r="M67" s="20"/>
+      <c r="O67" s="21"/>
+    </row>
+    <row r="68" spans="1:15">
+      <c r="J68" s="19"/>
+      <c r="M68" s="20"/>
+      <c r="O68" s="21"/>
+    </row>
+    <row r="71" spans="1:15" ht="93" customHeight="1"/>
+    <row r="72" spans="1:15" ht="60">
+      <c r="A72" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C72" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="D50" s="7" t="s">
+      <c r="D72" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G72" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H72" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I72" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J72" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="73" spans="1:15">
+      <c r="A73" s="1">
+        <v>1</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D73" s="10">
+        <v>91</v>
+      </c>
+      <c r="E73" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G73" s="10">
+        <v>98.1</v>
+      </c>
+      <c r="H73" s="10">
+        <v>3091.1</v>
+      </c>
+      <c r="I73" s="10">
+        <v>2184.92</v>
+      </c>
+      <c r="J73" s="10">
+        <v>41.47</v>
+      </c>
+      <c r="K73" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="L73" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15">
+      <c r="A74" s="1">
+        <v>2</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74" s="10">
+        <v>90</v>
+      </c>
+      <c r="E74" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G74" s="10">
+        <v>98.5</v>
+      </c>
+      <c r="H74" s="10">
+        <v>1474.5</v>
+      </c>
+      <c r="I74" s="10">
+        <v>1016.25</v>
+      </c>
+      <c r="J74" s="10">
+        <v>45.09</v>
+      </c>
+      <c r="K74" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L74" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N74" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="75" spans="1:15">
+      <c r="A75" s="1">
+        <v>3</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D75" s="10">
+        <v>89.6</v>
+      </c>
+      <c r="E75" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G75" s="10">
+        <v>94.2</v>
+      </c>
+      <c r="H75" s="10">
+        <v>1983.1</v>
+      </c>
+      <c r="I75" s="10">
+        <v>1676.41</v>
+      </c>
+      <c r="J75" s="10">
+        <v>18.29</v>
+      </c>
+      <c r="K75" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="L75" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N75" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15">
+      <c r="A76" s="1">
+        <v>4</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D76" s="10">
+        <v>89.5</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G76" s="10">
+        <v>93.7</v>
+      </c>
+      <c r="H76" s="10">
+        <v>1919.2</v>
+      </c>
+      <c r="I76" s="10">
+        <v>1642.3</v>
+      </c>
+      <c r="J76" s="10">
+        <v>16.86</v>
+      </c>
+      <c r="K76" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="L76" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N76" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15">
+      <c r="A77" s="1">
+        <v>5</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D77" s="10">
+        <v>88.7</v>
+      </c>
+      <c r="E77" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G77" s="10">
+        <v>94.8</v>
+      </c>
+      <c r="H77" s="10">
+        <v>283.05</v>
+      </c>
+      <c r="I77" s="10">
+        <v>230.88</v>
+      </c>
+      <c r="J77" s="10">
+        <v>22.6</v>
+      </c>
+      <c r="K77" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L77" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N77" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15">
+      <c r="A78" s="1">
+        <v>6</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D78" s="10">
+        <v>88.6</v>
+      </c>
+      <c r="E78" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F78" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G78" s="10">
+        <v>91.2</v>
+      </c>
+      <c r="H78" s="10">
+        <v>1406.5</v>
+      </c>
+      <c r="I78" s="10">
+        <v>1209.3499999999999</v>
+      </c>
+      <c r="J78" s="10">
+        <v>16.3</v>
+      </c>
+      <c r="K78" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="L78" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N78" s="7" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15">
+      <c r="A79" s="1">
+        <v>7</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C79" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D79" s="10">
+        <v>88.1</v>
+      </c>
+      <c r="E79" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F79" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G79" s="10">
+        <v>99.6</v>
+      </c>
+      <c r="H79" s="10">
+        <v>1489.1</v>
+      </c>
+      <c r="I79" s="10">
+        <v>948.97</v>
+      </c>
+      <c r="J79" s="10">
+        <v>56.92</v>
+      </c>
+      <c r="K79" s="1">
+        <v>41.2</v>
+      </c>
+      <c r="L79" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15">
+      <c r="A80" s="1">
+        <v>8</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D80" s="10">
+        <v>87.8</v>
+      </c>
+      <c r="E80" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G80" s="10">
+        <v>97.9</v>
+      </c>
+      <c r="H80" s="10">
+        <v>391.95</v>
+      </c>
+      <c r="I80" s="10">
+        <v>277.29000000000002</v>
+      </c>
+      <c r="J80" s="10">
+        <v>41.35</v>
+      </c>
+      <c r="K80" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="L80" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:14">
+      <c r="A81" s="1">
+        <v>9</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D81" s="10">
+        <v>86.3</v>
+      </c>
+      <c r="E81" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G81" s="10">
+        <v>87.9</v>
+      </c>
+      <c r="H81" s="10">
+        <v>1097.5999999999999</v>
+      </c>
+      <c r="I81" s="10">
+        <v>924.32</v>
+      </c>
+      <c r="J81" s="10">
+        <v>18.75</v>
+      </c>
+      <c r="K81" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L81" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="82" spans="1:14">
+      <c r="A82" s="1">
+        <v>10</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D82" s="10">
+        <v>86.2</v>
+      </c>
+      <c r="E82" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G82" s="10">
+        <v>92.3</v>
+      </c>
+      <c r="H82" s="10">
+        <v>1195.4000000000001</v>
+      </c>
+      <c r="I82" s="10">
+        <v>963.91</v>
+      </c>
+      <c r="J82" s="10">
+        <v>24.02</v>
+      </c>
+      <c r="K82" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="L82" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:14">
+      <c r="A83" s="1">
+        <v>11</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D83" s="10">
+        <v>85.7</v>
+      </c>
+      <c r="E83" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G83" s="10">
+        <v>82.9</v>
+      </c>
+      <c r="H83" s="10">
+        <v>1132.5</v>
+      </c>
+      <c r="I83" s="10">
+        <v>1018.08</v>
+      </c>
+      <c r="J83" s="10">
+        <v>11.24</v>
+      </c>
+      <c r="K83" s="1">
+        <v>58.3</v>
+      </c>
+      <c r="L83" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N83" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="1">
+        <v>12</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" s="10">
+        <v>83.8</v>
+      </c>
+      <c r="E84" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G84" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="H84" s="10">
+        <v>501.15</v>
+      </c>
+      <c r="I84" s="10">
+        <v>416</v>
+      </c>
+      <c r="J84" s="10">
+        <v>20.47</v>
+      </c>
+      <c r="K84" s="1">
+        <v>80</v>
+      </c>
+      <c r="L84" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N84" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:14">
+      <c r="A85" s="1">
+        <v>13</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C85" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D85" s="10">
+        <v>83.7</v>
+      </c>
+      <c r="E85" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F85" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G85" s="10">
+        <v>86</v>
+      </c>
+      <c r="H85" s="10">
+        <v>343.3</v>
+      </c>
+      <c r="I85" s="10">
+        <v>294.55</v>
+      </c>
+      <c r="J85" s="10">
+        <v>16.55</v>
+      </c>
+      <c r="K85" s="1">
+        <v>42.9</v>
+      </c>
+      <c r="L85" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N85" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="1:14">
+      <c r="A86" s="1">
+        <v>14</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D86" s="10">
+        <v>82.9</v>
+      </c>
+      <c r="E86" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G86" s="10">
+        <v>99.8</v>
+      </c>
+      <c r="H86" s="10">
+        <v>2730</v>
+      </c>
+      <c r="I86" s="10">
+        <v>1423.33</v>
+      </c>
+      <c r="J86" s="10">
+        <v>91.8</v>
+      </c>
+      <c r="K86" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L86" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N86" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14">
+      <c r="A87" s="1">
+        <v>15</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D87" s="10">
+        <v>82.8</v>
+      </c>
+      <c r="E87" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G87" s="10">
+        <v>82.7</v>
+      </c>
+      <c r="H87" s="10">
+        <v>743.7</v>
+      </c>
+      <c r="I87" s="10">
+        <v>673.48</v>
+      </c>
+      <c r="J87" s="10">
+        <v>10.43</v>
+      </c>
+      <c r="K87" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="L87" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N87" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="88" spans="1:14">
+      <c r="A88" s="1">
+        <v>16</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D88" s="10">
+        <v>82.7</v>
+      </c>
+      <c r="E88" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F88" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G88" s="10">
+        <v>83.5</v>
+      </c>
+      <c r="H88" s="10">
+        <v>636.04999999999995</v>
+      </c>
+      <c r="I88" s="10">
+        <v>537.41</v>
+      </c>
+      <c r="J88" s="10">
+        <v>18.350000000000001</v>
+      </c>
+      <c r="K88" s="1">
+        <v>80</v>
+      </c>
+      <c r="L88" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N88" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:14">
+      <c r="A89" s="1">
+        <v>17</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D89" s="10">
+        <v>82.6</v>
+      </c>
+      <c r="E89" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F89" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G89" s="10">
+        <v>82</v>
+      </c>
+      <c r="H89" s="10">
+        <v>10640</v>
+      </c>
+      <c r="I89" s="10">
+        <v>9226.5499999999993</v>
+      </c>
+      <c r="J89" s="10">
+        <v>15.32</v>
+      </c>
+      <c r="K89" s="1">
+        <v>44.4</v>
+      </c>
+      <c r="L89" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N89" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="90" spans="1:14">
+      <c r="A90" s="1">
+        <v>18</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="D90" s="10">
+        <v>82.3</v>
+      </c>
+      <c r="E90" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F90" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G90" s="10">
+        <v>80.2</v>
+      </c>
+      <c r="H90" s="10">
+        <v>497.9</v>
+      </c>
+      <c r="I90" s="10">
+        <v>455.9</v>
+      </c>
+      <c r="J90" s="10">
+        <v>9.2100000000000009</v>
+      </c>
+      <c r="K90" s="1">
+        <v>46.2</v>
+      </c>
+      <c r="L90" s="13">
+        <v>46309</v>
+      </c>
+      <c r="N90" s="7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="91" spans="1:14">
+      <c r="A91" s="1">
+        <v>19</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C91" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D91" s="10">
+        <v>82.2</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G91" s="10">
+        <v>76.2</v>
+      </c>
+      <c r="H91" s="10">
+        <v>4869</v>
+      </c>
+      <c r="I91" s="10">
+        <v>4410.57</v>
+      </c>
+      <c r="J91" s="10">
+        <v>10.39</v>
+      </c>
+      <c r="K91" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L91" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N91" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:14">
+      <c r="A92" s="1">
+        <v>20</v>
+      </c>
+      <c r="B92" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="E50" s="7" t="s">
+      <c r="C92" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="D92" s="10">
+        <v>82.1</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G92" s="10">
+        <v>97.5</v>
+      </c>
+      <c r="H92" s="10">
+        <v>25500</v>
+      </c>
+      <c r="I92" s="10">
+        <v>18462.580000000002</v>
+      </c>
+      <c r="J92" s="10">
+        <v>38.119999999999997</v>
+      </c>
+      <c r="K92" s="1">
+        <v>52.5</v>
+      </c>
+      <c r="L92" s="13">
+        <v>46308</v>
+      </c>
+      <c r="N92" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="97" spans="1:17">
+      <c r="N97" t="s">
+        <v>132</v>
+      </c>
+      <c r="O97" t="s">
+        <v>104</v>
+      </c>
+      <c r="P97" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="98" spans="1:17">
+      <c r="A98" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="29" t="s">
+        <v>21</v>
+      </c>
+      <c r="D98" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E98" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="F98" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="G98" s="29" t="s">
+        <v>25</v>
+      </c>
+      <c r="H98" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="I98" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="J98" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="K98" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="L98" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="99" spans="1:17">
+      <c r="A99" s="1">
+        <v>1</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C99" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D99" s="10">
+        <v>91.3</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G99" s="10">
+        <v>91.9</v>
+      </c>
+      <c r="H99" s="10">
+        <v>187.61</v>
+      </c>
+      <c r="I99" s="10">
+        <v>164.2</v>
+      </c>
+      <c r="J99" s="10">
+        <v>14.26</v>
+      </c>
+      <c r="K99" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L99" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N99" t="s">
+        <v>131</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="P99" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17">
+      <c r="A100" s="1">
+        <v>2</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D100" s="10">
+        <v>90.1</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G100" s="10">
+        <v>88.4</v>
+      </c>
+      <c r="H100" s="10">
+        <v>1063.5999999999999</v>
+      </c>
+      <c r="I100" s="10">
+        <v>988.66</v>
+      </c>
+      <c r="J100" s="10">
+        <v>7.58</v>
+      </c>
+      <c r="K100" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L100" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N100" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="O100" t="s">
+        <v>131</v>
+      </c>
+      <c r="P100" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17">
+      <c r="A101" s="1">
+        <v>3</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D101" s="10">
+        <v>88.3</v>
+      </c>
+      <c r="E101" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F101" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G101" s="10">
+        <v>97.6</v>
+      </c>
+      <c r="H101" s="10">
+        <v>508.05</v>
+      </c>
+      <c r="I101" s="10">
+        <v>389.55</v>
+      </c>
+      <c r="J101" s="10">
+        <v>30.42</v>
+      </c>
+      <c r="K101" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="L101" s="13">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="102" spans="1:17">
+      <c r="A102" s="1">
+        <v>4</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C102" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D102" s="10">
+        <v>88</v>
+      </c>
+      <c r="E102" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F102" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G102" s="10">
+        <v>99.1</v>
+      </c>
+      <c r="H102" s="10">
+        <v>1003.55</v>
+      </c>
+      <c r="I102" s="10">
+        <v>721.82</v>
+      </c>
+      <c r="J102" s="10">
+        <v>39.03</v>
+      </c>
+      <c r="K102" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L102" s="13">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17">
+      <c r="A103" s="1">
+        <v>5</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C103" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D103" s="10">
+        <v>87.2</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G103" s="10">
+        <v>94.5</v>
+      </c>
+      <c r="H103" s="10">
+        <v>7198.5</v>
+      </c>
+      <c r="I103" s="10">
+        <v>6330.3</v>
+      </c>
+      <c r="J103" s="10">
+        <v>13.72</v>
+      </c>
+      <c r="K103" s="1">
+        <v>45.7</v>
+      </c>
+      <c r="L103" s="13">
+        <v>46045</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17">
+      <c r="A104" s="1">
+        <v>6</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D104" s="10">
+        <v>87.1</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G104" s="10">
+        <v>96.7</v>
+      </c>
+      <c r="H104" s="10">
+        <v>278.55</v>
+      </c>
+      <c r="I104" s="10">
+        <v>218.77</v>
+      </c>
+      <c r="J104" s="10">
+        <v>27.32</v>
+      </c>
+      <c r="K104" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L104" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N104" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="O104" s="31"/>
+      <c r="P104" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="Q104" s="33" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17">
+      <c r="A105" s="1">
+        <v>7</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D105" s="10">
+        <v>86.9</v>
+      </c>
+      <c r="E105" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G105" s="10">
+        <v>95.9</v>
+      </c>
+      <c r="H105" s="10">
+        <v>172.77</v>
+      </c>
+      <c r="I105" s="10">
+        <v>143.19</v>
+      </c>
+      <c r="J105" s="10">
+        <v>20.66</v>
+      </c>
+      <c r="K105" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L105" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N105" s="28" t="s">
+        <v>133</v>
+      </c>
+      <c r="O105" s="28"/>
+      <c r="P105" s="32" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17">
+      <c r="A106" s="1">
+        <v>8</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D106" s="10">
+        <v>86.6</v>
+      </c>
+      <c r="E106" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F106" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G106" s="10">
+        <v>99.8</v>
+      </c>
+      <c r="H106" s="10">
+        <v>535.9</v>
+      </c>
+      <c r="I106" s="10">
+        <v>308.12</v>
+      </c>
+      <c r="J106" s="10">
+        <v>73.930000000000007</v>
+      </c>
+      <c r="K106" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L106" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N106" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="107" spans="1:17">
+      <c r="A107" s="1">
+        <v>9</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D107" s="10">
+        <v>86.5</v>
+      </c>
+      <c r="E107" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G107" s="10">
+        <v>99.6</v>
+      </c>
+      <c r="H107" s="10">
+        <v>370.65</v>
+      </c>
+      <c r="I107" s="10">
+        <v>221.01</v>
+      </c>
+      <c r="J107" s="10">
+        <v>67.7</v>
+      </c>
+      <c r="K107" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L107" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N107" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="108" spans="1:17">
+      <c r="A108" s="1">
+        <v>10</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D108" s="10">
+        <v>86.2</v>
+      </c>
+      <c r="E108" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G108" s="10">
+        <v>98.9</v>
+      </c>
+      <c r="H108" s="10">
+        <v>698.7</v>
+      </c>
+      <c r="I108" s="10">
+        <v>481.96</v>
+      </c>
+      <c r="J108" s="10">
+        <v>44.97</v>
+      </c>
+      <c r="K108" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L108" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N108" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="O108" s="1"/>
+      <c r="P108" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17">
+      <c r="A109" s="1">
+        <v>11</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D109" s="10">
+        <v>86.1</v>
+      </c>
+      <c r="E109" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F109" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G109" s="10">
+        <v>98.5</v>
+      </c>
+      <c r="H109" s="10">
+        <v>684.15</v>
+      </c>
+      <c r="I109" s="10">
+        <v>481.21</v>
+      </c>
+      <c r="J109" s="10">
+        <v>42.17</v>
+      </c>
+      <c r="K109" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L109" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N109" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="110" spans="1:17">
+      <c r="A110" s="1">
+        <v>12</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C110" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D110" s="10">
+        <v>85.8</v>
+      </c>
+      <c r="E110" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G110" s="10">
+        <v>93</v>
+      </c>
+      <c r="H110" s="10">
+        <v>296.14999999999998</v>
+      </c>
+      <c r="I110" s="10">
+        <v>259.19</v>
+      </c>
+      <c r="J110" s="10">
+        <v>14.26</v>
+      </c>
+      <c r="K110" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L110" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N110" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O110" s="1"/>
+      <c r="P110" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="111" spans="1:17">
+      <c r="A111" s="1">
+        <v>13</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C111" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D111" s="10">
+        <v>85.7</v>
+      </c>
+      <c r="E111" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G111" s="10">
+        <v>97.4</v>
+      </c>
+      <c r="H111" s="10">
+        <v>950.3</v>
+      </c>
+      <c r="I111" s="10">
+        <v>740.27</v>
+      </c>
+      <c r="J111" s="10">
+        <v>28.37</v>
+      </c>
+      <c r="K111" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L111" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N111" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O111" s="1"/>
+      <c r="P111" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="112" spans="1:17">
+      <c r="A112" s="1">
+        <v>14</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C112" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D112" s="10">
+        <v>85.3</v>
+      </c>
+      <c r="E112" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G112" s="10">
+        <v>91.3</v>
+      </c>
+      <c r="H112" s="10">
+        <v>65.63</v>
+      </c>
+      <c r="I112" s="10">
+        <v>56</v>
+      </c>
+      <c r="J112" s="10">
+        <v>17.190000000000001</v>
+      </c>
+      <c r="K112" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L112" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N112" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" s="1">
+        <v>15</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="D113" s="10">
+        <v>84.7</v>
+      </c>
+      <c r="E113" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G113" s="10">
+        <v>89.7</v>
+      </c>
+      <c r="H113" s="10">
+        <v>1258</v>
+      </c>
+      <c r="I113" s="10">
+        <v>1185</v>
+      </c>
+      <c r="J113" s="10">
+        <v>6.16</v>
+      </c>
+      <c r="K113" s="1">
+        <v>41.5</v>
+      </c>
+      <c r="L113" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O113" s="1"/>
+      <c r="P113" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" s="1">
+        <v>16</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C114" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="D114" s="10">
+        <v>84.2</v>
+      </c>
+      <c r="E114" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F114" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G114" s="10">
+        <v>95</v>
+      </c>
+      <c r="H114" s="10">
+        <v>431.5</v>
+      </c>
+      <c r="I114" s="10">
+        <v>373.64</v>
+      </c>
+      <c r="J114" s="10">
+        <v>15.48</v>
+      </c>
+      <c r="K114" s="1">
+        <v>30</v>
+      </c>
+      <c r="L114" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" s="1">
+        <v>17</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D115" s="10">
         <v>84</v>
       </c>
-      <c r="F50" s="7" t="s">
+      <c r="E115" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G115" s="10">
+        <v>86.5</v>
+      </c>
+      <c r="H115" s="10">
+        <v>155.4</v>
+      </c>
+      <c r="I115" s="10">
+        <v>142.72</v>
+      </c>
+      <c r="J115" s="10">
+        <v>8.89</v>
+      </c>
+      <c r="K115" s="1">
+        <v>43.8</v>
+      </c>
+      <c r="L115" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" s="1">
+        <v>18</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D116" s="10">
+        <v>84</v>
+      </c>
+      <c r="E116" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F116" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="G116" s="10">
+        <v>92.6</v>
+      </c>
+      <c r="H116" s="10">
+        <v>149.03</v>
+      </c>
+      <c r="I116" s="10">
+        <v>130.53</v>
+      </c>
+      <c r="J116" s="10">
+        <v>14.18</v>
+      </c>
+      <c r="K116" s="1">
+        <v>70.599999999999994</v>
+      </c>
+      <c r="L116" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N116" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="O116" s="1"/>
+      <c r="P116" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" s="1">
+        <v>19</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="D117" s="10">
+        <v>83.5</v>
+      </c>
+      <c r="E117" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G117" s="10">
+        <v>98.7</v>
+      </c>
+      <c r="H117" s="10">
+        <v>217.52</v>
+      </c>
+      <c r="I117" s="10">
+        <v>159.75</v>
+      </c>
+      <c r="J117" s="10">
+        <v>36.159999999999997</v>
+      </c>
+      <c r="K117" s="1">
+        <v>20</v>
+      </c>
+      <c r="L117" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N117" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="O117" s="1"/>
+      <c r="P117" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" s="1">
+        <v>20</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C118" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D118" s="10">
+        <v>82.7</v>
+      </c>
+      <c r="E118" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F118" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G118" s="10">
+        <v>85.6</v>
+      </c>
+      <c r="H118" s="10">
+        <v>1701.1</v>
+      </c>
+      <c r="I118" s="10">
+        <v>1528.74</v>
+      </c>
+      <c r="J118" s="10">
+        <v>11.27</v>
+      </c>
+      <c r="K118" s="1">
+        <v>38.5</v>
+      </c>
+      <c r="L118" s="13">
+        <v>46045</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="O118" s="1"/>
+      <c r="P118" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="N119" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="O119" s="1"/>
+      <c r="P119" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="N120" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="O120" s="1"/>
+      <c r="P120" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="N121" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O121" s="1"/>
+      <c r="P121" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="N122" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="O122" s="1"/>
+      <c r="P122" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="N123" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="O123" s="1"/>
+      <c r="P123" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="N124" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="O124" s="1"/>
+      <c r="P124" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B21:B66">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R5:R24">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q30">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min" val="0"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max" val="0"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M51"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" style="36" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="38" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="38" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="37" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="37" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="37" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="37" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="37" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="36" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="99.75" customHeight="1">
+      <c r="A1" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+    </row>
+    <row r="3" spans="1:12" ht="60">
+      <c r="A3" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G50" s="7" t="s">
+      <c r="G3" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="H50" s="7" t="s">
+      <c r="H3" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="I50" s="7" t="s">
+      <c r="I3" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="J50" s="7" t="s">
+      <c r="J3" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K3" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="L50" t="s">
+      <c r="L3" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
-      <c r="A51">
+    <row r="4" spans="1:12">
+      <c r="A4" s="41">
         <v>1</v>
       </c>
-      <c r="B51" t="s">
-        <v>85</v>
-      </c>
-      <c r="C51" s="7" t="s">
+      <c r="B4" s="41" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D4" s="41">
+        <v>95.6</v>
+      </c>
+      <c r="E4" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="42">
+        <v>99.2</v>
+      </c>
+      <c r="H4" s="42">
+        <v>2007</v>
+      </c>
+      <c r="I4" s="42">
+        <v>1333.97</v>
+      </c>
+      <c r="J4" s="42">
+        <v>50.45</v>
+      </c>
+      <c r="K4" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L4" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="41">
+        <v>2</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="41">
+        <v>94.5</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="42">
+        <v>96.2</v>
+      </c>
+      <c r="H5" s="42">
+        <v>2265.6</v>
+      </c>
+      <c r="I5" s="42">
+        <v>1635.94</v>
+      </c>
+      <c r="J5" s="42">
+        <v>38.49</v>
+      </c>
+      <c r="K5" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L5" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="41">
+        <v>3</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D6" s="41">
+        <v>94.3</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G6" s="42">
+        <v>95.6</v>
+      </c>
+      <c r="H6" s="42">
+        <v>2835.1</v>
+      </c>
+      <c r="I6" s="42">
+        <v>2099.5</v>
+      </c>
+      <c r="J6" s="42">
+        <v>35.04</v>
+      </c>
+      <c r="K6" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L6" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="41">
+        <v>4</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="41">
+        <v>90.7</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="42">
+        <v>97.9</v>
+      </c>
+      <c r="H7" s="42">
+        <v>1460.9</v>
+      </c>
+      <c r="I7" s="42">
+        <v>984</v>
+      </c>
+      <c r="J7" s="42">
+        <v>48.47</v>
+      </c>
+      <c r="K7" s="42">
+        <v>57.4</v>
+      </c>
+      <c r="L7" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="41">
+        <v>5</v>
+      </c>
+      <c r="B8" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="41">
+        <v>90.7</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G8" s="42">
+        <v>85.3</v>
+      </c>
+      <c r="H8" s="42">
+        <v>1495.4</v>
+      </c>
+      <c r="I8" s="42">
+        <v>1230.52</v>
+      </c>
+      <c r="J8" s="42">
+        <v>21.53</v>
+      </c>
+      <c r="K8" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L8" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="41">
+        <v>6</v>
+      </c>
+      <c r="B9" s="41" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" s="41">
+        <v>90.2</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" s="42">
+        <v>98.1</v>
+      </c>
+      <c r="H9" s="42">
+        <v>824.5</v>
+      </c>
+      <c r="I9" s="42">
+        <v>605.74</v>
+      </c>
+      <c r="J9" s="42">
+        <v>36.11</v>
+      </c>
+      <c r="K9" s="42">
+        <v>54.1</v>
+      </c>
+      <c r="L9" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="41">
+        <v>7</v>
+      </c>
+      <c r="B10" s="41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" s="41">
+        <v>90</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="42">
+        <v>83.4</v>
+      </c>
+      <c r="H10" s="42">
+        <v>3547.8</v>
+      </c>
+      <c r="I10" s="42">
+        <v>3083.31</v>
+      </c>
+      <c r="J10" s="42">
+        <v>15.06</v>
+      </c>
+      <c r="K10" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L10" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="41">
+        <v>8</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" s="41">
+        <v>89.3</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G11" s="42">
+        <v>81.3</v>
+      </c>
+      <c r="H11" s="42">
+        <v>1203.9000000000001</v>
+      </c>
+      <c r="I11" s="42">
+        <v>1005.77</v>
+      </c>
+      <c r="J11" s="42">
+        <v>19.7</v>
+      </c>
+      <c r="K11" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L11" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="41">
+        <v>9</v>
+      </c>
+      <c r="B12" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="41">
+        <v>89</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G12" s="42">
+        <v>92.9</v>
+      </c>
+      <c r="H12" s="42">
+        <v>1278.5</v>
+      </c>
+      <c r="I12" s="42">
+        <v>967.61</v>
+      </c>
+      <c r="J12" s="42">
+        <v>32.130000000000003</v>
+      </c>
+      <c r="K12" s="42">
+        <v>57.4</v>
+      </c>
+      <c r="L12" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="41">
+        <v>10</v>
+      </c>
+      <c r="B13" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="41">
+        <v>88.9</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="42">
+        <v>92.6</v>
+      </c>
+      <c r="H13" s="42">
+        <v>820.7</v>
+      </c>
+      <c r="I13" s="42">
+        <v>670.49</v>
+      </c>
+      <c r="J13" s="42">
+        <v>22.4</v>
+      </c>
+      <c r="K13" s="42">
+        <v>57.4</v>
+      </c>
+      <c r="L13" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="41">
+        <v>11</v>
+      </c>
+      <c r="B14" s="41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="41">
+        <v>88.1</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="42">
+        <v>98.9</v>
+      </c>
+      <c r="H14" s="42">
+        <v>224.68</v>
+      </c>
+      <c r="I14" s="42">
+        <v>147.49</v>
+      </c>
+      <c r="J14" s="42">
+        <v>52.34</v>
+      </c>
+      <c r="K14" s="42">
+        <v>80</v>
+      </c>
+      <c r="L14" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="41">
+        <v>12</v>
+      </c>
+      <c r="B15" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="41">
+        <v>87.2</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G15" s="42">
+        <v>96.8</v>
+      </c>
+      <c r="H15" s="42">
+        <v>3272.5</v>
+      </c>
+      <c r="I15" s="42">
+        <v>2632.42</v>
+      </c>
+      <c r="J15" s="42">
+        <v>24.32</v>
+      </c>
+      <c r="K15" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L15" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="41">
+        <v>13</v>
+      </c>
+      <c r="B16" s="41" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D16" s="41">
+        <v>87.1</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G16" s="42">
+        <v>96.4</v>
+      </c>
+      <c r="H16" s="42">
+        <v>9619.5</v>
+      </c>
+      <c r="I16" s="42">
+        <v>6976.27</v>
+      </c>
+      <c r="J16" s="42">
+        <v>37.89</v>
+      </c>
+      <c r="K16" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L16" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="41">
+        <v>14</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="41">
+        <v>87</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F17" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" s="42">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="H17" s="42">
+        <v>1071.95</v>
+      </c>
+      <c r="I17" s="42">
+        <v>957.54</v>
+      </c>
+      <c r="J17" s="42">
+        <v>11.95</v>
+      </c>
+      <c r="K17" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L17" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="41">
+        <v>15</v>
+      </c>
+      <c r="B18" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="41">
+        <v>86.7</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="42">
+        <v>88.2</v>
+      </c>
+      <c r="H18" s="42">
+        <v>1386.7</v>
+      </c>
+      <c r="I18" s="42">
+        <v>1117.24</v>
+      </c>
+      <c r="J18" s="42">
+        <v>24.12</v>
+      </c>
+      <c r="K18" s="42">
+        <v>54.1</v>
+      </c>
+      <c r="L18" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="41">
+        <v>16</v>
+      </c>
+      <c r="B19" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" s="41">
+        <v>86.4</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="42">
+        <v>94.1</v>
+      </c>
+      <c r="H19" s="42">
+        <v>8584.5</v>
+      </c>
+      <c r="I19" s="42">
+        <v>6956.07</v>
+      </c>
+      <c r="J19" s="42">
+        <v>23.41</v>
+      </c>
+      <c r="K19" s="42">
+        <v>42.3</v>
+      </c>
+      <c r="L19" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="41">
+        <v>17</v>
+      </c>
+      <c r="B20" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="41">
+        <v>86.3</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G20" s="42">
+        <v>94.3</v>
+      </c>
+      <c r="H20" s="42">
+        <v>1513.6</v>
+      </c>
+      <c r="I20" s="42">
+        <v>1186.18</v>
+      </c>
+      <c r="J20" s="42">
+        <v>27.6</v>
+      </c>
+      <c r="K20" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L20" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="41">
+        <v>18</v>
+      </c>
+      <c r="B21" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C21" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D21" s="41">
+        <v>85.8</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G21" s="42">
+        <v>71.400000000000006</v>
+      </c>
+      <c r="H21" s="42">
+        <v>8889</v>
+      </c>
+      <c r="I21" s="42">
+        <v>7992.71</v>
+      </c>
+      <c r="J21" s="42">
+        <v>11.21</v>
+      </c>
+      <c r="K21" s="42">
+        <v>79.2</v>
+      </c>
+      <c r="L21" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="41">
+        <v>19</v>
+      </c>
+      <c r="B22" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="41">
+        <v>85.8</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G22" s="42">
+        <v>91.4</v>
+      </c>
+      <c r="H22" s="42">
+        <v>3002.6</v>
+      </c>
+      <c r="I22" s="42">
+        <v>2387.33</v>
+      </c>
+      <c r="J22" s="42">
+        <v>25.77</v>
+      </c>
+      <c r="K22" s="42">
+        <v>44</v>
+      </c>
+      <c r="L22" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="41">
+        <v>20</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D23" s="41">
+        <v>85.2</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G23" s="42">
+        <v>82.1</v>
+      </c>
+      <c r="H23" s="42">
+        <v>2091.6</v>
+      </c>
+      <c r="I23" s="42">
+        <v>1731.48</v>
+      </c>
+      <c r="J23" s="42">
+        <v>20.8</v>
+      </c>
+      <c r="K23" s="42">
+        <v>57.4</v>
+      </c>
+      <c r="L23" s="43">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="44"/>
+      <c r="B24" s="44"/>
+      <c r="C24" s="44"/>
+      <c r="D24" s="44"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="44"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="44"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="45"/>
+      <c r="I25" s="45"/>
+      <c r="J25" s="45"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="45"/>
+    </row>
+    <row r="26" spans="1:12" ht="60">
+      <c r="A26" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="L26" s="16" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="41">
+        <v>1</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D27" s="41">
+        <v>90.3</v>
+      </c>
+      <c r="E27" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="42">
+        <v>98.5</v>
+      </c>
+      <c r="H27" s="42">
+        <v>3043.4</v>
+      </c>
+      <c r="I27" s="42">
+        <v>2216.77</v>
+      </c>
+      <c r="J27" s="42">
+        <v>37.29</v>
+      </c>
+      <c r="K27" s="42">
+        <v>54.2</v>
+      </c>
+      <c r="L27" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="41">
+        <v>2</v>
+      </c>
+      <c r="B28" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="C28" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" s="41">
+        <v>89.7</v>
+      </c>
+      <c r="E28" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G28" s="42">
+        <v>97.7</v>
+      </c>
+      <c r="H28" s="42">
+        <v>301.55</v>
+      </c>
+      <c r="I28" s="42">
+        <v>233.74</v>
+      </c>
+      <c r="J28" s="42">
+        <v>29.01</v>
+      </c>
+      <c r="K28" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L28" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="41">
+        <v>3</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D29" s="41">
+        <v>89</v>
+      </c>
+      <c r="E29" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G29" s="42">
+        <v>94.6</v>
+      </c>
+      <c r="H29" s="42">
+        <v>1954.9</v>
+      </c>
+      <c r="I29" s="42">
+        <v>1683.83</v>
+      </c>
+      <c r="J29" s="42">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="K29" s="42">
+        <v>54.2</v>
+      </c>
+      <c r="L29" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="41">
+        <v>4</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>71</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="41">
+        <v>88.8</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G30" s="42">
+        <v>95</v>
+      </c>
+      <c r="H30" s="42">
+        <v>1198.5</v>
+      </c>
+      <c r="I30" s="42">
+        <v>932.52</v>
+      </c>
+      <c r="J30" s="42">
+        <v>28.52</v>
+      </c>
+      <c r="K30" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L30" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="41">
+        <v>5</v>
+      </c>
+      <c r="B31" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D31" s="41">
+        <v>88</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G31" s="42">
+        <v>93.1</v>
+      </c>
+      <c r="H31" s="42">
+        <v>1194.5</v>
+      </c>
+      <c r="I31" s="42">
+        <v>964.63</v>
+      </c>
+      <c r="J31" s="42">
+        <v>23.83</v>
+      </c>
+      <c r="K31" s="42">
+        <v>51.9</v>
+      </c>
+      <c r="L31" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="41">
+        <v>6</v>
+      </c>
+      <c r="B32" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" s="41">
+        <v>88</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="42">
+        <v>98.3</v>
+      </c>
+      <c r="H32" s="42">
+        <v>383.5</v>
+      </c>
+      <c r="I32" s="42">
+        <v>282.39999999999998</v>
+      </c>
+      <c r="J32" s="42">
+        <v>35.799999999999997</v>
+      </c>
+      <c r="K32" s="42">
+        <v>42.9</v>
+      </c>
+      <c r="L32" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="41">
+        <v>7</v>
+      </c>
+      <c r="B33" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="41">
+        <v>87.7</v>
+      </c>
+      <c r="E33" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="42">
         <v>91</v>
       </c>
-      <c r="E51" s="7" t="s">
+      <c r="H33" s="42">
+        <v>1832.6</v>
+      </c>
+      <c r="I33" s="42">
+        <v>1653.34</v>
+      </c>
+      <c r="J33" s="42">
+        <v>10.84</v>
+      </c>
+      <c r="K33" s="42">
+        <v>54.2</v>
+      </c>
+      <c r="L33" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="41">
+        <v>8</v>
+      </c>
+      <c r="B34" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="41">
+        <v>87</v>
+      </c>
+      <c r="E34" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F51" s="7" t="s">
+      <c r="F34" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G34" s="42">
+        <v>90.4</v>
+      </c>
+      <c r="H34" s="42">
+        <v>1790</v>
+      </c>
+      <c r="I34" s="42">
+        <v>1517.25</v>
+      </c>
+      <c r="J34" s="42">
+        <v>17.98</v>
+      </c>
+      <c r="K34" s="42">
+        <v>51.9</v>
+      </c>
+      <c r="L34" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="41">
+        <v>9</v>
+      </c>
+      <c r="B35" s="41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="41">
+        <v>85.5</v>
+      </c>
+      <c r="E35" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G35" s="42">
+        <v>84.8</v>
+      </c>
+      <c r="H35" s="42">
+        <v>1123</v>
+      </c>
+      <c r="I35" s="42">
+        <v>1021.65</v>
+      </c>
+      <c r="J35" s="42">
+        <v>9.92</v>
+      </c>
+      <c r="K35" s="42">
+        <v>54.2</v>
+      </c>
+      <c r="L35" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="41">
+        <v>10</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D36" s="41">
+        <v>84.5</v>
+      </c>
+      <c r="E36" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G36" s="42">
+        <v>88.5</v>
+      </c>
+      <c r="H36" s="42">
+        <v>504</v>
+      </c>
+      <c r="I36" s="42">
+        <v>418.25</v>
+      </c>
+      <c r="J36" s="42">
+        <v>20.5</v>
+      </c>
+      <c r="K36" s="42">
+        <v>80</v>
+      </c>
+      <c r="L36" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="41">
+        <v>11</v>
+      </c>
+      <c r="B37" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="41">
+        <v>84.2</v>
+      </c>
+      <c r="E37" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" s="42">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="H37" s="42">
+        <v>4989</v>
+      </c>
+      <c r="I37" s="42">
+        <v>4432.21</v>
+      </c>
+      <c r="J37" s="42">
+        <v>12.56</v>
+      </c>
+      <c r="K37" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L37" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="41">
+        <v>12</v>
+      </c>
+      <c r="B38" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="D38" s="41">
+        <v>84.1</v>
+      </c>
+      <c r="E38" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G38" s="42">
+        <v>87.3</v>
+      </c>
+      <c r="H38" s="42">
+        <v>340.1</v>
+      </c>
+      <c r="I38" s="42">
+        <v>295.81</v>
+      </c>
+      <c r="J38" s="42">
+        <v>14.97</v>
+      </c>
+      <c r="K38" s="42">
+        <v>42.9</v>
+      </c>
+      <c r="L38" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="41">
+        <v>13</v>
+      </c>
+      <c r="B39" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="D39" s="41">
+        <v>83.6</v>
+      </c>
+      <c r="E39" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G39" s="42">
+        <v>86</v>
+      </c>
+      <c r="H39" s="42">
+        <v>638</v>
+      </c>
+      <c r="I39" s="42">
+        <v>543.64</v>
+      </c>
+      <c r="J39" s="42">
+        <v>17.36</v>
+      </c>
+      <c r="K39" s="42">
+        <v>80</v>
+      </c>
+      <c r="L39" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="41">
+        <v>14</v>
+      </c>
+      <c r="B40" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="41">
+        <v>83.3</v>
+      </c>
+      <c r="E40" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="42">
+        <v>79.400000000000006</v>
+      </c>
+      <c r="H40" s="42">
+        <v>1655.6</v>
+      </c>
+      <c r="I40" s="42">
+        <v>1593.14</v>
+      </c>
+      <c r="J40" s="42">
+        <v>3.92</v>
+      </c>
+      <c r="K40" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L40" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="41">
+        <v>15</v>
+      </c>
+      <c r="B41" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="41">
+        <v>82.9</v>
+      </c>
+      <c r="E41" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G41" s="42">
+        <v>99.8</v>
+      </c>
+      <c r="H41" s="42">
+        <v>2571.5</v>
+      </c>
+      <c r="I41" s="42">
+        <v>1451.4</v>
+      </c>
+      <c r="J41" s="42">
+        <v>77.17</v>
+      </c>
+      <c r="K41" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L41" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="41">
+        <v>16</v>
+      </c>
+      <c r="B42" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="41">
+        <v>82.8</v>
+      </c>
+      <c r="E42" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F42" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G42" s="42">
+        <v>89.6</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1448.9</v>
+      </c>
+      <c r="I42" s="42">
+        <v>1142.69</v>
+      </c>
+      <c r="J42" s="42">
+        <v>26.8</v>
+      </c>
+      <c r="K42" s="42">
+        <v>32.4</v>
+      </c>
+      <c r="L42" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="41">
+        <v>17</v>
+      </c>
+      <c r="B43" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>178</v>
+      </c>
+      <c r="D43" s="41">
+        <v>82.5</v>
+      </c>
+      <c r="E43" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="42">
+        <v>93.8</v>
+      </c>
+      <c r="H43" s="42">
+        <v>1197.7</v>
+      </c>
+      <c r="I43" s="42">
+        <v>977.45</v>
+      </c>
+      <c r="J43" s="42">
+        <v>22.53</v>
+      </c>
+      <c r="K43" s="42">
+        <v>23.1</v>
+      </c>
+      <c r="L43" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="41">
+        <v>18</v>
+      </c>
+      <c r="B44" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" s="41">
+        <v>82.3</v>
+      </c>
+      <c r="E44" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G44" s="42">
         <v>98.1</v>
       </c>
-      <c r="H51" s="7">
-        <v>3091.1</v>
-      </c>
-      <c r="I51" s="7">
-        <v>2184.92</v>
-      </c>
-      <c r="J51" s="7">
-        <v>41.47</v>
-      </c>
-      <c r="K51">
-        <v>58.3</v>
-      </c>
-      <c r="L51" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N51" s="7" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52">
-        <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>38</v>
-      </c>
-      <c r="C52" s="7" t="s">
+      <c r="H44" s="42">
+        <v>1367.7</v>
+      </c>
+      <c r="I44" s="42">
+        <v>1031.31</v>
+      </c>
+      <c r="J44" s="42">
+        <v>32.619999999999997</v>
+      </c>
+      <c r="K44" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L44" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="41">
+        <v>19</v>
+      </c>
+      <c r="B45" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="D52" s="7">
-        <v>90</v>
-      </c>
-      <c r="E52" s="7" t="s">
+      <c r="D45" s="41">
+        <v>82.3</v>
+      </c>
+      <c r="E45" s="42" t="s">
         <v>33</v>
       </c>
-      <c r="F52" s="7" t="s">
+      <c r="F45" s="42" t="s">
+        <v>49</v>
+      </c>
+      <c r="G45" s="42">
+        <v>97.9</v>
+      </c>
+      <c r="H45" s="42">
+        <v>24680</v>
+      </c>
+      <c r="I45" s="42">
+        <v>18567.22</v>
+      </c>
+      <c r="J45" s="42">
+        <v>32.92</v>
+      </c>
+      <c r="K45" s="42">
+        <v>52.5</v>
+      </c>
+      <c r="L45" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="41">
+        <v>20</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>179</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>180</v>
+      </c>
+      <c r="D46" s="41">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="E46" s="42" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="G52" s="7">
-        <v>98.5</v>
-      </c>
-      <c r="H52" s="7">
-        <v>1474.5</v>
-      </c>
-      <c r="I52" s="7">
-        <v>1016.25</v>
-      </c>
-      <c r="J52" s="7">
-        <v>45.09</v>
-      </c>
-      <c r="K52">
-        <v>52.5</v>
-      </c>
-      <c r="L52" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N52" s="7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53">
-        <v>3</v>
-      </c>
-      <c r="B53" t="s">
-        <v>35</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D53" s="7">
-        <v>89.6</v>
-      </c>
-      <c r="E53" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G53" s="7">
-        <v>94.2</v>
-      </c>
-      <c r="H53" s="7">
-        <v>1983.1</v>
-      </c>
-      <c r="I53" s="7">
-        <v>1676.41</v>
-      </c>
-      <c r="J53" s="7">
-        <v>18.29</v>
-      </c>
-      <c r="K53">
-        <v>58.3</v>
-      </c>
-      <c r="L53" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N53" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="54" spans="1:14">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>86</v>
-      </c>
-      <c r="C54" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D54" s="7">
-        <v>89.5</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G54" s="7">
-        <v>93.7</v>
-      </c>
-      <c r="H54" s="7">
-        <v>1919.2</v>
-      </c>
-      <c r="I54" s="7">
-        <v>1642.3</v>
-      </c>
-      <c r="J54" s="7">
-        <v>16.86</v>
-      </c>
-      <c r="K54">
-        <v>58.3</v>
-      </c>
-      <c r="L54" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N54" s="7" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14">
-      <c r="A55">
-        <v>5</v>
-      </c>
-      <c r="B55" t="s">
-        <v>87</v>
-      </c>
-      <c r="C55" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D55" s="7">
-        <v>88.7</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G55" s="7">
-        <v>94.8</v>
-      </c>
-      <c r="H55" s="7">
-        <v>283.05</v>
-      </c>
-      <c r="I55" s="7">
-        <v>230.88</v>
-      </c>
-      <c r="J55" s="7">
-        <v>22.6</v>
-      </c>
-      <c r="K55">
-        <v>52.5</v>
-      </c>
-      <c r="L55" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N55" s="7" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="A56">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
-        <v>54</v>
-      </c>
-      <c r="C56" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="7">
-        <v>88.6</v>
-      </c>
-      <c r="E56" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G56" s="7">
-        <v>91.2</v>
-      </c>
-      <c r="H56" s="7">
-        <v>1406.5</v>
-      </c>
-      <c r="I56" s="7">
-        <v>1209.3499999999999</v>
-      </c>
-      <c r="J56" s="7">
-        <v>16.3</v>
-      </c>
-      <c r="K56">
-        <v>58.3</v>
-      </c>
-      <c r="L56" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N56" s="7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="57" spans="1:14">
-      <c r="A57">
-        <v>7</v>
-      </c>
-      <c r="B57" t="s">
-        <v>88</v>
-      </c>
-      <c r="C57" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D57" s="7">
-        <v>88.1</v>
-      </c>
-      <c r="E57" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G57" s="7">
-        <v>99.6</v>
-      </c>
-      <c r="H57" s="7">
-        <v>1489.1</v>
-      </c>
-      <c r="I57" s="7">
-        <v>948.97</v>
-      </c>
-      <c r="J57" s="7">
-        <v>56.92</v>
-      </c>
-      <c r="K57">
-        <v>41.2</v>
-      </c>
-      <c r="L57" s="13">
-        <v>46309</v>
-      </c>
-      <c r="N57" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14">
-      <c r="A58">
-        <v>8</v>
-      </c>
-      <c r="B58" t="s">
-        <v>90</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D58" s="7">
-        <v>87.8</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F58" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G58" s="7">
-        <v>97.9</v>
-      </c>
-      <c r="H58" s="7">
-        <v>391.95</v>
-      </c>
-      <c r="I58" s="7">
-        <v>277.29000000000002</v>
-      </c>
-      <c r="J58" s="7">
-        <v>41.35</v>
-      </c>
-      <c r="K58">
-        <v>42.9</v>
-      </c>
-      <c r="L58" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N58" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:14">
-      <c r="A59">
-        <v>9</v>
-      </c>
-      <c r="B59" t="s">
-        <v>92</v>
-      </c>
-      <c r="C59" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D59" s="7">
-        <v>86.3</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G59" s="7">
-        <v>87.9</v>
-      </c>
-      <c r="H59" s="7">
-        <v>1097.5999999999999</v>
-      </c>
-      <c r="I59" s="7">
-        <v>924.32</v>
-      </c>
-      <c r="J59" s="7">
-        <v>18.75</v>
-      </c>
-      <c r="K59">
-        <v>52.5</v>
-      </c>
-      <c r="L59" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N59" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="60" spans="1:14">
-      <c r="A60">
-        <v>10</v>
-      </c>
-      <c r="B60" t="s">
-        <v>93</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D60" s="7">
-        <v>86.2</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G60" s="7">
-        <v>92.3</v>
-      </c>
-      <c r="H60" s="7">
-        <v>1195.4000000000001</v>
-      </c>
-      <c r="I60" s="7">
-        <v>963.91</v>
-      </c>
-      <c r="J60" s="7">
-        <v>24.02</v>
-      </c>
-      <c r="K60">
-        <v>44.4</v>
-      </c>
-      <c r="L60" s="13">
-        <v>46309</v>
-      </c>
-      <c r="N60" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:14">
-      <c r="A61">
-        <v>11</v>
-      </c>
-      <c r="B61" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D61" s="7">
-        <v>85.7</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G61" s="7">
-        <v>82.9</v>
-      </c>
-      <c r="H61" s="7">
-        <v>1132.5</v>
-      </c>
-      <c r="I61" s="7">
-        <v>1018.08</v>
-      </c>
-      <c r="J61" s="7">
-        <v>11.24</v>
-      </c>
-      <c r="K61">
-        <v>58.3</v>
-      </c>
-      <c r="L61" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N61" s="7" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="62" spans="1:14">
-      <c r="A62">
-        <v>12</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="7">
-        <v>83.8</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G62" s="7">
-        <v>86.6</v>
-      </c>
-      <c r="H62" s="7">
-        <v>501.15</v>
-      </c>
-      <c r="I62" s="7">
-        <v>416</v>
-      </c>
-      <c r="J62" s="7">
-        <v>20.47</v>
-      </c>
-      <c r="K62">
-        <v>80</v>
-      </c>
-      <c r="L62" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N62" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="63" spans="1:14">
-      <c r="A63">
-        <v>13</v>
-      </c>
-      <c r="B63" t="s">
-        <v>97</v>
-      </c>
-      <c r="C63" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D63" s="7">
-        <v>83.7</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G63" s="7">
-        <v>86</v>
-      </c>
-      <c r="H63" s="7">
-        <v>343.3</v>
-      </c>
-      <c r="I63" s="7">
-        <v>294.55</v>
-      </c>
-      <c r="J63" s="7">
-        <v>16.55</v>
-      </c>
-      <c r="K63">
-        <v>42.9</v>
-      </c>
-      <c r="L63" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N63" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="64" spans="1:14">
-      <c r="A64">
-        <v>14</v>
-      </c>
-      <c r="B64" t="s">
-        <v>98</v>
-      </c>
-      <c r="C64" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D64" s="7">
-        <v>82.9</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G64" s="7">
-        <v>99.8</v>
-      </c>
-      <c r="H64" s="7">
-        <v>2730</v>
-      </c>
-      <c r="I64" s="7">
-        <v>1423.33</v>
-      </c>
-      <c r="J64" s="7">
-        <v>91.8</v>
-      </c>
-      <c r="K64">
-        <v>52.5</v>
-      </c>
-      <c r="L64" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N64" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15">
-      <c r="A65">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>99</v>
-      </c>
-      <c r="C65" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D65" s="7">
-        <v>82.8</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G65" s="7">
-        <v>82.7</v>
-      </c>
-      <c r="H65" s="7">
-        <v>743.7</v>
-      </c>
-      <c r="I65" s="7">
-        <v>673.48</v>
-      </c>
-      <c r="J65" s="7">
-        <v>10.43</v>
-      </c>
-      <c r="K65">
-        <v>44.4</v>
-      </c>
-      <c r="L65" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N65" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15">
-      <c r="A66">
-        <v>16</v>
-      </c>
-      <c r="B66" t="s">
-        <v>100</v>
-      </c>
-      <c r="C66" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="D66" s="7">
-        <v>82.7</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G66" s="7">
-        <v>83.5</v>
-      </c>
-      <c r="H66" s="7">
-        <v>636.04999999999995</v>
-      </c>
-      <c r="I66" s="7">
-        <v>537.41</v>
-      </c>
-      <c r="J66" s="7">
-        <v>18.350000000000001</v>
-      </c>
-      <c r="K66">
-        <v>80</v>
-      </c>
-      <c r="L66" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N66" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15">
-      <c r="A67">
-        <v>17</v>
-      </c>
-      <c r="B67" t="s">
-        <v>101</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="D67" s="7">
-        <v>82.6</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G67" s="7">
-        <v>82</v>
-      </c>
-      <c r="H67" s="7">
-        <v>10640</v>
-      </c>
-      <c r="I67" s="7">
-        <v>9226.5499999999993</v>
-      </c>
-      <c r="J67" s="7">
-        <v>15.32</v>
-      </c>
-      <c r="K67">
-        <v>44.4</v>
-      </c>
-      <c r="L67" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N67" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15">
-      <c r="A68">
-        <v>18</v>
-      </c>
-      <c r="B68" t="s">
-        <v>102</v>
-      </c>
-      <c r="C68" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D68" s="7">
-        <v>82.3</v>
-      </c>
-      <c r="E68" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G68" s="7">
-        <v>80.2</v>
-      </c>
-      <c r="H68" s="7">
-        <v>497.9</v>
-      </c>
-      <c r="I68" s="7">
-        <v>455.9</v>
-      </c>
-      <c r="J68" s="7">
-        <v>9.2100000000000009</v>
-      </c>
-      <c r="K68">
-        <v>46.2</v>
-      </c>
-      <c r="L68" s="13">
-        <v>46309</v>
-      </c>
-      <c r="N68" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15">
-      <c r="A69">
-        <v>19</v>
-      </c>
-      <c r="B69" t="s">
-        <v>103</v>
-      </c>
-      <c r="C69" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D69" s="7">
-        <v>82.2</v>
-      </c>
-      <c r="E69" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F69" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G69" s="7">
-        <v>76.2</v>
-      </c>
-      <c r="H69" s="7">
-        <v>4869</v>
-      </c>
-      <c r="I69" s="7">
-        <v>4410.57</v>
-      </c>
-      <c r="J69" s="7">
-        <v>10.39</v>
-      </c>
-      <c r="K69">
-        <v>52.5</v>
-      </c>
-      <c r="L69" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N69" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="70" spans="1:15">
-      <c r="A70">
-        <v>20</v>
-      </c>
-      <c r="B70" t="s">
-        <v>104</v>
-      </c>
-      <c r="C70" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D70" s="7">
-        <v>82.1</v>
-      </c>
-      <c r="E70" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G70" s="7">
-        <v>97.5</v>
-      </c>
-      <c r="H70" s="7">
-        <v>25500</v>
-      </c>
-      <c r="I70" s="7">
-        <v>18462.580000000002</v>
-      </c>
-      <c r="J70" s="7">
-        <v>38.119999999999997</v>
-      </c>
-      <c r="K70">
-        <v>52.5</v>
-      </c>
-      <c r="L70" s="13">
-        <v>46308</v>
-      </c>
-      <c r="N70" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15">
-      <c r="J77" s="20"/>
-      <c r="M77" s="21"/>
-      <c r="O77" s="22"/>
-    </row>
-    <row r="78" spans="1:15">
-      <c r="J78" s="20"/>
-      <c r="M78" s="21"/>
-      <c r="O78" s="22"/>
-    </row>
-    <row r="79" spans="1:15">
-      <c r="J79" s="20"/>
-      <c r="M79" s="21"/>
-      <c r="O79" s="22"/>
-    </row>
-    <row r="80" spans="1:15">
-      <c r="J80" s="20"/>
-      <c r="M80" s="21"/>
-      <c r="O80" s="22"/>
-    </row>
-    <row r="81" spans="10:15">
-      <c r="J81" s="20"/>
-      <c r="M81" s="21"/>
-      <c r="O81" s="22"/>
-    </row>
-    <row r="82" spans="10:15">
-      <c r="J82" s="20"/>
-      <c r="M82" s="21"/>
-      <c r="O82" s="22"/>
-    </row>
-    <row r="83" spans="10:15">
-      <c r="J83" s="20"/>
-      <c r="M83" s="21"/>
-      <c r="O83" s="22"/>
-    </row>
-    <row r="85" spans="10:15">
-      <c r="J85" s="20"/>
-      <c r="M85" s="21"/>
-      <c r="O85" s="22"/>
-    </row>
-    <row r="86" spans="10:15">
-      <c r="J86" s="20"/>
-      <c r="M86" s="21"/>
-      <c r="O86" s="22"/>
-    </row>
-    <row r="87" spans="10:15">
-      <c r="J87" s="20"/>
-      <c r="M87" s="21"/>
-      <c r="O87" s="22"/>
-    </row>
-    <row r="88" spans="10:15">
-      <c r="J88" s="20"/>
-      <c r="M88" s="21"/>
-      <c r="O88" s="22"/>
-    </row>
-    <row r="89" spans="10:15">
-      <c r="J89" s="20"/>
-      <c r="M89" s="21"/>
-      <c r="O89" s="22"/>
-    </row>
-    <row r="91" spans="10:15">
-      <c r="J91" s="20"/>
-      <c r="M91" s="21"/>
-      <c r="O91" s="22"/>
-    </row>
-    <row r="92" spans="10:15">
-      <c r="J92" s="20"/>
-      <c r="M92" s="21"/>
-      <c r="O92" s="22"/>
-    </row>
-    <row r="93" spans="10:15">
-      <c r="J93" s="20"/>
-      <c r="M93" s="21"/>
-      <c r="O93" s="22"/>
-    </row>
-    <row r="94" spans="10:15">
-      <c r="J94" s="20"/>
-      <c r="M94" s="21"/>
-      <c r="O94" s="22"/>
-    </row>
-    <row r="96" spans="10:15">
-      <c r="J96" s="20"/>
-      <c r="M96" s="21"/>
-      <c r="O96" s="22"/>
-    </row>
-    <row r="97" spans="10:15">
-      <c r="J97" s="20"/>
-      <c r="M97" s="21"/>
-      <c r="O97" s="22"/>
-    </row>
-    <row r="98" spans="10:15">
-      <c r="J98" s="20"/>
-      <c r="M98" s="21"/>
-      <c r="O98" s="22"/>
-    </row>
-    <row r="99" spans="10:15">
-      <c r="J99" s="20"/>
-      <c r="M99" s="21"/>
-      <c r="O99" s="22"/>
+      <c r="G46" s="42">
+        <v>85.6</v>
+      </c>
+      <c r="H46" s="42">
+        <v>325.3</v>
+      </c>
+      <c r="I46" s="42">
+        <v>278.51</v>
+      </c>
+      <c r="J46" s="42">
+        <v>16.8</v>
+      </c>
+      <c r="K46" s="42">
+        <v>34.6</v>
+      </c>
+      <c r="L46" s="43">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="44"/>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="45"/>
+      <c r="G47" s="45"/>
+      <c r="H47" s="45"/>
+      <c r="I47" s="45"/>
+      <c r="J47" s="45"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="45"/>
+    </row>
+    <row r="48" spans="1:12" ht="283.5">
+      <c r="A48" s="46" t="s">
+        <v>183</v>
+      </c>
+      <c r="B48" s="44"/>
+      <c r="C48" s="44"/>
+      <c r="D48" s="44"/>
+      <c r="E48" s="45"/>
+      <c r="F48" s="45"/>
+      <c r="G48" s="45"/>
+      <c r="H48" s="45"/>
+      <c r="I48" s="45"/>
+      <c r="J48" s="45"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="45"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="47"/>
+      <c r="B49" s="44"/>
+      <c r="C49" s="44"/>
+      <c r="D49" s="44"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="45"/>
+      <c r="G49" s="45"/>
+      <c r="H49" s="45"/>
+      <c r="I49" s="45"/>
+      <c r="J49" s="45"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="45"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B50" s="39"/>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="40"/>
+      <c r="F50" s="40"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="B51" s="39"/>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="40"/>
+      <c r="F51" s="40"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
-  </conditionalFormatting>
+  <mergeCells count="1">
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/portfolio_parameter_sweep Study.xlsx
+++ b/portfolio_parameter_sweep Study.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" activeTab="3"/>
+    <workbookView xWindow="600" yWindow="615" windowWidth="28215" windowHeight="11970" tabRatio="426" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="portfolio_parameter_sweep copy" sheetId="1" r:id="rId1"/>
@@ -15,7 +15,7 @@
   <calcPr calcId="124519"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId5"/>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="6" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -1205,9 +1205,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1241,6 +1238,9 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1465,7 +1465,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46309.985704976854" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="42">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="DELL" refreshedDate="46317.958245138892" createdVersion="3" refreshedVersion="3" minRefreshableVersion="3" recordCount="42">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:J43" sheet="portfolio_parameter_sweep copy"/>
   </cacheSource>
@@ -2866,7 +2866,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" createdVersion="3" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="Q3:W15" firstHeaderRow="1" firstDataRow="2" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="10">
     <pivotField axis="axisRow" showAll="0">
@@ -8773,7 +8773,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="21" spans="1:26" ht="45">
+    <row r="21" spans="1:26" ht="60">
       <c r="A21" s="17" t="s">
         <v>19</v>
       </c>
@@ -12342,33 +12342,33 @@
   <dimension ref="A1:M51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.85546875" style="36" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" style="38" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" style="38" customWidth="1"/>
-    <col min="5" max="5" width="11.85546875" style="37" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="37" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" style="37" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" style="37" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9" style="37" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10" style="37" customWidth="1"/>
-    <col min="11" max="11" width="11.85546875" style="37" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="37" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="36" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.85546875" style="35" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="37" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="37" customWidth="1"/>
+    <col min="5" max="5" width="11.85546875" style="36" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9" style="36" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10" style="36" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" style="36" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="36" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.42578125" style="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="99.75" customHeight="1">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="B1" s="35"/>
-      <c r="C1" s="35"/>
-      <c r="D1" s="35"/>
-      <c r="E1" s="35"/>
-      <c r="F1" s="35"/>
-      <c r="G1" s="35"/>
-      <c r="H1" s="35"/>
-      <c r="I1" s="35"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="3" spans="1:12" ht="60">
       <c r="A3" s="15" t="s">
@@ -12409,792 +12409,792 @@
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="41">
+      <c r="A4" s="40">
         <v>1</v>
       </c>
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="41" t="s">
+      <c r="C4" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="41">
+      <c r="D4" s="40">
         <v>95.6</v>
       </c>
-      <c r="E4" s="42" t="s">
+      <c r="E4" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="42">
+      <c r="G4" s="41">
         <v>99.2</v>
       </c>
-      <c r="H4" s="42">
+      <c r="H4" s="41">
         <v>2007</v>
       </c>
-      <c r="I4" s="42">
+      <c r="I4" s="41">
         <v>1333.97</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="41">
         <v>50.45</v>
       </c>
-      <c r="K4" s="42">
+      <c r="K4" s="41">
         <v>79.2</v>
       </c>
-      <c r="L4" s="43">
+      <c r="L4" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="41">
+      <c r="A5" s="40">
         <v>2</v>
       </c>
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="40">
         <v>94.5</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G5" s="42">
+      <c r="G5" s="41">
         <v>96.2</v>
       </c>
-      <c r="H5" s="42">
+      <c r="H5" s="41">
         <v>2265.6</v>
       </c>
-      <c r="I5" s="42">
+      <c r="I5" s="41">
         <v>1635.94</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="41">
         <v>38.49</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="41">
         <v>79.2</v>
       </c>
-      <c r="L5" s="43">
+      <c r="L5" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="41">
+      <c r="A6" s="40">
         <v>3</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="41" t="s">
+      <c r="C6" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="40">
         <v>94.3</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="42" t="s">
+      <c r="F6" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="42">
+      <c r="G6" s="41">
         <v>95.6</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="41">
         <v>2835.1</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="41">
         <v>2099.5</v>
       </c>
-      <c r="J6" s="42">
+      <c r="J6" s="41">
         <v>35.04</v>
       </c>
-      <c r="K6" s="42">
+      <c r="K6" s="41">
         <v>79.2</v>
       </c>
-      <c r="L6" s="43">
+      <c r="L6" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="41">
+      <c r="A7" s="40">
         <v>4</v>
       </c>
-      <c r="B7" s="41" t="s">
+      <c r="B7" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="41" t="s">
+      <c r="C7" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="41">
+      <c r="D7" s="40">
         <v>90.7</v>
       </c>
-      <c r="E7" s="42" t="s">
+      <c r="E7" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F7" s="42" t="s">
+      <c r="F7" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G7" s="42">
+      <c r="G7" s="41">
         <v>97.9</v>
       </c>
-      <c r="H7" s="42">
+      <c r="H7" s="41">
         <v>1460.9</v>
       </c>
-      <c r="I7" s="42">
+      <c r="I7" s="41">
         <v>984</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="41">
         <v>48.47</v>
       </c>
-      <c r="K7" s="42">
+      <c r="K7" s="41">
         <v>57.4</v>
       </c>
-      <c r="L7" s="43">
+      <c r="L7" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="41">
+      <c r="A8" s="40">
         <v>5</v>
       </c>
-      <c r="B8" s="41" t="s">
+      <c r="B8" s="40" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="C8" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="41">
+      <c r="D8" s="40">
         <v>90.7</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="E8" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="42" t="s">
+      <c r="F8" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="41">
         <v>85.3</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="41">
         <v>1495.4</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="41">
         <v>1230.52</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="41">
         <v>21.53</v>
       </c>
-      <c r="K8" s="42">
+      <c r="K8" s="41">
         <v>79.2</v>
       </c>
-      <c r="L8" s="43">
+      <c r="L8" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="41">
+      <c r="A9" s="40">
         <v>6</v>
       </c>
-      <c r="B9" s="41" t="s">
+      <c r="B9" s="40" t="s">
         <v>40</v>
       </c>
-      <c r="C9" s="41" t="s">
+      <c r="C9" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="40">
         <v>90.2</v>
       </c>
-      <c r="E9" s="42" t="s">
+      <c r="E9" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="42" t="s">
+      <c r="F9" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="41">
         <v>98.1</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="41">
         <v>824.5</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="41">
         <v>605.74</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="41">
         <v>36.11</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="41">
         <v>54.1</v>
       </c>
-      <c r="L9" s="43">
+      <c r="L9" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="41">
+      <c r="A10" s="40">
         <v>7</v>
       </c>
-      <c r="B10" s="41" t="s">
+      <c r="B10" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="41" t="s">
+      <c r="C10" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="40">
         <v>90</v>
       </c>
-      <c r="E10" s="42" t="s">
+      <c r="E10" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="42" t="s">
+      <c r="F10" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="41">
         <v>83.4</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="41">
         <v>3547.8</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="41">
         <v>3083.31</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="41">
         <v>15.06</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="41">
         <v>79.2</v>
       </c>
-      <c r="L10" s="43">
+      <c r="L10" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="41">
+      <c r="A11" s="40">
         <v>8</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="41" t="s">
+      <c r="C11" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="41">
+      <c r="D11" s="40">
         <v>89.3</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="E11" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F11" s="42" t="s">
+      <c r="F11" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="41">
         <v>81.3</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="41">
         <v>1203.9000000000001</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="41">
         <v>1005.77</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="41">
         <v>19.7</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="41">
         <v>79.2</v>
       </c>
-      <c r="L11" s="43">
+      <c r="L11" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="41">
+      <c r="A12" s="40">
         <v>9</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="C12" s="41" t="s">
+      <c r="C12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="41">
+      <c r="D12" s="40">
         <v>89</v>
       </c>
-      <c r="E12" s="42" t="s">
+      <c r="E12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="42" t="s">
+      <c r="F12" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="41">
         <v>92.9</v>
       </c>
-      <c r="H12" s="42">
+      <c r="H12" s="41">
         <v>1278.5</v>
       </c>
-      <c r="I12" s="42">
+      <c r="I12" s="41">
         <v>967.61</v>
       </c>
-      <c r="J12" s="42">
+      <c r="J12" s="41">
         <v>32.130000000000003</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="41">
         <v>57.4</v>
       </c>
-      <c r="L12" s="43">
+      <c r="L12" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="41">
+      <c r="A13" s="40">
         <v>10</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="41" t="s">
+      <c r="C13" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="41">
+      <c r="D13" s="40">
         <v>88.9</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="E13" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="42" t="s">
+      <c r="F13" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="42">
+      <c r="G13" s="41">
         <v>92.6</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="41">
         <v>820.7</v>
       </c>
-      <c r="I13" s="42">
+      <c r="I13" s="41">
         <v>670.49</v>
       </c>
-      <c r="J13" s="42">
+      <c r="J13" s="41">
         <v>22.4</v>
       </c>
-      <c r="K13" s="42">
+      <c r="K13" s="41">
         <v>57.4</v>
       </c>
-      <c r="L13" s="43">
+      <c r="L13" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="41">
+      <c r="A14" s="40">
         <v>11</v>
       </c>
-      <c r="B14" s="41" t="s">
+      <c r="B14" s="40" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="41" t="s">
+      <c r="C14" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="D14" s="41">
+      <c r="D14" s="40">
         <v>88.1</v>
       </c>
-      <c r="E14" s="42" t="s">
+      <c r="E14" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="42" t="s">
+      <c r="F14" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="41">
         <v>98.9</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="41">
         <v>224.68</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="41">
         <v>147.49</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="41">
         <v>52.34</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="41">
         <v>80</v>
       </c>
-      <c r="L14" s="43">
+      <c r="L14" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="41">
+      <c r="A15" s="40">
         <v>12</v>
       </c>
-      <c r="B15" s="41" t="s">
+      <c r="B15" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="41" t="s">
+      <c r="C15" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="41">
+      <c r="D15" s="40">
         <v>87.2</v>
       </c>
-      <c r="E15" s="42" t="s">
+      <c r="E15" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F15" s="42" t="s">
+      <c r="F15" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G15" s="42">
+      <c r="G15" s="41">
         <v>96.8</v>
       </c>
-      <c r="H15" s="42">
+      <c r="H15" s="41">
         <v>3272.5</v>
       </c>
-      <c r="I15" s="42">
+      <c r="I15" s="41">
         <v>2632.42</v>
       </c>
-      <c r="J15" s="42">
+      <c r="J15" s="41">
         <v>24.32</v>
       </c>
-      <c r="K15" s="42">
+      <c r="K15" s="41">
         <v>79.2</v>
       </c>
-      <c r="L15" s="43">
+      <c r="L15" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="41">
+      <c r="A16" s="40">
         <v>13</v>
       </c>
-      <c r="B16" s="41" t="s">
+      <c r="B16" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="41" t="s">
+      <c r="C16" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="41">
+      <c r="D16" s="40">
         <v>87.1</v>
       </c>
-      <c r="E16" s="42" t="s">
+      <c r="E16" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F16" s="42" t="s">
+      <c r="F16" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="41">
         <v>96.4</v>
       </c>
-      <c r="H16" s="42">
+      <c r="H16" s="41">
         <v>9619.5</v>
       </c>
-      <c r="I16" s="42">
+      <c r="I16" s="41">
         <v>6976.27</v>
       </c>
-      <c r="J16" s="42">
+      <c r="J16" s="41">
         <v>37.89</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="41">
         <v>79.2</v>
       </c>
-      <c r="L16" s="43">
+      <c r="L16" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="41">
+      <c r="A17" s="40">
         <v>14</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="C17" s="41" t="s">
+      <c r="C17" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D17" s="41">
+      <c r="D17" s="40">
         <v>87</v>
       </c>
-      <c r="E17" s="42" t="s">
+      <c r="E17" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F17" s="42" t="s">
+      <c r="F17" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="42">
+      <c r="G17" s="41">
         <v>74.599999999999994</v>
       </c>
-      <c r="H17" s="42">
+      <c r="H17" s="41">
         <v>1071.95</v>
       </c>
-      <c r="I17" s="42">
+      <c r="I17" s="41">
         <v>957.54</v>
       </c>
-      <c r="J17" s="42">
+      <c r="J17" s="41">
         <v>11.95</v>
       </c>
-      <c r="K17" s="42">
+      <c r="K17" s="41">
         <v>79.2</v>
       </c>
-      <c r="L17" s="43">
+      <c r="L17" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="41">
+      <c r="A18" s="40">
         <v>15</v>
       </c>
-      <c r="B18" s="41" t="s">
+      <c r="B18" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="41" t="s">
+      <c r="C18" s="40" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="41">
+      <c r="D18" s="40">
         <v>86.7</v>
       </c>
-      <c r="E18" s="42" t="s">
+      <c r="E18" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="42" t="s">
+      <c r="F18" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="42">
+      <c r="G18" s="41">
         <v>88.2</v>
       </c>
-      <c r="H18" s="42">
+      <c r="H18" s="41">
         <v>1386.7</v>
       </c>
-      <c r="I18" s="42">
+      <c r="I18" s="41">
         <v>1117.24</v>
       </c>
-      <c r="J18" s="42">
+      <c r="J18" s="41">
         <v>24.12</v>
       </c>
-      <c r="K18" s="42">
+      <c r="K18" s="41">
         <v>54.1</v>
       </c>
-      <c r="L18" s="43">
+      <c r="L18" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="41">
+      <c r="A19" s="40">
         <v>16</v>
       </c>
-      <c r="B19" s="41" t="s">
+      <c r="B19" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="41" t="s">
+      <c r="C19" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="41">
+      <c r="D19" s="40">
         <v>86.4</v>
       </c>
-      <c r="E19" s="42" t="s">
+      <c r="E19" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F19" s="42" t="s">
+      <c r="F19" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G19" s="42">
+      <c r="G19" s="41">
         <v>94.1</v>
       </c>
-      <c r="H19" s="42">
+      <c r="H19" s="41">
         <v>8584.5</v>
       </c>
-      <c r="I19" s="42">
+      <c r="I19" s="41">
         <v>6956.07</v>
       </c>
-      <c r="J19" s="42">
+      <c r="J19" s="41">
         <v>23.41</v>
       </c>
-      <c r="K19" s="42">
+      <c r="K19" s="41">
         <v>42.3</v>
       </c>
-      <c r="L19" s="43">
+      <c r="L19" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="41">
+      <c r="A20" s="40">
         <v>17</v>
       </c>
-      <c r="B20" s="41" t="s">
+      <c r="B20" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C20" s="41" t="s">
+      <c r="C20" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="41">
+      <c r="D20" s="40">
         <v>86.3</v>
       </c>
-      <c r="E20" s="42" t="s">
+      <c r="E20" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="42" t="s">
+      <c r="F20" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G20" s="42">
+      <c r="G20" s="41">
         <v>94.3</v>
       </c>
-      <c r="H20" s="42">
+      <c r="H20" s="41">
         <v>1513.6</v>
       </c>
-      <c r="I20" s="42">
+      <c r="I20" s="41">
         <v>1186.18</v>
       </c>
-      <c r="J20" s="42">
+      <c r="J20" s="41">
         <v>27.6</v>
       </c>
-      <c r="K20" s="42">
+      <c r="K20" s="41">
         <v>79.2</v>
       </c>
-      <c r="L20" s="43">
+      <c r="L20" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="41">
+      <c r="A21" s="40">
         <v>18</v>
       </c>
-      <c r="B21" s="41" t="s">
+      <c r="B21" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="C21" s="41" t="s">
+      <c r="C21" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="41">
+      <c r="D21" s="40">
         <v>85.8</v>
       </c>
-      <c r="E21" s="42" t="s">
+      <c r="E21" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F21" s="42" t="s">
+      <c r="F21" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G21" s="42">
+      <c r="G21" s="41">
         <v>71.400000000000006</v>
       </c>
-      <c r="H21" s="42">
+      <c r="H21" s="41">
         <v>8889</v>
       </c>
-      <c r="I21" s="42">
+      <c r="I21" s="41">
         <v>7992.71</v>
       </c>
-      <c r="J21" s="42">
+      <c r="J21" s="41">
         <v>11.21</v>
       </c>
-      <c r="K21" s="42">
+      <c r="K21" s="41">
         <v>79.2</v>
       </c>
-      <c r="L21" s="43">
+      <c r="L21" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="41">
+      <c r="A22" s="40">
         <v>19</v>
       </c>
-      <c r="B22" s="41" t="s">
+      <c r="B22" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="41" t="s">
+      <c r="C22" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="D22" s="41">
+      <c r="D22" s="40">
         <v>85.8</v>
       </c>
-      <c r="E22" s="42" t="s">
+      <c r="E22" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F22" s="42" t="s">
+      <c r="F22" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="41">
         <v>91.4</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="41">
         <v>3002.6</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="41">
         <v>2387.33</v>
       </c>
-      <c r="J22" s="42">
+      <c r="J22" s="41">
         <v>25.77</v>
       </c>
-      <c r="K22" s="42">
+      <c r="K22" s="41">
         <v>44</v>
       </c>
-      <c r="L22" s="43">
+      <c r="L22" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="41">
+      <c r="A23" s="40">
         <v>20</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="41" t="s">
+      <c r="C23" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D23" s="41">
+      <c r="D23" s="40">
         <v>85.2</v>
       </c>
-      <c r="E23" s="42" t="s">
+      <c r="E23" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="42" t="s">
+      <c r="F23" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G23" s="42">
+      <c r="G23" s="41">
         <v>82.1</v>
       </c>
-      <c r="H23" s="42">
+      <c r="H23" s="41">
         <v>2091.6</v>
       </c>
-      <c r="I23" s="42">
+      <c r="I23" s="41">
         <v>1731.48</v>
       </c>
-      <c r="J23" s="42">
+      <c r="J23" s="41">
         <v>20.8</v>
       </c>
-      <c r="K23" s="42">
+      <c r="K23" s="41">
         <v>57.4</v>
       </c>
-      <c r="L23" s="43">
+      <c r="L23" s="42">
         <v>46290</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="44"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="45"/>
-      <c r="G24" s="45"/>
-      <c r="H24" s="45"/>
-      <c r="I24" s="45"/>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45"/>
+      <c r="A24" s="43"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="44"/>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+      <c r="K24" s="44"/>
+      <c r="L24" s="44"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="44"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="45"/>
-      <c r="I25" s="45"/>
-      <c r="J25" s="45"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="45"/>
+      <c r="A25" s="43"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="44"/>
+      <c r="F25" s="44"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="44"/>
+      <c r="I25" s="44"/>
+      <c r="J25" s="44"/>
+      <c r="K25" s="44"/>
+      <c r="L25" s="44"/>
     </row>
     <row r="26" spans="1:12" ht="60">
       <c r="A26" s="15" t="s">
@@ -13235,828 +13235,828 @@
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="41">
+      <c r="A27" s="40">
         <v>1</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="C27" s="41" t="s">
+      <c r="C27" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D27" s="41">
+      <c r="D27" s="40">
         <v>90.3</v>
       </c>
-      <c r="E27" s="42" t="s">
+      <c r="E27" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="42">
+      <c r="G27" s="41">
         <v>98.5</v>
       </c>
-      <c r="H27" s="42">
+      <c r="H27" s="41">
         <v>3043.4</v>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="41">
         <v>2216.77</v>
       </c>
-      <c r="J27" s="42">
+      <c r="J27" s="41">
         <v>37.29</v>
       </c>
-      <c r="K27" s="42">
+      <c r="K27" s="41">
         <v>54.2</v>
       </c>
-      <c r="L27" s="43">
+      <c r="L27" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="41">
+      <c r="A28" s="40">
         <v>2</v>
       </c>
-      <c r="B28" s="41" t="s">
+      <c r="B28" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D28" s="41">
+      <c r="D28" s="40">
         <v>89.7</v>
       </c>
-      <c r="E28" s="42" t="s">
+      <c r="E28" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G28" s="42">
+      <c r="G28" s="41">
         <v>97.7</v>
       </c>
-      <c r="H28" s="42">
+      <c r="H28" s="41">
         <v>301.55</v>
       </c>
-      <c r="I28" s="42">
+      <c r="I28" s="41">
         <v>233.74</v>
       </c>
-      <c r="J28" s="42">
+      <c r="J28" s="41">
         <v>29.01</v>
       </c>
-      <c r="K28" s="42">
+      <c r="K28" s="41">
         <v>52.5</v>
       </c>
-      <c r="L28" s="43">
+      <c r="L28" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="41">
+      <c r="A29" s="40">
         <v>3</v>
       </c>
-      <c r="B29" s="41" t="s">
+      <c r="B29" s="40" t="s">
         <v>35</v>
       </c>
-      <c r="C29" s="41" t="s">
+      <c r="C29" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D29" s="41">
+      <c r="D29" s="40">
         <v>89</v>
       </c>
-      <c r="E29" s="42" t="s">
+      <c r="E29" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F29" s="42" t="s">
+      <c r="F29" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G29" s="42">
+      <c r="G29" s="41">
         <v>94.6</v>
       </c>
-      <c r="H29" s="42">
+      <c r="H29" s="41">
         <v>1954.9</v>
       </c>
-      <c r="I29" s="42">
+      <c r="I29" s="41">
         <v>1683.83</v>
       </c>
-      <c r="J29" s="42">
+      <c r="J29" s="41">
         <v>16.100000000000001</v>
       </c>
-      <c r="K29" s="42">
+      <c r="K29" s="41">
         <v>54.2</v>
       </c>
-      <c r="L29" s="43">
+      <c r="L29" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="30" spans="1:12">
-      <c r="A30" s="41">
+      <c r="A30" s="40">
         <v>4</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C30" s="41" t="s">
+      <c r="C30" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D30" s="41">
+      <c r="D30" s="40">
         <v>88.8</v>
       </c>
-      <c r="E30" s="42" t="s">
+      <c r="E30" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F30" s="42" t="s">
+      <c r="F30" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G30" s="42">
+      <c r="G30" s="41">
         <v>95</v>
       </c>
-      <c r="H30" s="42">
+      <c r="H30" s="41">
         <v>1198.5</v>
       </c>
-      <c r="I30" s="42">
+      <c r="I30" s="41">
         <v>932.52</v>
       </c>
-      <c r="J30" s="42">
+      <c r="J30" s="41">
         <v>28.52</v>
       </c>
-      <c r="K30" s="42">
+      <c r="K30" s="41">
         <v>52.5</v>
       </c>
-      <c r="L30" s="43">
+      <c r="L30" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="31" spans="1:12">
-      <c r="A31" s="41">
+      <c r="A31" s="40">
         <v>5</v>
       </c>
-      <c r="B31" s="41" t="s">
+      <c r="B31" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="41" t="s">
+      <c r="C31" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="41">
+      <c r="D31" s="40">
         <v>88</v>
       </c>
-      <c r="E31" s="42" t="s">
+      <c r="E31" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F31" s="42" t="s">
+      <c r="F31" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G31" s="42">
+      <c r="G31" s="41">
         <v>93.1</v>
       </c>
-      <c r="H31" s="42">
+      <c r="H31" s="41">
         <v>1194.5</v>
       </c>
-      <c r="I31" s="42">
+      <c r="I31" s="41">
         <v>964.63</v>
       </c>
-      <c r="J31" s="42">
+      <c r="J31" s="41">
         <v>23.83</v>
       </c>
-      <c r="K31" s="42">
+      <c r="K31" s="41">
         <v>51.9</v>
       </c>
-      <c r="L31" s="43">
+      <c r="L31" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="41">
+      <c r="A32" s="40">
         <v>6</v>
       </c>
-      <c r="B32" s="41" t="s">
+      <c r="B32" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C32" s="41" t="s">
+      <c r="C32" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D32" s="41">
+      <c r="D32" s="40">
         <v>88</v>
       </c>
-      <c r="E32" s="42" t="s">
+      <c r="E32" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F32" s="42" t="s">
+      <c r="F32" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G32" s="42">
+      <c r="G32" s="41">
         <v>98.3</v>
       </c>
-      <c r="H32" s="42">
+      <c r="H32" s="41">
         <v>383.5</v>
       </c>
-      <c r="I32" s="42">
+      <c r="I32" s="41">
         <v>282.39999999999998</v>
       </c>
-      <c r="J32" s="42">
+      <c r="J32" s="41">
         <v>35.799999999999997</v>
       </c>
-      <c r="K32" s="42">
+      <c r="K32" s="41">
         <v>42.9</v>
       </c>
-      <c r="L32" s="43">
+      <c r="L32" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="33" spans="1:12">
-      <c r="A33" s="41">
+      <c r="A33" s="40">
         <v>7</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="B33" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="C33" s="41" t="s">
+      <c r="C33" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D33" s="41">
+      <c r="D33" s="40">
         <v>87.7</v>
       </c>
-      <c r="E33" s="42" t="s">
+      <c r="E33" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F33" s="42" t="s">
+      <c r="F33" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G33" s="42">
+      <c r="G33" s="41">
         <v>91</v>
       </c>
-      <c r="H33" s="42">
+      <c r="H33" s="41">
         <v>1832.6</v>
       </c>
-      <c r="I33" s="42">
+      <c r="I33" s="41">
         <v>1653.34</v>
       </c>
-      <c r="J33" s="42">
+      <c r="J33" s="41">
         <v>10.84</v>
       </c>
-      <c r="K33" s="42">
+      <c r="K33" s="41">
         <v>54.2</v>
       </c>
-      <c r="L33" s="43">
+      <c r="L33" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="34" spans="1:12">
-      <c r="A34" s="41">
+      <c r="A34" s="40">
         <v>8</v>
       </c>
-      <c r="B34" s="41" t="s">
+      <c r="B34" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="41" t="s">
+      <c r="C34" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="41">
+      <c r="D34" s="40">
         <v>87</v>
       </c>
-      <c r="E34" s="42" t="s">
+      <c r="E34" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F34" s="42" t="s">
+      <c r="F34" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G34" s="42">
+      <c r="G34" s="41">
         <v>90.4</v>
       </c>
-      <c r="H34" s="42">
+      <c r="H34" s="41">
         <v>1790</v>
       </c>
-      <c r="I34" s="42">
+      <c r="I34" s="41">
         <v>1517.25</v>
       </c>
-      <c r="J34" s="42">
+      <c r="J34" s="41">
         <v>17.98</v>
       </c>
-      <c r="K34" s="42">
+      <c r="K34" s="41">
         <v>51.9</v>
       </c>
-      <c r="L34" s="43">
+      <c r="L34" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="35" spans="1:12">
-      <c r="A35" s="41">
+      <c r="A35" s="40">
         <v>9</v>
       </c>
-      <c r="B35" s="41" t="s">
+      <c r="B35" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="41" t="s">
+      <c r="C35" s="40" t="s">
         <v>32</v>
       </c>
-      <c r="D35" s="41">
+      <c r="D35" s="40">
         <v>85.5</v>
       </c>
-      <c r="E35" s="42" t="s">
+      <c r="E35" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F35" s="42" t="s">
+      <c r="F35" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="42">
+      <c r="G35" s="41">
         <v>84.8</v>
       </c>
-      <c r="H35" s="42">
+      <c r="H35" s="41">
         <v>1123</v>
       </c>
-      <c r="I35" s="42">
+      <c r="I35" s="41">
         <v>1021.65</v>
       </c>
-      <c r="J35" s="42">
+      <c r="J35" s="41">
         <v>9.92</v>
       </c>
-      <c r="K35" s="42">
+      <c r="K35" s="41">
         <v>54.2</v>
       </c>
-      <c r="L35" s="43">
+      <c r="L35" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="36" spans="1:12">
-      <c r="A36" s="41">
+      <c r="A36" s="40">
         <v>10</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="C36" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D36" s="41">
+      <c r="D36" s="40">
         <v>84.5</v>
       </c>
-      <c r="E36" s="42" t="s">
+      <c r="E36" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F36" s="42" t="s">
+      <c r="F36" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G36" s="42">
+      <c r="G36" s="41">
         <v>88.5</v>
       </c>
-      <c r="H36" s="42">
+      <c r="H36" s="41">
         <v>504</v>
       </c>
-      <c r="I36" s="42">
+      <c r="I36" s="41">
         <v>418.25</v>
       </c>
-      <c r="J36" s="42">
+      <c r="J36" s="41">
         <v>20.5</v>
       </c>
-      <c r="K36" s="42">
+      <c r="K36" s="41">
         <v>80</v>
       </c>
-      <c r="L36" s="43">
+      <c r="L36" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="37" spans="1:12">
-      <c r="A37" s="41">
+      <c r="A37" s="40">
         <v>11</v>
       </c>
-      <c r="B37" s="41" t="s">
+      <c r="B37" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C37" s="41" t="s">
+      <c r="C37" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D37" s="41">
+      <c r="D37" s="40">
         <v>84.2</v>
       </c>
-      <c r="E37" s="42" t="s">
+      <c r="E37" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F37" s="42" t="s">
+      <c r="F37" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="42">
+      <c r="G37" s="41">
         <v>81.900000000000006</v>
       </c>
-      <c r="H37" s="42">
+      <c r="H37" s="41">
         <v>4989</v>
       </c>
-      <c r="I37" s="42">
+      <c r="I37" s="41">
         <v>4432.21</v>
       </c>
-      <c r="J37" s="42">
+      <c r="J37" s="41">
         <v>12.56</v>
       </c>
-      <c r="K37" s="42">
+      <c r="K37" s="41">
         <v>52.5</v>
       </c>
-      <c r="L37" s="43">
+      <c r="L37" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="38" spans="1:12">
-      <c r="A38" s="41">
+      <c r="A38" s="40">
         <v>12</v>
       </c>
-      <c r="B38" s="41" t="s">
+      <c r="B38" s="40" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="41" t="s">
+      <c r="C38" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="D38" s="41">
+      <c r="D38" s="40">
         <v>84.1</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G38" s="42">
+      <c r="G38" s="41">
         <v>87.3</v>
       </c>
-      <c r="H38" s="42">
+      <c r="H38" s="41">
         <v>340.1</v>
       </c>
-      <c r="I38" s="42">
+      <c r="I38" s="41">
         <v>295.81</v>
       </c>
-      <c r="J38" s="42">
+      <c r="J38" s="41">
         <v>14.97</v>
       </c>
-      <c r="K38" s="42">
+      <c r="K38" s="41">
         <v>42.9</v>
       </c>
-      <c r="L38" s="43">
+      <c r="L38" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="39" spans="1:12">
-      <c r="A39" s="41">
+      <c r="A39" s="40">
         <v>13</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="C39" s="41" t="s">
+      <c r="C39" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="D39" s="41">
+      <c r="D39" s="40">
         <v>83.6</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="E39" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F39" s="42" t="s">
+      <c r="F39" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G39" s="42">
+      <c r="G39" s="41">
         <v>86</v>
       </c>
-      <c r="H39" s="42">
+      <c r="H39" s="41">
         <v>638</v>
       </c>
-      <c r="I39" s="42">
+      <c r="I39" s="41">
         <v>543.64</v>
       </c>
-      <c r="J39" s="42">
+      <c r="J39" s="41">
         <v>17.36</v>
       </c>
-      <c r="K39" s="42">
+      <c r="K39" s="41">
         <v>80</v>
       </c>
-      <c r="L39" s="43">
+      <c r="L39" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="40" spans="1:12">
-      <c r="A40" s="41">
+      <c r="A40" s="40">
         <v>14</v>
       </c>
-      <c r="B40" s="41" t="s">
+      <c r="B40" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="C40" s="41" t="s">
+      <c r="C40" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="41">
+      <c r="D40" s="40">
         <v>83.3</v>
       </c>
-      <c r="E40" s="42" t="s">
+      <c r="E40" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F40" s="42" t="s">
+      <c r="F40" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G40" s="42">
+      <c r="G40" s="41">
         <v>79.400000000000006</v>
       </c>
-      <c r="H40" s="42">
+      <c r="H40" s="41">
         <v>1655.6</v>
       </c>
-      <c r="I40" s="42">
+      <c r="I40" s="41">
         <v>1593.14</v>
       </c>
-      <c r="J40" s="42">
+      <c r="J40" s="41">
         <v>3.92</v>
       </c>
-      <c r="K40" s="42">
+      <c r="K40" s="41">
         <v>52.5</v>
       </c>
-      <c r="L40" s="43">
+      <c r="L40" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="41" spans="1:12">
-      <c r="A41" s="41">
+      <c r="A41" s="40">
         <v>15</v>
       </c>
-      <c r="B41" s="41" t="s">
+      <c r="B41" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="C41" s="41" t="s">
+      <c r="C41" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D41" s="41">
+      <c r="D41" s="40">
         <v>82.9</v>
       </c>
-      <c r="E41" s="42" t="s">
+      <c r="E41" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F41" s="42" t="s">
+      <c r="F41" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G41" s="42">
+      <c r="G41" s="41">
         <v>99.8</v>
       </c>
-      <c r="H41" s="42">
+      <c r="H41" s="41">
         <v>2571.5</v>
       </c>
-      <c r="I41" s="42">
+      <c r="I41" s="41">
         <v>1451.4</v>
       </c>
-      <c r="J41" s="42">
+      <c r="J41" s="41">
         <v>77.17</v>
       </c>
-      <c r="K41" s="42">
+      <c r="K41" s="41">
         <v>52.5</v>
       </c>
-      <c r="L41" s="43">
+      <c r="L41" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="42" spans="1:12">
-      <c r="A42" s="41">
+      <c r="A42" s="40">
         <v>16</v>
       </c>
-      <c r="B42" s="41" t="s">
+      <c r="B42" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="C42" s="41" t="s">
+      <c r="C42" s="40" t="s">
         <v>109</v>
       </c>
-      <c r="D42" s="41">
+      <c r="D42" s="40">
         <v>82.8</v>
       </c>
-      <c r="E42" s="42" t="s">
+      <c r="E42" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F42" s="42" t="s">
+      <c r="F42" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G42" s="42">
+      <c r="G42" s="41">
         <v>89.6</v>
       </c>
-      <c r="H42" s="42">
+      <c r="H42" s="41">
         <v>1448.9</v>
       </c>
-      <c r="I42" s="42">
+      <c r="I42" s="41">
         <v>1142.69</v>
       </c>
-      <c r="J42" s="42">
+      <c r="J42" s="41">
         <v>26.8</v>
       </c>
-      <c r="K42" s="42">
+      <c r="K42" s="41">
         <v>32.4</v>
       </c>
-      <c r="L42" s="43">
+      <c r="L42" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="43" spans="1:12">
-      <c r="A43" s="41">
+      <c r="A43" s="40">
         <v>17</v>
       </c>
-      <c r="B43" s="41" t="s">
+      <c r="B43" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="C43" s="41" t="s">
+      <c r="C43" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="D43" s="41">
+      <c r="D43" s="40">
         <v>82.5</v>
       </c>
-      <c r="E43" s="42" t="s">
+      <c r="E43" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F43" s="42" t="s">
+      <c r="F43" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="42">
+      <c r="G43" s="41">
         <v>93.8</v>
       </c>
-      <c r="H43" s="42">
+      <c r="H43" s="41">
         <v>1197.7</v>
       </c>
-      <c r="I43" s="42">
+      <c r="I43" s="41">
         <v>977.45</v>
       </c>
-      <c r="J43" s="42">
+      <c r="J43" s="41">
         <v>22.53</v>
       </c>
-      <c r="K43" s="42">
+      <c r="K43" s="41">
         <v>23.1</v>
       </c>
-      <c r="L43" s="43">
+      <c r="L43" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="44" spans="1:12">
-      <c r="A44" s="41">
+      <c r="A44" s="40">
         <v>18</v>
       </c>
-      <c r="B44" s="41" t="s">
+      <c r="B44" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="C44" s="41" t="s">
+      <c r="C44" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D44" s="41">
+      <c r="D44" s="40">
         <v>82.3</v>
       </c>
-      <c r="E44" s="42" t="s">
+      <c r="E44" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F44" s="42" t="s">
+      <c r="F44" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G44" s="42">
+      <c r="G44" s="41">
         <v>98.1</v>
       </c>
-      <c r="H44" s="42">
+      <c r="H44" s="41">
         <v>1367.7</v>
       </c>
-      <c r="I44" s="42">
+      <c r="I44" s="41">
         <v>1031.31</v>
       </c>
-      <c r="J44" s="42">
+      <c r="J44" s="41">
         <v>32.619999999999997</v>
       </c>
-      <c r="K44" s="42">
+      <c r="K44" s="41">
         <v>52.5</v>
       </c>
-      <c r="L44" s="43">
+      <c r="L44" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="45" spans="1:12">
-      <c r="A45" s="41">
+      <c r="A45" s="40">
         <v>19</v>
       </c>
-      <c r="B45" s="41" t="s">
+      <c r="B45" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="C45" s="41" t="s">
+      <c r="C45" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="D45" s="41">
+      <c r="D45" s="40">
         <v>82.3</v>
       </c>
-      <c r="E45" s="42" t="s">
+      <c r="E45" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F45" s="42" t="s">
+      <c r="F45" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="G45" s="42">
+      <c r="G45" s="41">
         <v>97.9</v>
       </c>
-      <c r="H45" s="42">
+      <c r="H45" s="41">
         <v>24680</v>
       </c>
-      <c r="I45" s="42">
+      <c r="I45" s="41">
         <v>18567.22</v>
       </c>
-      <c r="J45" s="42">
+      <c r="J45" s="41">
         <v>32.92</v>
       </c>
-      <c r="K45" s="42">
+      <c r="K45" s="41">
         <v>52.5</v>
       </c>
-      <c r="L45" s="43">
+      <c r="L45" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="46" spans="1:12">
-      <c r="A46" s="41">
+      <c r="A46" s="40">
         <v>20</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="D46" s="41">
+      <c r="D46" s="40">
         <v>81.900000000000006</v>
       </c>
-      <c r="E46" s="42" t="s">
+      <c r="E46" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="F46" s="42" t="s">
+      <c r="F46" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="G46" s="42">
+      <c r="G46" s="41">
         <v>85.6</v>
       </c>
-      <c r="H46" s="42">
+      <c r="H46" s="41">
         <v>325.3</v>
       </c>
-      <c r="I46" s="42">
+      <c r="I46" s="41">
         <v>278.51</v>
       </c>
-      <c r="J46" s="42">
+      <c r="J46" s="41">
         <v>16.8</v>
       </c>
-      <c r="K46" s="42">
+      <c r="K46" s="41">
         <v>34.6</v>
       </c>
-      <c r="L46" s="43">
+      <c r="L46" s="42">
         <v>46311</v>
       </c>
     </row>
     <row r="47" spans="1:12">
-      <c r="A47" s="44"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="45"/>
-      <c r="F47" s="45"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="45"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="45"/>
+      <c r="A47" s="43"/>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="44"/>
+      <c r="F47" s="44"/>
+      <c r="G47" s="44"/>
+      <c r="H47" s="44"/>
+      <c r="I47" s="44"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:12" ht="283.5">
-      <c r="A48" s="46" t="s">
+      <c r="A48" s="45" t="s">
         <v>183</v>
       </c>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="45"/>
-      <c r="F48" s="45"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="45"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="45"/>
+      <c r="B48" s="43"/>
+      <c r="C48" s="43"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="44"/>
+      <c r="F48" s="44"/>
+      <c r="G48" s="44"/>
+      <c r="H48" s="44"/>
+      <c r="I48" s="44"/>
+      <c r="J48" s="44"/>
+      <c r="K48" s="44"/>
+      <c r="L48" s="44"/>
     </row>
     <row r="49" spans="1:12">
-      <c r="A49" s="47"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="45"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="45"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="45"/>
+      <c r="A49" s="46"/>
+      <c r="B49" s="43"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="44"/>
+      <c r="F49" s="44"/>
+      <c r="G49" s="44"/>
+      <c r="H49" s="44"/>
+      <c r="I49" s="44"/>
+      <c r="J49" s="44"/>
+      <c r="K49" s="44"/>
+      <c r="L49" s="44"/>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="B50" s="39"/>
-      <c r="C50" s="39"/>
-      <c r="D50" s="39"/>
-      <c r="E50" s="40"/>
-      <c r="F50" s="40"/>
+      <c r="B50" s="38"/>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="B51" s="39"/>
-      <c r="C51" s="39"/>
-      <c r="D51" s="39"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
+      <c r="B51" s="38"/>
+      <c r="C51" s="38"/>
+      <c r="D51" s="38"/>
+      <c r="E51" s="39"/>
+      <c r="F51" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="1">
